--- a/research/traditional_assets/database/data/belgium/belgium_power.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_power.xlsx
@@ -650,10 +650,10 @@
         <v>0.07082833133253301</v>
       </c>
       <c r="X2">
-        <v>0.1094172271639924</v>
+        <v>0.1093875172917082</v>
       </c>
       <c r="Y2">
-        <v>-0.03858889583145943</v>
+        <v>-0.03855918595917519</v>
       </c>
       <c r="Z2">
         <v>0.425396861062116</v>
@@ -662,10 +662,10 @@
         <v>0.04850661990058097</v>
       </c>
       <c r="AB2">
-        <v>0.06605231358361097</v>
+        <v>0.06604351373266742</v>
       </c>
       <c r="AC2">
-        <v>-0.01754569368302999</v>
+        <v>-0.01753689383208645</v>
       </c>
       <c r="AD2">
         <v>13452.5</v>
@@ -787,10 +787,10 @@
         <v>0.07082833133253301</v>
       </c>
       <c r="X3">
-        <v>0.1094172271639924</v>
+        <v>0.1093875172917082</v>
       </c>
       <c r="Y3">
-        <v>-0.03858889583145943</v>
+        <v>-0.03855918595917519</v>
       </c>
       <c r="Z3">
         <v>0.425396861062116</v>
@@ -799,10 +799,10 @@
         <v>0.04850661990058097</v>
       </c>
       <c r="AB3">
-        <v>0.06605231358361097</v>
+        <v>0.06604351373266742</v>
       </c>
       <c r="AC3">
-        <v>-0.01754569368302999</v>
+        <v>-0.01753689383208645</v>
       </c>
       <c r="AD3">
         <v>13452.5</v>
@@ -1139,49 +1139,49 @@
         <v>2.37207285342585</v>
       </c>
       <c r="F2">
-        <v>3.08200144560983</v>
+        <v>3.04376007283184</v>
       </c>
       <c r="G2">
         <v>11.5067145667608</v>
       </c>
       <c r="H2">
-        <v>2.94286374133949</v>
+        <v>3.10635617141391</v>
       </c>
       <c r="I2">
         <v>0.703807176975918</v>
       </c>
       <c r="J2">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K2">
         <v>5661.4</v>
       </c>
       <c r="L2">
-        <v>14219.6275221252</v>
+        <v>14309.4401267996</v>
       </c>
       <c r="M2">
         <v>16483.1</v>
       </c>
       <c r="N2">
-        <v>15029.3295221252</v>
+        <v>15310.2811267996</v>
       </c>
       <c r="O2">
         <v>13452.5</v>
       </c>
       <c r="P2">
-        <v>3440.502</v>
+        <v>3631.641</v>
       </c>
       <c r="Q2">
-        <v>0.06605231358361099</v>
+        <v>0.0660435137326674</v>
       </c>
       <c r="R2">
-        <v>0.06801129755246819</v>
+        <v>0.06759423476573879</v>
       </c>
       <c r="S2">
         <v>0.0478024624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.109417227163992</v>
+        <v>0.109387517291708</v>
       </c>
       <c r="X2">
-        <v>0.07243091988173921</v>
+        <v>0.0726765640633675</v>
       </c>
       <c r="Y2">
         <v>1.23943906739909</v>
       </c>
       <c r="Z2">
-        <v>0.5188437782287521</v>
+        <v>0.523874258917416</v>
       </c>
       <c r="AA2">
         <v>13452.5</v>
@@ -1236,7 +1236,7 @@
         <v>5661.4</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06866633958432057</v>
+        <v>0.06865566077829674</v>
       </c>
       <c r="C2">
-        <v>17229.59089082184</v>
+        <v>17230.06555804425</v>
       </c>
       <c r="D2">
-        <v>14598.79089082184</v>
+        <v>14599.26555804425</v>
       </c>
       <c r="E2">
         <v>-13452.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06866633958432057</v>
+        <v>0.06865566077829674</v>
       </c>
       <c r="T2">
         <v>0.4454993697880388</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06858344836032877</v>
+        <v>0.06856229625132</v>
       </c>
       <c r="C3">
-        <v>17091.56552079576</v>
+        <v>17098.80863268141</v>
       </c>
       <c r="D3">
-        <v>14651.90452079576</v>
+        <v>14659.14763268141</v>
       </c>
       <c r="E3">
         <v>-13261.361</v>
@@ -1539,37 +1539,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M3">
-        <v>11.01660527226011</v>
+        <v>10.74901067226011</v>
       </c>
       <c r="N3">
-        <v>665.8833947277396</v>
+        <v>666.1509893277397</v>
       </c>
       <c r="O3">
-        <v>166.4708486819349</v>
+        <v>166.5377473319349</v>
       </c>
       <c r="P3">
-        <v>499.4125460458047</v>
+        <v>499.6132419958047</v>
       </c>
       <c r="Q3">
-        <v>1121.512546045805</v>
+        <v>1121.713241995805</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06883956942965633</v>
+        <v>0.06882880972358686</v>
       </c>
       <c r="T3">
         <v>0.4488743650137058</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.44361019309995</v>
+        <v>62.97323731819066</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06850055713633697</v>
+        <v>0.06846893172434326</v>
       </c>
       <c r="C4">
-        <v>16953.92804026269</v>
+        <v>16968.04496934263</v>
       </c>
       <c r="D4">
-        <v>14705.40604026269</v>
+        <v>14719.52296934263</v>
       </c>
       <c r="E4">
         <v>-13070.222</v>
@@ -1621,37 +1621,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M4">
-        <v>22.03321054452021</v>
+        <v>21.49802134452021</v>
       </c>
       <c r="N4">
-        <v>654.8667894554795</v>
+        <v>655.4019786554795</v>
       </c>
       <c r="O4">
-        <v>163.7166973638699</v>
+        <v>163.8504946638699</v>
       </c>
       <c r="P4">
-        <v>491.1500920916096</v>
+        <v>491.5514839916096</v>
       </c>
       <c r="Q4">
-        <v>1113.25009209161</v>
+        <v>1113.65148399161</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06901633457795812</v>
+        <v>0.06900549232082169</v>
       </c>
       <c r="T4">
         <v>0.4523182376929578</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.72180509654997</v>
+        <v>31.48661865909533</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06841766591234517</v>
+        <v>0.06837556719736654</v>
       </c>
       <c r="C5">
-        <v>16816.68271393785</v>
+        <v>16837.78068789748</v>
       </c>
       <c r="D5">
-        <v>14759.29971393785</v>
+        <v>14780.39768789748</v>
       </c>
       <c r="E5">
         <v>-12879.083</v>
@@ -1703,37 +1703,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M5">
-        <v>33.04981581678032</v>
+        <v>32.24703201678032</v>
       </c>
       <c r="N5">
-        <v>643.8501841832194</v>
+        <v>644.6529679832195</v>
       </c>
       <c r="O5">
-        <v>160.9625460458049</v>
+        <v>161.1632419958049</v>
       </c>
       <c r="P5">
-        <v>482.8876381374146</v>
+        <v>483.4897259874146</v>
       </c>
       <c r="Q5">
-        <v>1104.987638137415</v>
+        <v>1105.589725987415</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06919674436849295</v>
+        <v>0.06918581785820568</v>
       </c>
       <c r="T5">
         <v>0.455833118056318</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.48120339769999</v>
+        <v>20.99107910606356</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06833477468835339</v>
+        <v>0.0682822026703898</v>
       </c>
       <c r="C6">
-        <v>16679.83386928527</v>
+        <v>16708.02200987438</v>
       </c>
       <c r="D6">
-        <v>14813.58986928527</v>
+        <v>14841.77800987438</v>
       </c>
       <c r="E6">
         <v>-12687.944</v>
@@ -1785,37 +1785,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M6">
-        <v>44.06642108904042</v>
+        <v>42.99604268904042</v>
       </c>
       <c r="N6">
-        <v>632.8335789109593</v>
+        <v>633.9039573109593</v>
       </c>
       <c r="O6">
-        <v>158.2083947277398</v>
+        <v>158.4759893277398</v>
       </c>
       <c r="P6">
-        <v>474.6251841832195</v>
+        <v>475.4279679832194</v>
       </c>
       <c r="Q6">
-        <v>1096.725184183219</v>
+        <v>1097.527967983219</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06938091269633059</v>
+        <v>0.06936990017761852</v>
       </c>
       <c r="T6">
         <v>0.459421225093915</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.36090254827499</v>
+        <v>15.74330932954766</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06825188346436159</v>
+        <v>0.06818883814341306</v>
       </c>
       <c r="C7">
-        <v>16543.38589767613</v>
+        <v>16578.77526058027</v>
       </c>
       <c r="D7">
-        <v>14868.28089767613</v>
+        <v>14903.67026058027</v>
       </c>
       <c r="E7">
         <v>-12496.805</v>
@@ -1867,37 +1867,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M7">
-        <v>55.08302636130053</v>
+        <v>53.74505336130053</v>
       </c>
       <c r="N7">
-        <v>621.8169736386992</v>
+        <v>623.1549466386992</v>
       </c>
       <c r="O7">
-        <v>155.4542434096748</v>
+        <v>155.7887366596748</v>
       </c>
       <c r="P7">
-        <v>466.3627302290244</v>
+        <v>467.3662099790245</v>
       </c>
       <c r="Q7">
-        <v>1088.462730229024</v>
+        <v>1089.466209979024</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0695689582521227</v>
+        <v>0.06955785791428214</v>
       </c>
       <c r="T7">
         <v>0.4630848712270404</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.28872203861999</v>
+        <v>12.59464746363813</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06816899224036978</v>
+        <v>0.06809547361643631</v>
       </c>
       <c r="C8">
-        <v>16407.34325557277</v>
+        <v>16450.0468712735</v>
       </c>
       <c r="D8">
-        <v>14923.37725557276</v>
+        <v>14966.0808712735</v>
       </c>
       <c r="E8">
         <v>-12305.666</v>
@@ -1949,37 +1949,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M8">
-        <v>66.09963163356063</v>
+        <v>64.49406403356063</v>
       </c>
       <c r="N8">
-        <v>610.8003683664391</v>
+        <v>612.4059359664391</v>
       </c>
       <c r="O8">
-        <v>152.7000920916098</v>
+        <v>153.1014839916098</v>
       </c>
       <c r="P8">
-        <v>458.1002762748293</v>
+        <v>459.3044519748293</v>
       </c>
       <c r="Q8">
-        <v>1080.200276274829</v>
+        <v>1081.404451974829</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06976100477718697</v>
+        <v>0.06974981475172583</v>
       </c>
       <c r="T8">
         <v>0.4668264672778917</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.24060169884999</v>
+        <v>10.49553955303178</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06808610101637799</v>
+        <v>0.06800210908945957</v>
       </c>
       <c r="C9">
-        <v>16271.7104657392</v>
+        <v>16321.84338139157</v>
       </c>
       <c r="D9">
-        <v>14978.8834657392</v>
+        <v>15029.01638139157</v>
       </c>
       <c r="E9">
         <v>-12114.527</v>
@@ -2031,37 +2031,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M9">
-        <v>77.11623690582074</v>
+        <v>75.24307470582075</v>
       </c>
       <c r="N9">
-        <v>599.783763094179</v>
+        <v>601.656925294179</v>
       </c>
       <c r="O9">
-        <v>149.9459407735447</v>
+        <v>150.4142313235448</v>
       </c>
       <c r="P9">
-        <v>449.8378223206342</v>
+        <v>451.2426939706343</v>
       </c>
       <c r="Q9">
-        <v>1071.937822320634</v>
+        <v>1073.342693970634</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06995718133504834</v>
+        <v>0.06994589969320059</v>
       </c>
       <c r="T9">
         <v>0.4706485277599443</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.777658599014279</v>
+        <v>8.996176759741523</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06806920979238622</v>
+        <v>0.06799874456248285</v>
       </c>
       <c r="C10">
-        <v>16091.93296792654</v>
+        <v>16132.98223683093</v>
       </c>
       <c r="D10">
-        <v>14990.24496792654</v>
+        <v>15031.29423683093</v>
       </c>
       <c r="E10">
         <v>-11923.388</v>
@@ -2113,37 +2113,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M10">
-        <v>89.81486537808084</v>
+        <v>88.28575337808084</v>
       </c>
       <c r="N10">
-        <v>587.0851346219189</v>
+        <v>588.6142466219189</v>
       </c>
       <c r="O10">
-        <v>146.7712836554797</v>
+        <v>147.1535616554797</v>
       </c>
       <c r="P10">
-        <v>440.3138509664392</v>
+        <v>441.4606849664392</v>
       </c>
       <c r="Q10">
-        <v>1062.413850966439</v>
+        <v>1063.560684966439</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07015762260068931</v>
+        <v>0.07014624735079435</v>
       </c>
       <c r="T10">
         <v>0.4745536765133457</v>
       </c>
       <c r="U10">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.536614313794829</v>
+        <v>7.667148708593987</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0681430685683944</v>
+        <v>0.0679166300355061</v>
       </c>
       <c r="C11">
-        <v>15851.2411886382</v>
+        <v>15997.65136013562</v>
       </c>
       <c r="D11">
-        <v>14940.6921886382</v>
+        <v>15087.10236013562</v>
       </c>
       <c r="E11">
         <v>-11732.249</v>
@@ -2195,45 +2195,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M11">
-        <v>104.8262757503409</v>
+        <v>99.32147255034094</v>
       </c>
       <c r="N11">
-        <v>572.0737242496588</v>
+        <v>577.5785274496588</v>
       </c>
       <c r="O11">
-        <v>143.0184310624147</v>
+        <v>144.3946318624147</v>
       </c>
       <c r="P11">
-        <v>429.055293187244</v>
+        <v>433.1838955872441</v>
       </c>
       <c r="Q11">
-        <v>1051.155293187244</v>
+        <v>1055.283895587244</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07036246916887182</v>
+        <v>0.07035099825360995</v>
       </c>
       <c r="T11">
         <v>0.4785446527118769</v>
       </c>
       <c r="U11">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04570246249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.457350460605276</v>
+        <v>6.815243296527989</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06808492734440262</v>
+        <v>0.06796201550852937</v>
       </c>
       <c r="C12">
-        <v>15699.08235302048</v>
+        <v>15775.61556390778</v>
       </c>
       <c r="D12">
-        <v>14979.67235302048</v>
+        <v>15056.20556390778</v>
       </c>
       <c r="E12">
         <v>-11541.11</v>
@@ -2277,37 +2277,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M12">
-        <v>116.4736397226011</v>
+        <v>113.6065547226011</v>
       </c>
       <c r="N12">
-        <v>560.4263602773987</v>
+        <v>563.2934452773986</v>
       </c>
       <c r="O12">
-        <v>140.1065900693497</v>
+        <v>140.8233613193497</v>
       </c>
       <c r="P12">
-        <v>420.319770208049</v>
+        <v>422.470083958049</v>
       </c>
       <c r="Q12">
-        <v>1042.419770208049</v>
+        <v>1044.570083958049</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07057186788301395</v>
+        <v>0.07056029917648812</v>
       </c>
       <c r="T12">
         <v>0.4826243172703754</v>
       </c>
       <c r="U12">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.811615414544748</v>
+        <v>5.958282967499728</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06815053612041082</v>
+        <v>0.06795865098155264</v>
       </c>
       <c r="C13">
-        <v>15463.97134434959</v>
+        <v>15586.762669223</v>
       </c>
       <c r="D13">
-        <v>14935.7003443496</v>
+        <v>15058.491669223</v>
       </c>
       <c r="E13">
         <v>-11349.971</v>
@@ -2359,37 +2359,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M13">
-        <v>131.2747971948612</v>
+        <v>126.6492333948612</v>
       </c>
       <c r="N13">
-        <v>545.6252028051385</v>
+        <v>550.2507666051386</v>
       </c>
       <c r="O13">
-        <v>136.4063007012846</v>
+        <v>137.5626916512846</v>
       </c>
       <c r="P13">
-        <v>409.2189021038539</v>
+        <v>412.6880749538539</v>
       </c>
       <c r="Q13">
-        <v>1031.318902103854</v>
+        <v>1034.788074953854</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07078597218623793</v>
+        <v>0.07077430349089166</v>
       </c>
       <c r="T13">
         <v>0.4867956596841211</v>
       </c>
       <c r="U13">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.156359137201527</v>
+        <v>5.34468296298006</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06810364489641901</v>
+        <v>0.0678952864545759</v>
       </c>
       <c r="C14">
-        <v>15304.23318818359</v>
+        <v>15438.80818296828</v>
       </c>
       <c r="D14">
-        <v>14967.10118818359</v>
+        <v>15101.67618296827</v>
       </c>
       <c r="E14">
         <v>-11158.832</v>
@@ -2441,37 +2441,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M14">
-        <v>143.2088696671213</v>
+        <v>138.1628000671213</v>
       </c>
       <c r="N14">
-        <v>533.6911303328785</v>
+        <v>538.7371999328785</v>
       </c>
       <c r="O14">
-        <v>133.4227825832196</v>
+        <v>134.6842999832196</v>
       </c>
       <c r="P14">
-        <v>400.2683477496589</v>
+        <v>404.0528999496589</v>
       </c>
       <c r="Q14">
-        <v>1022.368347749659</v>
+        <v>1026.152899949659</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07100494249635335</v>
+        <v>0.07099317153971345</v>
       </c>
       <c r="T14">
         <v>0.4910618053345428</v>
       </c>
       <c r="U14">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.726662542434734</v>
+        <v>4.899292716065056</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06805675367242722</v>
+        <v>0.06783192192759915</v>
       </c>
       <c r="C15">
-        <v>15144.62734457523</v>
+        <v>15291.10209685724</v>
       </c>
       <c r="D15">
-        <v>14998.63434457524</v>
+        <v>15145.10909685724</v>
       </c>
       <c r="E15">
         <v>-10967.693</v>
@@ -2523,37 +2523,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M15">
-        <v>155.1429421393814</v>
+        <v>149.6763667393814</v>
       </c>
       <c r="N15">
-        <v>521.7570578606184</v>
+        <v>527.2236332606184</v>
       </c>
       <c r="O15">
-        <v>130.4392644651546</v>
+        <v>131.8059083151546</v>
       </c>
       <c r="P15">
-        <v>391.3177933954638</v>
+        <v>395.4177249454638</v>
       </c>
       <c r="Q15">
-        <v>1013.417793395464</v>
+        <v>1017.517724945464</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07122894660670132</v>
+        <v>0.07121707103793343</v>
       </c>
       <c r="T15">
         <v>0.4954260232987673</v>
       </c>
       <c r="U15">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.3630731160936</v>
+        <v>4.522424045598513</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06815686244843543</v>
+        <v>0.06787355740062243</v>
       </c>
       <c r="C16">
-        <v>14886.3279847755</v>
+        <v>15071.39616630807</v>
       </c>
       <c r="D16">
-        <v>14931.4739847755</v>
+        <v>15116.54216630807</v>
       </c>
       <c r="E16">
         <v>-10776.554</v>
@@ -2605,37 +2605,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M16">
-        <v>170.8233390116415</v>
+        <v>163.8658794116415</v>
       </c>
       <c r="N16">
-        <v>506.0766609883583</v>
+        <v>513.0341205883583</v>
       </c>
       <c r="O16">
-        <v>126.5191652470896</v>
+        <v>128.2585301470896</v>
       </c>
       <c r="P16">
-        <v>379.5574957412687</v>
+        <v>384.7755904412687</v>
       </c>
       <c r="Q16">
-        <v>1001.657495741269</v>
+        <v>1006.875590441269</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07145816011496436</v>
+        <v>0.07144617750122831</v>
       </c>
       <c r="T16">
         <v>0.4998917347040203</v>
       </c>
       <c r="U16">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.962573287212642</v>
+        <v>4.130817241700354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06812047122444363</v>
+        <v>0.0678176928736457</v>
       </c>
       <c r="C17">
-        <v>14719.53321159956</v>
+        <v>14918.6117061089</v>
       </c>
       <c r="D17">
-        <v>14955.81821159956</v>
+        <v>15154.8967061089</v>
       </c>
       <c r="E17">
         <v>-10585.415</v>
@@ -2687,37 +2687,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M17">
-        <v>183.0250060839016</v>
+        <v>175.5705850839016</v>
       </c>
       <c r="N17">
-        <v>493.8749939160982</v>
+        <v>501.3294149160982</v>
       </c>
       <c r="O17">
-        <v>123.4687484790246</v>
+        <v>125.3323537290245</v>
       </c>
       <c r="P17">
-        <v>370.4062454370737</v>
+        <v>375.9970611870737</v>
       </c>
       <c r="Q17">
-        <v>992.5062454370736</v>
+        <v>998.0970611870737</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07169276688224535</v>
+        <v>0.07168067470483601</v>
       </c>
       <c r="T17">
         <v>0.5044625216717499</v>
       </c>
       <c r="U17">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.6984017347318</v>
+        <v>3.855429425586998</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06808408000045184</v>
+        <v>0.06776182834666895</v>
       </c>
       <c r="C18">
-        <v>14552.81794955544</v>
+        <v>14766.02237157865</v>
       </c>
       <c r="D18">
-        <v>14980.24194955544</v>
+        <v>15193.44637157865</v>
       </c>
       <c r="E18">
         <v>-10394.276</v>
@@ -2769,37 +2769,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M18">
-        <v>195.2266731561617</v>
+        <v>187.2752907561617</v>
       </c>
       <c r="N18">
-        <v>481.673326843838</v>
+        <v>489.6247092438381</v>
       </c>
       <c r="O18">
-        <v>120.4183317109595</v>
+        <v>122.4061773109595</v>
       </c>
       <c r="P18">
-        <v>361.2549951328785</v>
+        <v>367.2185319328786</v>
       </c>
       <c r="Q18">
-        <v>983.3549951328786</v>
+        <v>989.3185319328786</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07193295952493779</v>
+        <v>0.07192075517519628</v>
       </c>
       <c r="T18">
         <v>0.5091421369006158</v>
       </c>
       <c r="U18">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.467251626311062</v>
+        <v>3.61446508648781</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06804768877646004</v>
+        <v>0.06770596381969222</v>
       </c>
       <c r="C19">
-        <v>14386.1825888195</v>
+        <v>14613.62965554409</v>
       </c>
       <c r="D19">
-        <v>15004.7455888195</v>
+        <v>15232.19265554409</v>
       </c>
       <c r="E19">
         <v>-10203.137</v>
@@ -2851,37 +2851,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M19">
-        <v>207.4283402284218</v>
+        <v>198.9799964284218</v>
       </c>
       <c r="N19">
-        <v>469.4716597715779</v>
+        <v>477.9200035715779</v>
       </c>
       <c r="O19">
-        <v>117.3679149428945</v>
+        <v>119.4800008928945</v>
       </c>
       <c r="P19">
-        <v>352.1037448286835</v>
+        <v>358.4400026786834</v>
       </c>
       <c r="Q19">
-        <v>974.2037448286835</v>
+        <v>980.5400026786834</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07217893994215295</v>
+        <v>0.07216662071713148</v>
       </c>
       <c r="T19">
         <v>0.5139345139422256</v>
       </c>
       <c r="U19">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.263295648292764</v>
+        <v>3.401849493164998</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06801129755246824</v>
+        <v>0.06765009929271548</v>
       </c>
       <c r="C20">
-        <v>14219.6275221252</v>
+        <v>14461.43506609898</v>
       </c>
       <c r="D20">
-        <v>15029.3295221252</v>
+        <v>15271.13706609898</v>
       </c>
       <c r="E20">
         <v>-10011.998</v>
@@ -2933,37 +2933,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M20">
-        <v>219.6300073006819</v>
+        <v>210.6847021006819</v>
       </c>
       <c r="N20">
-        <v>457.2699926993179</v>
+        <v>466.2152978993179</v>
       </c>
       <c r="O20">
-        <v>114.3174981748295</v>
+        <v>116.5538244748295</v>
       </c>
       <c r="P20">
-        <v>342.9524945244884</v>
+        <v>349.6614734244884</v>
       </c>
       <c r="Q20">
-        <v>965.0524945244885</v>
+        <v>971.7614734244885</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07243091988173919</v>
+        <v>0.07241848297960168</v>
       </c>
       <c r="T20">
         <v>0.5188437782287525</v>
       </c>
       <c r="U20">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.082001445609833</v>
+        <v>3.212857854655832</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06834540632847645</v>
+        <v>0.06759423476573875</v>
       </c>
       <c r="C21">
-        <v>13805.76328853653</v>
+        <v>14309.44012679964</v>
       </c>
       <c r="D21">
-        <v>14806.60428853653</v>
+        <v>15310.28112679963</v>
       </c>
       <c r="E21">
         <v>-9820.859</v>
@@ -3015,45 +3015,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M21">
-        <v>241.273940972942</v>
+        <v>222.389407772942</v>
       </c>
       <c r="N21">
-        <v>435.6260590270577</v>
+        <v>454.5105922270577</v>
       </c>
       <c r="O21">
-        <v>108.9065147567644</v>
+        <v>113.6276480567644</v>
       </c>
       <c r="P21">
-        <v>326.7195442702933</v>
+        <v>340.8829441702933</v>
       </c>
       <c r="Q21">
-        <v>948.8195442702934</v>
+        <v>962.9829441702933</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07268912154822882</v>
+        <v>0.07267656406336746</v>
       </c>
       <c r="T21">
         <v>0.5238742589174161</v>
       </c>
       <c r="U21">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.805524696411005</v>
+        <v>3.04376007283184</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06832851510448465</v>
+        <v>0.06791337023876201</v>
       </c>
       <c r="C22">
-        <v>13625.72584886732</v>
+        <v>13897.34639413045</v>
       </c>
       <c r="D22">
-        <v>14817.70584886732</v>
+        <v>15089.32639413045</v>
       </c>
       <c r="E22">
         <v>-9629.719999999999</v>
@@ -3097,37 +3097,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M22">
-        <v>253.9725694452021</v>
+        <v>243.6510634452021</v>
       </c>
       <c r="N22">
-        <v>422.9274305547976</v>
+        <v>433.2489365547976</v>
       </c>
       <c r="O22">
-        <v>105.7318576386994</v>
+        <v>108.3122341386994</v>
       </c>
       <c r="P22">
-        <v>317.1955729160982</v>
+        <v>324.9367024160982</v>
       </c>
       <c r="Q22">
-        <v>939.2955729160983</v>
+        <v>947.0367024160983</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07295377825638068</v>
+        <v>0.07294109717422737</v>
       </c>
       <c r="T22">
         <v>0.5290305016232961</v>
       </c>
       <c r="U22">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.665248461590454</v>
+        <v>2.778153275543723</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06831162388049286</v>
+        <v>0.06787625571178527</v>
       </c>
       <c r="C23">
-        <v>13445.70506894182</v>
+        <v>13731.57551899852</v>
       </c>
       <c r="D23">
-        <v>14828.82406894182</v>
+        <v>15114.69451899852</v>
       </c>
       <c r="E23">
         <v>-9438.581</v>
@@ -3179,37 +3179,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M23">
-        <v>266.6711979174622</v>
+        <v>255.8336166174622</v>
       </c>
       <c r="N23">
-        <v>410.2288020825376</v>
+        <v>421.0663833825375</v>
       </c>
       <c r="O23">
-        <v>102.5572005206344</v>
+        <v>105.2665958456344</v>
       </c>
       <c r="P23">
-        <v>307.6716015619032</v>
+        <v>315.7997875369032</v>
       </c>
       <c r="Q23">
-        <v>929.7716015619033</v>
+        <v>937.8997875369032</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07322513513435916</v>
+        <v>0.07321232732586855</v>
       </c>
       <c r="T23">
         <v>0.5343172821191985</v>
       </c>
       <c r="U23">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.538331868181386</v>
+        <v>2.645860262422594</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06874023265650106</v>
+        <v>0.06783914118480854</v>
       </c>
       <c r="C24">
-        <v>12977.50854171448</v>
+        <v>13565.89008512282</v>
       </c>
       <c r="D24">
-        <v>14551.76654171448</v>
+        <v>15140.14808512282</v>
       </c>
       <c r="E24">
         <v>-9247.441999999999</v>
@@ -3261,45 +3261,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M24">
-        <v>290.7234829897223</v>
+        <v>268.0161697897223</v>
       </c>
       <c r="N24">
-        <v>386.1765170102775</v>
+        <v>408.8838302102774</v>
       </c>
       <c r="O24">
-        <v>96.54412925256936</v>
+        <v>102.2209575525694</v>
       </c>
       <c r="P24">
-        <v>289.6323877577081</v>
+        <v>306.6628726577081</v>
       </c>
       <c r="Q24">
-        <v>911.7323877577081</v>
+        <v>928.7628726577082</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07350344988100377</v>
+        <v>0.07349051209678258</v>
       </c>
       <c r="T24">
         <v>0.5397396210893547</v>
       </c>
       <c r="U24">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.328329287469116</v>
+        <v>2.52559388685793</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06955434143250927</v>
+        <v>0.0684057766578318</v>
       </c>
       <c r="C25">
-        <v>12287.65140710775</v>
+        <v>12995.24875252397</v>
       </c>
       <c r="D25">
-        <v>14053.04840710775</v>
+        <v>14760.64575252397</v>
       </c>
       <c r="E25">
         <v>-9056.303</v>
@@ -3343,45 +3343,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M25">
-        <v>324.6003126619825</v>
+        <v>295.5854124619824</v>
       </c>
       <c r="N25">
-        <v>352.2996873380173</v>
+        <v>381.3145875380173</v>
       </c>
       <c r="O25">
-        <v>88.07492183450432</v>
+        <v>95.32864688450434</v>
       </c>
       <c r="P25">
-        <v>264.224765503513</v>
+        <v>285.985940653513</v>
       </c>
       <c r="Q25">
-        <v>886.3247655035129</v>
+        <v>908.085940653513</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07378899358210667</v>
+        <v>0.07377592244616191</v>
       </c>
       <c r="T25">
         <v>0.5453028000327618</v>
       </c>
       <c r="U25">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.085333789264951</v>
+        <v>2.290031819777511</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07126695020851748</v>
+        <v>0.06889891213085507</v>
       </c>
       <c r="C26">
-        <v>11151.4689749487</v>
+        <v>12488.98677252974</v>
       </c>
       <c r="D26">
-        <v>13108.0049749487</v>
+        <v>14445.52277252974</v>
       </c>
       <c r="E26">
         <v>-8865.164000000001</v>
@@ -3425,45 +3425,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M26">
-        <v>381.3755945342425</v>
+        <v>321.2814929342425</v>
       </c>
       <c r="N26">
-        <v>295.5244054657572</v>
+        <v>355.6185070657572</v>
       </c>
       <c r="O26">
-        <v>73.88110136643931</v>
+        <v>88.90462676643931</v>
       </c>
       <c r="P26">
-        <v>221.6433040993179</v>
+        <v>266.7138802993179</v>
       </c>
       <c r="Q26">
-        <v>843.7433040993179</v>
+        <v>888.8138802993179</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07408205159113333</v>
+        <v>0.07406884359420912</v>
       </c>
       <c r="T26">
         <v>0.5510123784220481</v>
       </c>
       <c r="U26">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.77489071063047</v>
+        <v>2.106875169864025</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07225655898452568</v>
+        <v>0.06890904760387834</v>
       </c>
       <c r="C27">
-        <v>10470.02446066185</v>
+        <v>12291.51206329249</v>
       </c>
       <c r="D27">
-        <v>12617.69946066184</v>
+        <v>14439.18706329249</v>
       </c>
       <c r="E27">
         <v>-8674.025</v>
@@ -3507,45 +3507,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M27">
-        <v>419.7250768065026</v>
+        <v>334.6682218065026</v>
       </c>
       <c r="N27">
-        <v>257.1749231934971</v>
+        <v>342.2317781934971</v>
       </c>
       <c r="O27">
-        <v>64.29373079837428</v>
+        <v>85.55794454837428</v>
       </c>
       <c r="P27">
-        <v>192.8811923951229</v>
+        <v>256.6738336451228</v>
       </c>
       <c r="Q27">
-        <v>814.9811923951229</v>
+        <v>878.7738336451229</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07438292448040071</v>
+        <v>0.07436957597287092</v>
       </c>
       <c r="T27">
         <v>0.5568742122350485</v>
       </c>
       <c r="U27">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.612722320882575</v>
+        <v>2.022600163069464</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07240016776053389</v>
+        <v>0.07120068307690161</v>
       </c>
       <c r="C28">
-        <v>10210.76512428286</v>
+        <v>10797.67765247694</v>
       </c>
       <c r="D28">
-        <v>12549.57912428286</v>
+        <v>13136.49165247695</v>
       </c>
       <c r="E28">
         <v>-8482.885999999999</v>
@@ -3589,37 +3589,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M28">
-        <v>436.5140798787627</v>
+        <v>406.1994344787628</v>
       </c>
       <c r="N28">
-        <v>240.385920121237</v>
+        <v>270.700565521237</v>
       </c>
       <c r="O28">
-        <v>60.09648003030925</v>
+        <v>67.67514138030924</v>
       </c>
       <c r="P28">
-        <v>180.2894400909278</v>
+        <v>203.0254241409277</v>
       </c>
       <c r="Q28">
-        <v>802.3894400909278</v>
+        <v>825.1254241409277</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07469192906937802</v>
+        <v>0.07467843625365872</v>
       </c>
       <c r="T28">
         <v>0.562894473988941</v>
       </c>
       <c r="U28">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.550694539310168</v>
+        <v>1.666422802554123</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07584452653654208</v>
+        <v>0.07129856854992486</v>
       </c>
       <c r="C29">
-        <v>8580.91971167357</v>
+        <v>10556.10948047261</v>
       </c>
       <c r="D29">
-        <v>11110.87271167357</v>
+        <v>13086.0624804726</v>
       </c>
       <c r="E29">
         <v>-8291.746999999999</v>
@@ -3671,45 +3671,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M29">
-        <v>537.4233568510228</v>
+        <v>421.8224896510229</v>
       </c>
       <c r="N29">
-        <v>139.4766431489769</v>
+        <v>255.0775103489769</v>
       </c>
       <c r="O29">
-        <v>34.86916078724423</v>
+        <v>63.76937758724422</v>
       </c>
       <c r="P29">
-        <v>104.6074823617327</v>
+        <v>191.3081327617327</v>
       </c>
       <c r="Q29">
-        <v>726.7074823617327</v>
+        <v>813.4081327617328</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07500939953750538</v>
+        <v>0.07499575845994755</v>
       </c>
       <c r="T29">
         <v>0.5690796744210223</v>
       </c>
       <c r="U29">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.259528435768453</v>
+        <v>1.604703439496563</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08382360624725035</v>
+        <v>0.07139645402294813</v>
       </c>
       <c r="C30">
-        <v>6058.214935258354</v>
+        <v>10314.92700903064</v>
       </c>
       <c r="D30">
-        <v>8779.306935258355</v>
+        <v>13036.01900903064</v>
       </c>
       <c r="E30">
         <v>-8100.607999999999</v>
@@ -3753,45 +3753,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M30">
-        <v>732.3347940232831</v>
+        <v>437.445544823283</v>
       </c>
       <c r="N30">
-        <v>-55.4347940232833</v>
+        <v>239.4544551767167</v>
       </c>
       <c r="O30">
-        <v>-13.85869850582083</v>
+        <v>59.86361379417919</v>
       </c>
       <c r="P30">
-        <v>-41.57609551746248</v>
+        <v>179.5908413825376</v>
       </c>
       <c r="Q30">
-        <v>580.5239044825375</v>
+        <v>801.6908413825377</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07550396958249375</v>
+        <v>0.07532189517196662</v>
       </c>
       <c r="T30">
-        <v>0.578715263123179</v>
+        <v>0.5754366859762169</v>
       </c>
       <c r="U30">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V30">
-        <v>0.2310760070135624</v>
+        <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.1052169576709102</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.9243040280542496</v>
+        <v>1.547392602371686</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08473397241387569</v>
+        <v>0.07458283949597139</v>
       </c>
       <c r="C31">
-        <v>5661.795469260235</v>
+        <v>8680.64402727567</v>
       </c>
       <c r="D31">
-        <v>8574.026469260234</v>
+        <v>11592.87502727567</v>
       </c>
       <c r="E31">
         <v>-7909.469</v>
@@ -3835,45 +3835,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M31">
-        <v>758.4896080955431</v>
+        <v>531.779640195543</v>
       </c>
       <c r="N31">
-        <v>-81.58960809554333</v>
+        <v>145.1203598044567</v>
       </c>
       <c r="O31">
-        <v>-20.39740202388583</v>
+        <v>36.28008995111418</v>
       </c>
       <c r="P31">
-        <v>-61.19220607165749</v>
+        <v>108.8402698533425</v>
       </c>
       <c r="Q31">
-        <v>560.9077939283425</v>
+        <v>730.9402698533426</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07592233535126126</v>
+        <v>0.07565721883362003</v>
       </c>
       <c r="T31">
-        <v>0.586866182322097</v>
+        <v>0.5819727682794451</v>
       </c>
       <c r="U31">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V31">
-        <v>0.223107868840681</v>
+        <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.1063072907395869</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.8924314753627239</v>
+        <v>1.272895667369089</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08564433858050104</v>
+        <v>0.08179829628306119</v>
       </c>
       <c r="C32">
-        <v>5274.756527450571</v>
+        <v>6165.842592262035</v>
       </c>
       <c r="D32">
-        <v>8378.126527450571</v>
+        <v>9269.212592262036</v>
       </c>
       <c r="E32">
         <v>-7718.33</v>
@@ -3917,37 +3917,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M32">
-        <v>784.6444221678032</v>
+        <v>714.1141311678032</v>
       </c>
       <c r="N32">
-        <v>-107.7444221678035</v>
+        <v>-37.21413116780343</v>
       </c>
       <c r="O32">
-        <v>-26.93610554195087</v>
+        <v>-9.303532791950857</v>
       </c>
       <c r="P32">
-        <v>-80.8083166258526</v>
+        <v>-27.91059837585257</v>
       </c>
       <c r="Q32">
-        <v>541.2916833741474</v>
+        <v>594.1894016241474</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07635265442770786</v>
+        <v>0.07612973685993665</v>
       </c>
       <c r="T32">
-        <v>0.5952499849266983</v>
+        <v>0.5911830241096959</v>
       </c>
       <c r="U32">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V32">
-        <v>0.2156709398793249</v>
+        <v>0.2369719245343365</v>
       </c>
       <c r="W32">
-        <v>0.1073249349370185</v>
+        <v>0.09502493493701848</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8626837595172997</v>
+        <v>0.9478876981373461</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08655470474712637</v>
+        <v>0.08258566244968653</v>
       </c>
       <c r="C33">
-        <v>4896.469491963087</v>
+        <v>5776.303892477187</v>
       </c>
       <c r="D33">
-        <v>8190.978491963087</v>
+        <v>9070.812892477188</v>
       </c>
       <c r="E33">
         <v>-7527.191</v>
@@ -3999,37 +3999,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M33">
-        <v>810.7992362400634</v>
+        <v>737.9179355400632</v>
       </c>
       <c r="N33">
-        <v>-133.8992362400636</v>
+        <v>-61.01793554006349</v>
       </c>
       <c r="O33">
-        <v>-33.4748090600159</v>
+        <v>-15.25448388501587</v>
       </c>
       <c r="P33">
-        <v>-100.4244271800477</v>
+        <v>-45.76345165504762</v>
       </c>
       <c r="Q33">
-        <v>521.6755728199523</v>
+        <v>576.3365483449525</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07679544652086304</v>
+        <v>0.07656929826370384</v>
       </c>
       <c r="T33">
-        <v>0.6038767963024476</v>
+        <v>0.5997508940243291</v>
       </c>
       <c r="U33">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.2087138127864435</v>
+        <v>0.2293276689041966</v>
       </c>
       <c r="W33">
-        <v>0.1082769246700996</v>
+        <v>0.09597692467009962</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8348552511457739</v>
+        <v>0.9173106756167866</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08746507091375172</v>
+        <v>0.08337302861631186</v>
       </c>
       <c r="C34">
-        <v>4526.360685189566</v>
+        <v>5395.080370724667</v>
       </c>
       <c r="D34">
-        <v>8012.008685189566</v>
+        <v>8880.728370724666</v>
       </c>
       <c r="E34">
         <v>-7336.052</v>
@@ -4081,37 +4081,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M34">
-        <v>836.9540503123235</v>
+        <v>761.7217399123234</v>
       </c>
       <c r="N34">
-        <v>-160.0540503123237</v>
+        <v>-84.82173991232366</v>
       </c>
       <c r="O34">
-        <v>-40.01351257808093</v>
+        <v>-21.20543497808092</v>
       </c>
       <c r="P34">
-        <v>-120.0405377342428</v>
+        <v>-63.61630493424275</v>
       </c>
       <c r="Q34">
-        <v>502.0594622657572</v>
+        <v>558.4836950657573</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07725126191087574</v>
+        <v>0.07702178794405243</v>
       </c>
       <c r="T34">
-        <v>0.6127573374245425</v>
+        <v>0.6085707601129222</v>
       </c>
       <c r="U34">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.2021915061368671</v>
+        <v>0.2221611792509405</v>
       </c>
       <c r="W34">
-        <v>0.1091694150448632</v>
+        <v>0.0968694150448632</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8087660245474684</v>
+        <v>0.8886447170037619</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.116958910854356</v>
+        <v>0.08416039478293721</v>
       </c>
       <c r="C35">
-        <v>1014.416196086904</v>
+        <v>5021.660007520116</v>
       </c>
       <c r="D35">
-        <v>4691.203196086904</v>
+        <v>8698.447007520117</v>
       </c>
       <c r="E35">
         <v>-7144.913</v>
@@ -4163,45 +4163,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M35">
-        <v>1398.623000684584</v>
+        <v>785.5255442845835</v>
       </c>
       <c r="N35">
-        <v>-721.7230006845838</v>
+        <v>-108.6255442845837</v>
       </c>
       <c r="O35">
-        <v>-180.4307501711459</v>
+        <v>-27.15638607114593</v>
       </c>
       <c r="P35">
-        <v>-541.2922505134378</v>
+        <v>-81.46915821343779</v>
       </c>
       <c r="Q35">
-        <v>80.80774948656222</v>
+        <v>540.6308417865622</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07856616697518568</v>
+        <v>0.07748778477903828</v>
       </c>
       <c r="T35">
-        <v>0.6383753151214562</v>
+        <v>0.6176539057862495</v>
       </c>
       <c r="U35">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1209940061883506</v>
+        <v>0.2154290223039423</v>
       </c>
       <c r="W35">
-        <v>0.1949078150938836</v>
+        <v>0.09770781509388353</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.4839760247534023</v>
+        <v>0.8617160892157691</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1187182770209813</v>
+        <v>0.08494776094956256</v>
       </c>
       <c r="C36">
-        <v>710.0882327549125</v>
+        <v>4655.571975703739</v>
       </c>
       <c r="D36">
-        <v>4578.014232754913</v>
+        <v>8523.49797570374</v>
       </c>
       <c r="E36">
         <v>-6953.773999999999</v>
@@ -4245,45 +4245,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M36">
-        <v>1441.005515856844</v>
+        <v>809.3293486568436</v>
       </c>
       <c r="N36">
-        <v>-764.1055158568439</v>
+        <v>-132.4293486568439</v>
       </c>
       <c r="O36">
-        <v>-191.026378964211</v>
+        <v>-33.10733716421097</v>
       </c>
       <c r="P36">
-        <v>-573.079136892633</v>
+        <v>-99.32201149263292</v>
       </c>
       <c r="Q36">
-        <v>49.02086310736706</v>
+        <v>522.7779885073671</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07906262405056727</v>
+        <v>0.07796790273023585</v>
       </c>
       <c r="T36">
-        <v>0.6480476683808721</v>
+        <v>0.6270122982981624</v>
       </c>
       <c r="U36">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.1174353589475167</v>
+        <v>0.2090928745891204</v>
       </c>
       <c r="W36">
-        <v>0.1956968974929615</v>
+        <v>0.09849689749296149</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.4697414357900669</v>
+        <v>0.8363714983564817</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1204776431876066</v>
+        <v>0.08573512711618791</v>
       </c>
       <c r="C37">
-        <v>411.09361482648</v>
+        <v>4296.382579674116</v>
       </c>
       <c r="D37">
-        <v>4470.158614826481</v>
+        <v>8355.447579674115</v>
       </c>
       <c r="E37">
         <v>-6762.634999999999</v>
@@ -4327,45 +4327,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M37">
-        <v>1483.388031029104</v>
+        <v>833.1331530291038</v>
       </c>
       <c r="N37">
-        <v>-806.488031029104</v>
+        <v>-156.2331530291041</v>
       </c>
       <c r="O37">
-        <v>-201.622007757276</v>
+        <v>-39.05828825727602</v>
       </c>
       <c r="P37">
-        <v>-604.866023271828</v>
+        <v>-117.1748647718281</v>
       </c>
       <c r="Q37">
-        <v>17.23397672817202</v>
+        <v>504.9251352281719</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07957435672826832</v>
+        <v>0.07846279354147025</v>
       </c>
       <c r="T37">
-        <v>0.6580176325098086</v>
+        <v>0.6366586413489034</v>
       </c>
       <c r="U37">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V37">
-        <v>0.1140800629775877</v>
+        <v>0.2031187924580027</v>
       </c>
       <c r="W37">
-        <v>0.196440889469235</v>
+        <v>0.099240889469235</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.4563202519103506</v>
+        <v>0.8124751698320107</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.122237009354232</v>
+        <v>0.1167605436013848</v>
       </c>
       <c r="C38">
-        <v>117.0640662189689</v>
+        <v>452.0691827045739</v>
       </c>
       <c r="D38">
-        <v>4367.268066218969</v>
+        <v>4702.273182704574</v>
       </c>
       <c r="E38">
         <v>-6571.496</v>
@@ -4409,37 +4409,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M38">
-        <v>1525.770546201364</v>
+        <v>1422.555486201364</v>
       </c>
       <c r="N38">
-        <v>-848.8705462013642</v>
+        <v>-745.6554862013639</v>
       </c>
       <c r="O38">
-        <v>-212.217636550341</v>
+        <v>-186.413871550341</v>
       </c>
       <c r="P38">
-        <v>-636.6529096510232</v>
+        <v>-559.2416146510229</v>
       </c>
       <c r="Q38">
-        <v>-14.55290965102313</v>
+        <v>62.85838534897709</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.0801020810521475</v>
+        <v>0.07998260331332377</v>
       </c>
       <c r="T38">
-        <v>0.6682991580177743</v>
+        <v>0.6662825626227695</v>
       </c>
       <c r="U38">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.1109111723393214</v>
+        <v>0.1189584530385383</v>
       </c>
       <c r="W38">
-        <v>0.1971435485579378</v>
+        <v>0.1821435485579377</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4436446893572854</v>
+        <v>0.4758338121541532</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1239963755208573</v>
+        <v>0.1183699097680101</v>
       </c>
       <c r="C39">
-        <v>-172.3355452877586</v>
+        <v>156.6489538775522</v>
       </c>
       <c r="D39">
-        <v>4269.007454712241</v>
+        <v>4597.991953877552</v>
       </c>
       <c r="E39">
         <v>-6380.357</v>
@@ -4491,37 +4491,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M39">
-        <v>1568.153061373624</v>
+        <v>1462.070916373624</v>
       </c>
       <c r="N39">
-        <v>-891.2530613736243</v>
+        <v>-785.1709163736242</v>
       </c>
       <c r="O39">
-        <v>-222.8132653434061</v>
+        <v>-196.2927290934061</v>
       </c>
       <c r="P39">
-        <v>-668.4397960302182</v>
+        <v>-588.8781872802182</v>
       </c>
       <c r="Q39">
-        <v>-46.33979603021817</v>
+        <v>33.22181271978184</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08064655852916572</v>
+        <v>0.08052518431829717</v>
       </c>
       <c r="T39">
-        <v>0.6789070811609136</v>
+        <v>0.6768584763151944</v>
       </c>
       <c r="U39">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1079135730869073</v>
+        <v>0.1157433597131724</v>
       </c>
       <c r="W39">
-        <v>0.1978082260742782</v>
+        <v>0.1828082260742782</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.431654292347629</v>
+        <v>0.4629734388526895</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1257557416874827</v>
+        <v>0.1199792759346355</v>
       </c>
       <c r="C40">
-        <v>-457.4108545805766</v>
+        <v>-134.2463809174506</v>
       </c>
       <c r="D40">
-        <v>4175.071145419424</v>
+        <v>4498.23561908255</v>
       </c>
       <c r="E40">
         <v>-6189.217999999999</v>
@@ -4573,37 +4573,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M40">
-        <v>1610.535576545884</v>
+        <v>1501.586346545884</v>
       </c>
       <c r="N40">
-        <v>-933.6355765458846</v>
+        <v>-824.6863465458845</v>
       </c>
       <c r="O40">
-        <v>-233.4088941364712</v>
+        <v>-206.1715866364711</v>
       </c>
       <c r="P40">
-        <v>-700.2266824094135</v>
+        <v>-618.5147599094133</v>
       </c>
       <c r="Q40">
-        <v>-78.12668240941343</v>
+        <v>3.585240090586694</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08120859979576517</v>
+        <v>0.08108526793633422</v>
       </c>
       <c r="T40">
-        <v>0.6898571953731863</v>
+        <v>0.6877755485138266</v>
       </c>
       <c r="U40">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.1050737422161992</v>
+        <v>0.1126974818259836</v>
       </c>
       <c r="W40">
-        <v>0.1984379205634428</v>
+        <v>0.1834379205634428</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4202949688647967</v>
+        <v>0.4507899273039345</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.127515107854108</v>
+        <v>0.1215886421012608</v>
       </c>
       <c r="C41">
-        <v>-738.4411746730502</v>
+        <v>-420.9050790430319</v>
       </c>
       <c r="D41">
-        <v>4085.179825326951</v>
+        <v>4402.715920956969</v>
       </c>
       <c r="E41">
         <v>-5998.078999999999</v>
@@ -4655,37 +4655,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M41">
-        <v>1652.918091718145</v>
+        <v>1541.101776718144</v>
       </c>
       <c r="N41">
-        <v>-976.0180917181448</v>
+        <v>-864.2017767181445</v>
       </c>
       <c r="O41">
-        <v>-244.0045229295362</v>
+        <v>-216.0504441795361</v>
       </c>
       <c r="P41">
-        <v>-732.0135687886086</v>
+        <v>-648.1513325386084</v>
       </c>
       <c r="Q41">
-        <v>-109.9135687886086</v>
+        <v>-26.05133253860834</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08178906864487606</v>
+        <v>0.08166371495168395</v>
       </c>
       <c r="T41">
-        <v>0.7011663297235665</v>
+        <v>0.6990505575058564</v>
       </c>
       <c r="U41">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1023795436978351</v>
+        <v>0.1098078028048046</v>
       </c>
       <c r="W41">
-        <v>0.1990353230275221</v>
+        <v>0.1840353230275221</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4095181747913403</v>
+        <v>0.4392312112192183</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1292744740207334</v>
+        <v>0.1231980082678862</v>
       </c>
       <c r="C42">
-        <v>-1015.682270596117</v>
+        <v>-703.5914224827593</v>
       </c>
       <c r="D42">
-        <v>3999.077729403885</v>
+        <v>4311.168577517242</v>
       </c>
       <c r="E42">
         <v>-5806.939999999999</v>
@@ -4737,37 +4737,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M42">
-        <v>1695.300606890405</v>
+        <v>1580.617206890405</v>
       </c>
       <c r="N42">
-        <v>-1018.400606890405</v>
+        <v>-903.7172068904048</v>
       </c>
       <c r="O42">
-        <v>-254.6001517226012</v>
+        <v>-225.9293017226012</v>
       </c>
       <c r="P42">
-        <v>-763.8004551678036</v>
+        <v>-677.7879051678036</v>
       </c>
       <c r="Q42">
-        <v>-141.7004551678036</v>
+        <v>-55.68790516780359</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08238888645562401</v>
+        <v>0.08226144353421203</v>
       </c>
       <c r="T42">
-        <v>0.7128524352189594</v>
+        <v>0.7107014001309542</v>
       </c>
       <c r="U42">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.09982005510538919</v>
+        <v>0.1070626077346844</v>
       </c>
       <c r="W42">
-        <v>0.1996028553683974</v>
+        <v>0.1846028553683974</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3992802204215568</v>
+        <v>0.4282504309387377</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1310338401873587</v>
+        <v>0.1248073744345115</v>
       </c>
       <c r="C43">
-        <v>-1289.368789742879</v>
+        <v>-982.5481597121588</v>
       </c>
       <c r="D43">
-        <v>3916.530210257122</v>
+        <v>4223.350840287842</v>
       </c>
       <c r="E43">
         <v>-5615.800999999999</v>
@@ -4819,37 +4819,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M43">
-        <v>1737.683122062665</v>
+        <v>1620.132637062665</v>
       </c>
       <c r="N43">
-        <v>-1060.783122062665</v>
+        <v>-943.2326370626648</v>
       </c>
       <c r="O43">
-        <v>-265.1957805156662</v>
+        <v>-235.8081592656662</v>
       </c>
       <c r="P43">
-        <v>-795.5873415469987</v>
+        <v>-707.4244777969986</v>
       </c>
       <c r="Q43">
-        <v>-173.4873415469987</v>
+        <v>-85.32447779699862</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08300903707351594</v>
+        <v>0.0828794341025885</v>
       </c>
       <c r="T43">
-        <v>0.7249346798836874</v>
+        <v>0.7227471865738516</v>
       </c>
       <c r="U43">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.09738541961501385</v>
+        <v>0.1044513246192043</v>
       </c>
       <c r="W43">
-        <v>0.2001427032048397</v>
+        <v>0.1851427032048397</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3895416784600555</v>
+        <v>0.4178052984768174</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.132793206353984</v>
+        <v>0.1264167406011368</v>
       </c>
       <c r="C44">
-        <v>-1559.716397303036</v>
+        <v>-1257.998655084771</v>
       </c>
       <c r="D44">
-        <v>3837.321602696965</v>
+        <v>4139.03934491523</v>
       </c>
       <c r="E44">
         <v>-5424.661999999999</v>
@@ -4901,37 +4901,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M44">
-        <v>1780.065637234925</v>
+        <v>1659.648067234925</v>
       </c>
       <c r="N44">
-        <v>-1103.165637234925</v>
+        <v>-982.7480672349249</v>
       </c>
       <c r="O44">
-        <v>-275.7914093087312</v>
+        <v>-245.6870168087312</v>
       </c>
       <c r="P44">
-        <v>-827.3742279261936</v>
+        <v>-737.0610504261937</v>
       </c>
       <c r="Q44">
-        <v>-205.2742279261936</v>
+        <v>-114.9610504261937</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.0836505721954731</v>
+        <v>0.08351873469056416</v>
       </c>
       <c r="T44">
-        <v>0.7374335536747855</v>
+        <v>0.7352083449630559</v>
       </c>
       <c r="U44">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.09506671914798973</v>
+        <v>0.1019643883187471</v>
       </c>
       <c r="W44">
-        <v>0.2006568440014515</v>
+        <v>0.1856568440014515</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3802668765919589</v>
+        <v>0.4078575532749884</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1345525725206094</v>
+        <v>0.1280261067677622</v>
       </c>
       <c r="C45">
-        <v>-1826.923657709547</v>
+        <v>-1530.148785805717</v>
       </c>
       <c r="D45">
-        <v>3761.253342290453</v>
+        <v>4058.028214194283</v>
       </c>
       <c r="E45">
         <v>-5233.522999999999</v>
@@ -4983,37 +4983,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M45">
-        <v>1822.448152407185</v>
+        <v>1699.163497407185</v>
       </c>
       <c r="N45">
-        <v>-1145.548152407185</v>
+        <v>-1022.263497407185</v>
       </c>
       <c r="O45">
-        <v>-286.3870381017963</v>
+        <v>-255.5658743517962</v>
       </c>
       <c r="P45">
-        <v>-859.1611143053889</v>
+        <v>-766.6976230553887</v>
       </c>
       <c r="Q45">
-        <v>-237.0611143053889</v>
+        <v>-144.5976230553887</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08431461732170947</v>
+        <v>0.08418046687811792</v>
       </c>
       <c r="T45">
-        <v>0.7503709844410097</v>
+        <v>0.7481067369799517</v>
       </c>
       <c r="U45">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.09285586521431553</v>
+        <v>0.09959312347412508</v>
       </c>
       <c r="W45">
-        <v>0.2011470712726395</v>
+        <v>0.1861470712726395</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3714234608572621</v>
+        <v>0.3983724938965003</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1363119386872347</v>
+        <v>0.1296354729343875</v>
       </c>
       <c r="C46">
-        <v>-2091.173696656562</v>
+        <v>-1799.188620411216</v>
       </c>
       <c r="D46">
-        <v>3688.142303343437</v>
+        <v>3980.127379588784</v>
       </c>
       <c r="E46">
         <v>-5042.384</v>
@@ -5065,37 +5065,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M46">
-        <v>1864.830667579445</v>
+        <v>1738.678927579445</v>
       </c>
       <c r="N46">
-        <v>-1187.930667579445</v>
+        <v>-1061.778927579445</v>
       </c>
       <c r="O46">
-        <v>-296.9826668948613</v>
+        <v>-265.4447318948612</v>
       </c>
       <c r="P46">
-        <v>-890.9480006845838</v>
+        <v>-796.3341956845836</v>
       </c>
       <c r="Q46">
-        <v>-268.8480006845838</v>
+        <v>-174.2341956845836</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08500237834531144</v>
+        <v>0.08486583235808431</v>
       </c>
       <c r="T46">
-        <v>0.7637704663060277</v>
+        <v>0.7614657858545937</v>
       </c>
       <c r="U46">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.09074550464126292</v>
+        <v>0.09732964339516768</v>
       </c>
       <c r="W46">
-        <v>0.2016150154860462</v>
+        <v>0.1866150154860462</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3629820185650516</v>
+        <v>0.3893185735806708</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1380713048538601</v>
+        <v>0.1312448391010129</v>
       </c>
       <c r="C47">
-        <v>-2352.635672976005</v>
+        <v>-2065.29390756165</v>
       </c>
       <c r="D47">
-        <v>3617.819327023995</v>
+        <v>3905.16109243835</v>
       </c>
       <c r="E47">
         <v>-4851.244999999999</v>
@@ -5147,37 +5147,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M47">
-        <v>1907.213182751705</v>
+        <v>1778.194357751705</v>
       </c>
       <c r="N47">
-        <v>-1230.313182751705</v>
+        <v>-1101.294357751705</v>
       </c>
       <c r="O47">
-        <v>-307.5782956879264</v>
+        <v>-275.3235894379263</v>
       </c>
       <c r="P47">
-        <v>-922.7348870637791</v>
+        <v>-825.970768313779</v>
       </c>
       <c r="Q47">
-        <v>-300.634887063779</v>
+        <v>-203.870768313779</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08571514886068073</v>
+        <v>0.08557612021914038</v>
       </c>
       <c r="T47">
-        <v>0.7776572020570465</v>
+        <v>0.7753106183246771</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.08872893787145707</v>
+        <v>0.09516676243083062</v>
       </c>
       <c r="W47">
-        <v>0.202062162178857</v>
+        <v>0.187062162178857</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3549157514858282</v>
+        <v>0.3806670497233224</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1398306710204854</v>
+        <v>0.1328542052676382</v>
       </c>
       <c r="C48">
-        <v>-2611.466085276388</v>
+        <v>-2328.627399695259</v>
       </c>
       <c r="D48">
-        <v>3550.127914723612</v>
+        <v>3832.966600304742</v>
       </c>
       <c r="E48">
         <v>-4660.106</v>
@@ -5229,37 +5229,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M48">
-        <v>1949.595697923965</v>
+        <v>1817.709787923965</v>
       </c>
       <c r="N48">
-        <v>-1272.695697923965</v>
+        <v>-1140.809787923965</v>
       </c>
       <c r="O48">
-        <v>-318.1739244809913</v>
+        <v>-285.2024469809912</v>
       </c>
       <c r="P48">
-        <v>-954.521773442974</v>
+        <v>-855.6073409429737</v>
       </c>
       <c r="Q48">
-        <v>-332.421773442974</v>
+        <v>-233.5073409429737</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08645431828402667</v>
+        <v>0.08631271503801335</v>
       </c>
       <c r="T48">
-        <v>0.7920582613543993</v>
+        <v>0.7896682223677267</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.08680004791772976</v>
+        <v>0.09309791976929084</v>
       </c>
       <c r="W48">
-        <v>0.2024898677111109</v>
+        <v>0.1874898677111109</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.347200191670919</v>
+        <v>0.3723916790771634</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1415900371871108</v>
+        <v>0.1344635714342635</v>
       </c>
       <c r="C49">
-        <v>-2867.809934588186</v>
+        <v>-2589.340032524937</v>
       </c>
       <c r="D49">
-        <v>3484.923065411815</v>
+        <v>3763.392967475065</v>
       </c>
       <c r="E49">
         <v>-4468.966999999999</v>
@@ -5311,37 +5311,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M49">
-        <v>1991.978213096225</v>
+        <v>1857.225218096225</v>
       </c>
       <c r="N49">
-        <v>-1315.078213096226</v>
+        <v>-1180.325218096225</v>
       </c>
       <c r="O49">
-        <v>-328.7695532740564</v>
+        <v>-295.0813045240563</v>
       </c>
       <c r="P49">
-        <v>-986.3086598221693</v>
+        <v>-885.243913572169</v>
       </c>
       <c r="Q49">
-        <v>-364.2086598221692</v>
+        <v>-263.143913572169</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08722138089315926</v>
+        <v>0.08707710588778719</v>
       </c>
       <c r="T49">
-        <v>0.807002756851652</v>
+        <v>0.8045676227897594</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.08495323838756527</v>
+        <v>0.09111711296568889</v>
       </c>
       <c r="W49">
-        <v>0.2028993730079497</v>
+        <v>0.1878993730079496</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3398129535502611</v>
+        <v>0.3644684518627556</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1433494033537361</v>
+        <v>0.1360729376008889</v>
       </c>
       <c r="C50">
-        <v>-3121.801761194868</v>
+        <v>-2847.571978368215</v>
       </c>
       <c r="D50">
-        <v>3422.070238805132</v>
+        <v>3696.300021631785</v>
       </c>
       <c r="E50">
         <v>-4277.828</v>
@@ -5393,37 +5393,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M50">
-        <v>2034.360728268485</v>
+        <v>1896.740648268485</v>
       </c>
       <c r="N50">
-        <v>-1357.460728268486</v>
+        <v>-1219.840648268485</v>
       </c>
       <c r="O50">
-        <v>-339.3651820671214</v>
+        <v>-304.9601620671214</v>
       </c>
       <c r="P50">
-        <v>-1018.095546201364</v>
+        <v>-914.8804862013641</v>
       </c>
       <c r="Q50">
-        <v>-395.9955462013642</v>
+        <v>-292.7804862013641</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08801794591033538</v>
+        <v>0.08787089638562925</v>
       </c>
       <c r="T50">
-        <v>0.8225220406372606</v>
+        <v>0.8200400770741777</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.08318337925449101</v>
+        <v>0.08921883977890371</v>
       </c>
       <c r="W50">
-        <v>0.2032918155840868</v>
+        <v>0.1882918155840868</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3327335170179639</v>
+        <v>0.3568753591156149</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1451087695203614</v>
+        <v>0.1376823037675142</v>
       </c>
       <c r="C51">
-        <v>-3373.566571252204</v>
+        <v>-3103.453588779492</v>
       </c>
       <c r="D51">
-        <v>3361.444428747795</v>
+        <v>3631.557411220508</v>
       </c>
       <c r="E51">
         <v>-4086.689</v>
@@ -5475,37 +5475,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M51">
-        <v>2076.743243440745</v>
+        <v>1936.256078440745</v>
       </c>
       <c r="N51">
-        <v>-1399.843243440745</v>
+        <v>-1259.356078440745</v>
       </c>
       <c r="O51">
-        <v>-349.9608108601864</v>
+        <v>-314.8390196101864</v>
       </c>
       <c r="P51">
-        <v>-1049.882432580559</v>
+        <v>-944.5170588305591</v>
       </c>
       <c r="Q51">
-        <v>-427.782432580559</v>
+        <v>-322.4170588305591</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08884574877132234</v>
+        <v>0.08869581592260239</v>
       </c>
       <c r="T51">
-        <v>0.8386499237870109</v>
+        <v>0.8361192942717107</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.08148575926970548</v>
+        <v>0.08739804713035466</v>
       </c>
       <c r="W51">
-        <v>0.2036682400958919</v>
+        <v>0.1886682400958919</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3259430370788219</v>
+        <v>0.3495921885214186</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1468681356869868</v>
+        <v>0.1392916699341396</v>
       </c>
       <c r="C52">
-        <v>-3623.220666625549</v>
+        <v>-3357.106239823406</v>
       </c>
       <c r="D52">
-        <v>3302.929333374452</v>
+        <v>3569.043760176594</v>
       </c>
       <c r="E52">
         <v>-3895.549999999999</v>
@@ -5557,37 +5557,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M52">
-        <v>2119.125758613005</v>
+        <v>1975.771508613005</v>
       </c>
       <c r="N52">
-        <v>-1442.225758613006</v>
+        <v>-1298.871508613006</v>
       </c>
       <c r="O52">
-        <v>-360.5564396532515</v>
+        <v>-324.7178771532514</v>
       </c>
       <c r="P52">
-        <v>-1081.669318959754</v>
+        <v>-974.1536314597541</v>
       </c>
       <c r="Q52">
-        <v>-459.5693189597545</v>
+        <v>-352.0536314597541</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08970666374674879</v>
+        <v>0.08955373224105442</v>
       </c>
       <c r="T52">
-        <v>0.8554229222627512</v>
+        <v>0.8528416801571449</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.07985604408431136</v>
+        <v>0.08565008618774757</v>
       </c>
       <c r="W52">
-        <v>0.2040296076272247</v>
+        <v>0.1890296076272247</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3194241763372454</v>
+        <v>0.3426003447509903</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1486275018536121</v>
+        <v>0.1409010361007649</v>
       </c>
       <c r="C53">
-        <v>-3870.872389536646</v>
+        <v>-3608.64309152239</v>
       </c>
       <c r="D53">
-        <v>3246.416610463356</v>
+        <v>3508.645908477611</v>
       </c>
       <c r="E53">
         <v>-3704.410999999998</v>
@@ -5639,37 +5639,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M53">
-        <v>2161.508273785266</v>
+        <v>2015.286938785266</v>
       </c>
       <c r="N53">
-        <v>-1484.608273785266</v>
+        <v>-1338.386938785266</v>
       </c>
       <c r="O53">
-        <v>-371.1520684463165</v>
+        <v>-334.5967346963165</v>
       </c>
       <c r="P53">
-        <v>-1113.45620533895</v>
+        <v>-1003.79020408895</v>
       </c>
       <c r="Q53">
-        <v>-491.3562053389495</v>
+        <v>-381.6902040889495</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09060271810892734</v>
+        <v>0.09044666555209635</v>
       </c>
       <c r="T53">
-        <v>0.8728805329211746</v>
+        <v>0.8702466124052499</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.07829023929834447</v>
+        <v>0.08397067273308584</v>
       </c>
       <c r="W53">
-        <v>0.204376803882819</v>
+        <v>0.189376803882819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3131609571933778</v>
+        <v>0.3358826909323434</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1503868680202374</v>
+        <v>0.1425104022673903</v>
       </c>
       <c r="C54">
-        <v>-4116.622792051485</v>
+        <v>-3858.16977147599</v>
       </c>
       <c r="D54">
-        <v>3191.805207948516</v>
+        <v>3450.258228524011</v>
       </c>
       <c r="E54">
         <v>-3513.271999999999</v>
@@ -5721,37 +5721,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M54">
-        <v>2203.890788957526</v>
+        <v>2054.802368957526</v>
       </c>
       <c r="N54">
-        <v>-1526.990788957526</v>
+        <v>-1377.902368957526</v>
       </c>
       <c r="O54">
-        <v>-381.7476972393815</v>
+        <v>-344.4755922393815</v>
       </c>
       <c r="P54">
-        <v>-1145.243091718145</v>
+        <v>-1033.426776718145</v>
       </c>
       <c r="Q54">
-        <v>-523.1430917181445</v>
+        <v>-411.3267767181445</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09153610806953</v>
+        <v>0.09137680441776505</v>
       </c>
       <c r="T54">
-        <v>0.8910655440236992</v>
+        <v>0.8883767501636928</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.07678465777337631</v>
+        <v>0.08235585210360342</v>
       </c>
       <c r="W54">
-        <v>0.2047106464362751</v>
+        <v>0.1897106464362751</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3071386310935053</v>
+        <v>0.3294234084144136</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1521462341868628</v>
+        <v>0.1441197684340156</v>
       </c>
       <c r="C55">
-        <v>-4360.56623911311</v>
+        <v>-4105.784991340502</v>
       </c>
       <c r="D55">
-        <v>3139.000760886891</v>
+        <v>3393.7820086595</v>
       </c>
       <c r="E55">
         <v>-3322.132999999998</v>
@@ -5803,37 +5803,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M55">
-        <v>2246.273304129786</v>
+        <v>2094.317799129786</v>
       </c>
       <c r="N55">
-        <v>-1569.373304129786</v>
+        <v>-1417.417799129786</v>
       </c>
       <c r="O55">
-        <v>-392.3433260324466</v>
+        <v>-354.3544497824465</v>
       </c>
       <c r="P55">
-        <v>-1177.02997809734</v>
+        <v>-1063.06334934734</v>
       </c>
       <c r="Q55">
-        <v>-554.9299780973398</v>
+        <v>-440.9633493473397</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09250921675186043</v>
+        <v>0.09234652366069621</v>
       </c>
       <c r="T55">
-        <v>0.9100243853859055</v>
+        <v>0.9072783831458988</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.07533589064557675</v>
+        <v>0.08080196810164865</v>
       </c>
       <c r="W55">
-        <v>0.2050318911575253</v>
+        <v>0.1900318911575253</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.301343562582307</v>
+        <v>0.3232078724065945</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1539056003534881</v>
+        <v>0.1457291346006409</v>
       </c>
       <c r="C56">
-        <v>-4602.790952689995</v>
+        <v>-4351.581103737863</v>
       </c>
       <c r="D56">
-        <v>3087.915047310006</v>
+        <v>3339.124896262138</v>
       </c>
       <c r="E56">
         <v>-3130.993999999999</v>
@@ -5885,37 +5885,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M56">
-        <v>2288.655819302046</v>
+        <v>2133.833229302046</v>
       </c>
       <c r="N56">
-        <v>-1611.755819302046</v>
+        <v>-1456.933229302046</v>
       </c>
       <c r="O56">
-        <v>-402.9389548255116</v>
+        <v>-364.2333073255115</v>
       </c>
       <c r="P56">
-        <v>-1208.816864476535</v>
+        <v>-1092.699921976535</v>
       </c>
       <c r="Q56">
-        <v>-586.7168644765346</v>
+        <v>-470.5999219765346</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09352463450733565</v>
+        <v>0.09335840460984177</v>
       </c>
       <c r="T56">
-        <v>0.9298075241986425</v>
+        <v>0.9270018262577662</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.07394078155954756</v>
+        <v>0.07930563535902552</v>
       </c>
       <c r="W56">
-        <v>0.2053412379261365</v>
+        <v>0.1903412379261365</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2957631262381902</v>
+        <v>0.3172225414361021</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1556649665201135</v>
+        <v>0.1473385007672663</v>
       </c>
       <c r="C57">
-        <v>-4843.379503640854</v>
+        <v>-4595.64460620317</v>
       </c>
       <c r="D57">
-        <v>3038.465496359148</v>
+        <v>3286.200393796832</v>
       </c>
       <c r="E57">
         <v>-2939.854999999998</v>
@@ -5967,37 +5967,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M57">
-        <v>2331.038334474306</v>
+        <v>2173.348659474306</v>
       </c>
       <c r="N57">
-        <v>-1654.138334474307</v>
+        <v>-1496.448659474307</v>
       </c>
       <c r="O57">
-        <v>-413.5345836185767</v>
+        <v>-374.1121648685767</v>
       </c>
       <c r="P57">
-        <v>-1240.60375085573</v>
+        <v>-1122.33649460573</v>
       </c>
       <c r="Q57">
-        <v>-618.5037508557301</v>
+        <v>-500.2364946057299</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09458518194083201</v>
+        <v>0.09441525804561604</v>
       </c>
       <c r="T57">
-        <v>0.9504699136252792</v>
+        <v>0.9476018668412723</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.07259640371301032</v>
+        <v>0.07786371471613414</v>
       </c>
       <c r="W57">
-        <v>0.2056393357213438</v>
+        <v>0.1906393357213438</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2903856148520413</v>
+        <v>0.3114548588645365</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1574243326867388</v>
+        <v>0.1489478669338916</v>
       </c>
       <c r="C58">
-        <v>-5082.409257064257</v>
+        <v>-4838.056597955068</v>
       </c>
       <c r="D58">
-        <v>2990.574742935744</v>
+        <v>3234.927402044933</v>
       </c>
       <c r="E58">
         <v>-2748.715999999999</v>
@@ -6049,37 +6049,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M58">
-        <v>2373.420849646566</v>
+        <v>2212.864089646566</v>
       </c>
       <c r="N58">
-        <v>-1696.520849646567</v>
+        <v>-1535.964089646567</v>
       </c>
       <c r="O58">
-        <v>-424.1302124116417</v>
+        <v>-383.9910224116417</v>
       </c>
       <c r="P58">
-        <v>-1272.390637234925</v>
+        <v>-1151.973067234925</v>
       </c>
       <c r="Q58">
-        <v>-650.2906372349249</v>
+        <v>-529.8730672349251</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09569393607585092</v>
+        <v>0.09552015027392549</v>
       </c>
       <c r="T58">
-        <v>0.9720715025713083</v>
+        <v>0.9691382729058464</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.07130003936099229</v>
+        <v>0.07647329123906031</v>
       </c>
       <c r="W58">
-        <v>0.2059267871667222</v>
+        <v>0.1909267871667222</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2852001574439691</v>
+        <v>0.3058931649562412</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1591836988533642</v>
+        <v>0.150557233100517</v>
       </c>
       <c r="C59">
-        <v>-5319.952776185566</v>
+        <v>-5078.893194562503</v>
       </c>
       <c r="D59">
-        <v>2944.170223814437</v>
+        <v>3185.229805437499</v>
       </c>
       <c r="E59">
         <v>-2557.576999999997</v>
@@ -6131,37 +6131,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M59">
-        <v>2415.803364818827</v>
+        <v>2252.379519818826</v>
       </c>
       <c r="N59">
-        <v>-1738.903364818827</v>
+        <v>-1575.479519818827</v>
       </c>
       <c r="O59">
-        <v>-434.7258412047067</v>
+        <v>-393.8698799547067</v>
       </c>
       <c r="P59">
-        <v>-1304.17752361412</v>
+        <v>-1181.60963986412</v>
       </c>
       <c r="Q59">
-        <v>-682.0775236141202</v>
+        <v>-559.50963986412</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09685426017063815</v>
+        <v>0.0966764328384354</v>
       </c>
       <c r="T59">
-        <v>0.9946778165845946</v>
+        <v>0.9916763722757501</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.07004916147746611</v>
+        <v>0.07513165455065575</v>
       </c>
       <c r="W59">
-        <v>0.2062041525964733</v>
+        <v>0.1912041525964732</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2801966459098644</v>
+        <v>0.3005266182026229</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1609430650199895</v>
+        <v>0.1521665992671423</v>
       </c>
       <c r="C60">
-        <v>-5556.07818921587</v>
+        <v>-5318.225904967054</v>
       </c>
       <c r="D60">
-        <v>2899.18381078413</v>
+        <v>3137.036095032946</v>
       </c>
       <c r="E60">
         <v>-2366.438</v>
@@ -6213,37 +6213,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M60">
-        <v>2458.185879991086</v>
+        <v>2291.894949991086</v>
       </c>
       <c r="N60">
-        <v>-1781.285879991086</v>
+        <v>-1614.994949991086</v>
       </c>
       <c r="O60">
-        <v>-445.3214699977716</v>
+        <v>-403.7487374977716</v>
       </c>
       <c r="P60">
-        <v>-1335.964409993315</v>
+        <v>-1211.246212493315</v>
       </c>
       <c r="Q60">
-        <v>-713.8644099933148</v>
+        <v>-589.1462124933147</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09806983779374856</v>
+        <v>0.09788777647744576</v>
       </c>
       <c r="T60">
-        <v>1.01836062174137</v>
+        <v>1.015287714472792</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.06884141731406153</v>
+        <v>0.07383628119633412</v>
       </c>
       <c r="W60">
-        <v>0.2064719537010605</v>
+        <v>0.1914719537010605</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2753656692562461</v>
+        <v>0.2953451247853364</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1627024311866148</v>
+        <v>0.1537759654337676</v>
       </c>
       <c r="C61">
-        <v>-5790.849523083925</v>
+        <v>-5556.121974788535</v>
       </c>
       <c r="D61">
-        <v>2855.551476916075</v>
+        <v>3090.279025211466</v>
       </c>
       <c r="E61">
         <v>-2175.298999999999</v>
@@ -6295,37 +6295,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M61">
-        <v>2500.568395163346</v>
+        <v>2331.410380163346</v>
       </c>
       <c r="N61">
-        <v>-1823.668395163347</v>
+        <v>-1654.510380163347</v>
       </c>
       <c r="O61">
-        <v>-455.9170987908367</v>
+        <v>-413.6275950408367</v>
       </c>
       <c r="P61">
-        <v>-1367.75129637251</v>
+        <v>-1240.88278512251</v>
       </c>
       <c r="Q61">
-        <v>-745.65129637251</v>
+        <v>-618.7827851225101</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09934471188627901</v>
+        <v>0.09915821005006636</v>
       </c>
       <c r="T61">
-        <v>1.043198685686282</v>
+        <v>1.040050829459933</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.06767461363077235</v>
+        <v>0.0725848188031759</v>
       </c>
       <c r="W61">
-        <v>0.2067306768021024</v>
+        <v>0.1917306768021024</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2706984545230894</v>
+        <v>0.2903392752127035</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1644617973532402</v>
+        <v>0.155385331600393</v>
       </c>
       <c r="C62">
-        <v>-6024.327007479097</v>
+        <v>-5792.644699379915</v>
       </c>
       <c r="D62">
-        <v>2813.212992520903</v>
+        <v>3044.895300620086</v>
       </c>
       <c r="E62">
         <v>-1984.16</v>
@@ -6377,37 +6377,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M62">
-        <v>2542.950910335606</v>
+        <v>2370.925810335606</v>
       </c>
       <c r="N62">
-        <v>-1866.050910335607</v>
+        <v>-1694.025810335607</v>
       </c>
       <c r="O62">
-        <v>-466.5127275839017</v>
+        <v>-423.5064525839017</v>
       </c>
       <c r="P62">
-        <v>-1399.538182751705</v>
+        <v>-1270.519357751705</v>
       </c>
       <c r="Q62">
-        <v>-777.4381827517049</v>
+        <v>-648.4193577517052</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.100683329683436</v>
+        <v>0.100492165301318</v>
       </c>
       <c r="T62">
-        <v>1.069278652828439</v>
+        <v>1.066052100196431</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06654670340359281</v>
+        <v>0.07137507182312297</v>
       </c>
       <c r="W62">
-        <v>0.2069807757997763</v>
+        <v>0.1919807757997763</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2661868136143712</v>
+        <v>0.2855002872924919</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1662211635198655</v>
+        <v>0.1569946977670183</v>
       </c>
       <c r="C63">
-        <v>-6256.567352241767</v>
+        <v>-6027.853709696432</v>
       </c>
       <c r="D63">
-        <v>2772.111647758233</v>
+        <v>3000.82529030357</v>
       </c>
       <c r="E63">
         <v>-1793.020999999999</v>
@@ -6459,37 +6459,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M63">
-        <v>2585.333425507867</v>
+        <v>2410.441240507866</v>
       </c>
       <c r="N63">
-        <v>-1908.433425507867</v>
+        <v>-1733.541240507867</v>
       </c>
       <c r="O63">
-        <v>-477.1083563769668</v>
+        <v>-433.3853101269667</v>
       </c>
       <c r="P63">
-        <v>-1431.3250691309</v>
+        <v>-1300.1559303809</v>
       </c>
       <c r="Q63">
-        <v>-809.2250691309004</v>
+        <v>-678.0559303809001</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1020905945471138</v>
+        <v>0.1018945285141724</v>
       </c>
       <c r="T63">
-        <v>1.096696054183014</v>
+        <v>1.093386769432237</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.06545577383959948</v>
+        <v>0.07020498867848161</v>
       </c>
       <c r="W63">
-        <v>0.2072226748303133</v>
+        <v>0.1922226748303133</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2618230953583979</v>
+        <v>0.2808199547139264</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1679805296864909</v>
+        <v>0.1586040639336437</v>
       </c>
       <c r="C64">
-        <v>-6487.62400078764</v>
+        <v>-6261.805233693875</v>
       </c>
       <c r="D64">
-        <v>2732.19399921236</v>
+        <v>2958.012766306125</v>
       </c>
       <c r="E64">
         <v>-1601.882</v>
@@ -6541,37 +6541,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M64">
-        <v>2627.715940680127</v>
+        <v>2449.956670680127</v>
       </c>
       <c r="N64">
-        <v>-1950.815940680127</v>
+        <v>-1773.056670680127</v>
       </c>
       <c r="O64">
-        <v>-487.7039851700317</v>
+        <v>-443.2641676700317</v>
       </c>
       <c r="P64">
-        <v>-1463.111955510095</v>
+        <v>-1329.792503010095</v>
       </c>
       <c r="Q64">
-        <v>-841.0119555100952</v>
+        <v>-707.692503010095</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1035719259825642</v>
+        <v>0.1033707003171769</v>
       </c>
       <c r="T64">
-        <v>1.125556476661514</v>
+        <v>1.122160105469928</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.06440003555186401</v>
+        <v>0.06907265015140933</v>
       </c>
       <c r="W64">
-        <v>0.2074567706663169</v>
+        <v>0.1924567706663169</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.257600142207456</v>
+        <v>0.2762906006056373</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1697398958531162</v>
+        <v>0.160213430100269</v>
       </c>
       <c r="C65">
-        <v>-6717.547361947409</v>
+        <v>-6494.552335665532</v>
       </c>
       <c r="D65">
-        <v>2693.409638052593</v>
+        <v>2916.404664334469</v>
       </c>
       <c r="E65">
         <v>-1410.742999999999</v>
@@ -6623,37 +6623,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M65">
-        <v>2670.098455852387</v>
+        <v>2489.472100852387</v>
       </c>
       <c r="N65">
-        <v>-1993.198455852387</v>
+        <v>-1812.572100852387</v>
       </c>
       <c r="O65">
-        <v>-498.2996139630968</v>
+        <v>-453.1430252130968</v>
       </c>
       <c r="P65">
-        <v>-1494.89884188929</v>
+        <v>-1359.429075639291</v>
       </c>
       <c r="Q65">
-        <v>-872.7988418892904</v>
+        <v>-737.3290756392906</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1051333293874984</v>
+        <v>0.1049266651906141</v>
       </c>
       <c r="T65">
-        <v>1.155976921976691</v>
+        <v>1.152488756969115</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.06337781276532649</v>
+        <v>0.06797625887916472</v>
       </c>
       <c r="W65">
-        <v>0.207683434888479</v>
+        <v>0.1926834348884791</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2535112510613059</v>
+        <v>0.2719050355166589</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1714992620197415</v>
+        <v>0.1618227962668943</v>
       </c>
       <c r="C66">
-        <v>-6946.385022336584</v>
+        <v>-6726.145135659897</v>
       </c>
       <c r="D66">
-        <v>2655.710977663417</v>
+        <v>2875.950864340103</v>
       </c>
       <c r="E66">
         <v>-1219.603999999999</v>
@@ -6705,37 +6705,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M66">
-        <v>2712.480971024647</v>
+        <v>2528.987531024647</v>
       </c>
       <c r="N66">
-        <v>-2035.580971024647</v>
+        <v>-1852.087531024647</v>
       </c>
       <c r="O66">
-        <v>-508.8952427561618</v>
+        <v>-463.0218827561617</v>
       </c>
       <c r="P66">
-        <v>-1526.685728268485</v>
+        <v>-1389.065648268485</v>
       </c>
       <c r="Q66">
-        <v>-904.5857282684855</v>
+        <v>-766.9656482684853</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.10678147742604</v>
+        <v>0.10656907255702</v>
       </c>
       <c r="T66">
-        <v>1.188087392031599</v>
+        <v>1.18450233355159</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06238753444086826</v>
+        <v>0.06691412983417779</v>
       </c>
       <c r="W66">
-        <v>0.2079030158536986</v>
+        <v>0.1929030158536987</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.249550137763473</v>
+        <v>0.2676565193367111</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1732586281863669</v>
+        <v>0.1634321624335197</v>
       </c>
       <c r="C67">
-        <v>-7174.181941136752</v>
+        <v>-6956.631010886831</v>
       </c>
       <c r="D67">
-        <v>2619.053058863249</v>
+        <v>2836.60398911317</v>
       </c>
       <c r="E67">
         <v>-1028.464999999998</v>
@@ -6787,37 +6787,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M67">
-        <v>2754.863486196907</v>
+        <v>2568.502961196907</v>
       </c>
       <c r="N67">
-        <v>-2077.963486196908</v>
+        <v>-1891.602961196907</v>
       </c>
       <c r="O67">
-        <v>-519.4908715492269</v>
+        <v>-472.9007402992269</v>
       </c>
       <c r="P67">
-        <v>-1558.472614647681</v>
+        <v>-1418.70222089768</v>
       </c>
       <c r="Q67">
-        <v>-936.3726146476805</v>
+        <v>-796.6022208976805</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1085238053524983</v>
+        <v>0.1083053317729349</v>
       </c>
       <c r="T67">
-        <v>1.222032746089645</v>
+        <v>1.21834525736735</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.06142772621870105</v>
+        <v>0.06588468168288274</v>
       </c>
       <c r="W67">
-        <v>0.2081158404815269</v>
+        <v>0.1931158404815269</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2457109048748042</v>
+        <v>0.2635387267315309</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1750179943529922</v>
+        <v>0.1650415286001451</v>
       </c>
       <c r="C68">
-        <v>-7400.980628964538</v>
+        <v>-7186.054780813771</v>
       </c>
       <c r="D68">
-        <v>2583.393371035462</v>
+        <v>2798.31921918623</v>
       </c>
       <c r="E68">
         <v>-837.3259999999991</v>
@@ -6869,37 +6869,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M68">
-        <v>2797.246001369167</v>
+        <v>2608.018391369167</v>
       </c>
       <c r="N68">
-        <v>-2120.346001369167</v>
+        <v>-1931.118391369168</v>
       </c>
       <c r="O68">
-        <v>-530.0865003422919</v>
+        <v>-482.7795978422919</v>
       </c>
       <c r="P68">
-        <v>-1590.259501026876</v>
+        <v>-1448.338793526876</v>
       </c>
       <c r="Q68">
-        <v>-968.1595010268755</v>
+        <v>-826.2387935268756</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1103686231569835</v>
+        <v>0.1101437238839036</v>
       </c>
       <c r="T68">
-        <v>1.257974885680516</v>
+        <v>1.254178941407566</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.06049700309417529</v>
+        <v>0.06488642893011179</v>
       </c>
       <c r="W68">
-        <v>0.2083222158782088</v>
+        <v>0.1933222158782088</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2419880123767011</v>
+        <v>0.2595457157204472</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1767773605196176</v>
+        <v>0.1666508947667704</v>
       </c>
       <c r="C69">
-        <v>-7626.821312324568</v>
+        <v>-7414.458877472485</v>
       </c>
       <c r="D69">
-        <v>2548.691687675434</v>
+        <v>2761.054122527516</v>
       </c>
       <c r="E69">
         <v>-646.1869999999981</v>
@@ -6951,37 +6951,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M69">
-        <v>2839.628516541427</v>
+        <v>2647.533821541427</v>
       </c>
       <c r="N69">
-        <v>-2162.728516541428</v>
+        <v>-1970.633821541428</v>
       </c>
       <c r="O69">
-        <v>-540.6821291353569</v>
+        <v>-492.6584553853569</v>
       </c>
       <c r="P69">
-        <v>-1622.046387406071</v>
+        <v>-1477.975366156071</v>
       </c>
       <c r="Q69">
-        <v>-999.9463874060708</v>
+        <v>-855.8753661560708</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1123252481011346</v>
+        <v>0.1120935336985673</v>
       </c>
       <c r="T69">
-        <v>1.296095336761744</v>
+        <v>1.292184363874462</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05959406274948609</v>
+        <v>0.06391797476697579</v>
       </c>
       <c r="W69">
-        <v>0.2085224308152883</v>
+        <v>0.1935224308152883</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2383762509979444</v>
+        <v>0.2556718990679031</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1785367266862429</v>
+        <v>0.1682602609333957</v>
       </c>
       <c r="C70">
-        <v>-7851.742084983876</v>
+        <v>-7641.883502336816</v>
       </c>
       <c r="D70">
-        <v>2514.909915016125</v>
+        <v>2724.768497663185</v>
       </c>
       <c r="E70">
         <v>-455.0479999999989</v>
@@ -7033,37 +7033,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M70">
-        <v>2882.011031713687</v>
+        <v>2687.049251713687</v>
       </c>
       <c r="N70">
-        <v>-2205.111031713688</v>
+        <v>-2010.149251713688</v>
       </c>
       <c r="O70">
-        <v>-551.2777579284219</v>
+        <v>-502.5373129284219</v>
       </c>
       <c r="P70">
-        <v>-1653.833273785266</v>
+        <v>-1507.611938785266</v>
       </c>
       <c r="Q70">
-        <v>-1031.733273785266</v>
+        <v>-885.5119387852657</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.114404162104295</v>
+        <v>0.1141652066266476</v>
       </c>
       <c r="T70">
-        <v>1.336598316035549</v>
+        <v>1.332565125245539</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05871767947375836</v>
+        <v>0.06297800454981439</v>
       </c>
       <c r="W70">
-        <v>0.2087167570777478</v>
+        <v>0.1937167570777478</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2348707178950334</v>
+        <v>0.2519120181992575</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1802960928528682</v>
+        <v>0.1698696271000211</v>
       </c>
       <c r="C71">
-        <v>-8075.779047465436</v>
+        <v>-7868.366770990823</v>
       </c>
       <c r="D71">
-        <v>2482.011952534566</v>
+        <v>2689.424229009179</v>
       </c>
       <c r="E71">
         <v>-263.9089999999978</v>
@@ -7115,37 +7115,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M71">
-        <v>2924.393546885948</v>
+        <v>2726.564681885948</v>
       </c>
       <c r="N71">
-        <v>-2247.493546885948</v>
+        <v>-2049.664681885948</v>
       </c>
       <c r="O71">
-        <v>-561.873386721487</v>
+        <v>-512.416170471487</v>
       </c>
       <c r="P71">
-        <v>-1685.620160164461</v>
+        <v>-1537.248511414461</v>
       </c>
       <c r="Q71">
-        <v>-1063.520160164461</v>
+        <v>-915.148511414461</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1166171995915303</v>
+        <v>0.1163705358726685</v>
       </c>
       <c r="T71">
-        <v>1.379714390746373</v>
+        <v>1.375551097027653</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05786669861181983</v>
+        <v>0.06206527984619388</v>
       </c>
       <c r="W71">
-        <v>0.2089054506949186</v>
+        <v>0.1939054506949186</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2314667944472792</v>
+        <v>0.2482611193847755</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1820554590194936</v>
+        <v>0.1714789932666464</v>
       </c>
       <c r="C72">
-        <v>-8298.966435734592</v>
+        <v>-8093.944846681753</v>
       </c>
       <c r="D72">
-        <v>2449.963564265409</v>
+        <v>2654.985153318248</v>
       </c>
       <c r="E72">
         <v>-72.76999999999862</v>
@@ -7197,37 +7197,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M72">
-        <v>2966.776062058208</v>
+        <v>2766.080112058208</v>
       </c>
       <c r="N72">
-        <v>-2289.876062058208</v>
+        <v>-2089.180112058208</v>
       </c>
       <c r="O72">
-        <v>-572.469015514552</v>
+        <v>-522.295028014552</v>
       </c>
       <c r="P72">
-        <v>-1717.407046543656</v>
+        <v>-1566.885084043656</v>
       </c>
       <c r="Q72">
-        <v>-1095.307046543656</v>
+        <v>-944.7850840436562</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.118977772911248</v>
+        <v>0.1187228870684241</v>
       </c>
       <c r="T72">
-        <v>1.425704870437919</v>
+        <v>1.421402800261909</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05704003148879384</v>
+        <v>0.06117863299124825</v>
       </c>
       <c r="W72">
-        <v>0.2090887530658845</v>
+        <v>0.1940887530658846</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2281601259551753</v>
+        <v>0.2447145319649929</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1838148251861189</v>
+        <v>0.1730883594332717</v>
       </c>
       <c r="C73">
-        <v>-8521.336740042811</v>
+        <v>-8318.65206374156</v>
       </c>
       <c r="D73">
-        <v>2418.732259957189</v>
+        <v>2621.416936258441</v>
       </c>
       <c r="E73">
         <v>118.3690000000006</v>
@@ -7279,37 +7279,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M73">
-        <v>3009.158577230468</v>
+        <v>2805.595542230467</v>
       </c>
       <c r="N73">
-        <v>-2332.258577230468</v>
+        <v>-2128.695542230468</v>
       </c>
       <c r="O73">
-        <v>-583.0646443076171</v>
+        <v>-532.1738855576169</v>
       </c>
       <c r="P73">
-        <v>-1749.193932922851</v>
+        <v>-1596.521656672851</v>
       </c>
       <c r="Q73">
-        <v>-1127.093932922851</v>
+        <v>-974.4216566728509</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1215011443909462</v>
+        <v>0.1212374693811283</v>
       </c>
       <c r="T73">
-        <v>1.474867107349571</v>
+        <v>1.470416689926112</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05623665076359955</v>
+        <v>0.06031696210404758</v>
       </c>
       <c r="W73">
-        <v>0.209266891989781</v>
+        <v>0.194266891989781</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2249466030543982</v>
+        <v>0.2412678484161903</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1855741913527443</v>
+        <v>0.1746977255998971</v>
       </c>
       <c r="C74">
-        <v>-8742.920814795951</v>
+        <v>-8542.521041762491</v>
       </c>
       <c r="D74">
-        <v>2388.28718520405</v>
+        <v>2588.686958237507</v>
       </c>
       <c r="E74">
         <v>309.5079999999998</v>
@@ -7361,37 +7361,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M74">
-        <v>3051.541092402728</v>
+        <v>2845.110972402727</v>
       </c>
       <c r="N74">
-        <v>-2374.641092402728</v>
+        <v>-2168.210972402728</v>
       </c>
       <c r="O74">
-        <v>-593.660273100682</v>
+        <v>-542.0527431006819</v>
       </c>
       <c r="P74">
-        <v>-1780.980819302046</v>
+        <v>-1626.158229302046</v>
       </c>
       <c r="Q74">
-        <v>-1158.880819302046</v>
+        <v>-1004.058229302046</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1242047566906229</v>
+        <v>0.1239316647161686</v>
       </c>
       <c r="T74">
-        <v>1.527540932612055</v>
+        <v>1.522931571709187</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05545558616966068</v>
+        <v>0.05947922651926915</v>
       </c>
       <c r="W74">
-        <v>0.2094400826102359</v>
+        <v>0.1944400826102359</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2218223446786427</v>
+        <v>0.2379169060770766</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1873335575193696</v>
+        <v>0.1763070917665224</v>
       </c>
       <c r="C75">
-        <v>-8963.747980228081</v>
+        <v>-8765.582791324832</v>
       </c>
       <c r="D75">
-        <v>2358.59901977192</v>
+        <v>2556.764208675169</v>
       </c>
       <c r="E75">
         <v>500.6470000000008</v>
@@ -7443,37 +7443,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M75">
-        <v>3093.923607574988</v>
+        <v>2884.626402574988</v>
       </c>
       <c r="N75">
-        <v>-2417.023607574989</v>
+        <v>-2207.726402574988</v>
       </c>
       <c r="O75">
-        <v>-604.2559018937471</v>
+        <v>-551.9316006437471</v>
       </c>
       <c r="P75">
-        <v>-1812.767705681241</v>
+        <v>-1655.794801931241</v>
       </c>
       <c r="Q75">
-        <v>-1190.667705681241</v>
+        <v>-1033.694801931241</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1271086365680533</v>
+        <v>0.1268254300760267</v>
       </c>
       <c r="T75">
-        <v>1.584116522708798</v>
+        <v>1.579336444735453</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05469592060569271</v>
+        <v>0.05866444259434764</v>
       </c>
       <c r="W75">
-        <v>0.2096085282821852</v>
+        <v>0.1946085282821852</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2187836824227708</v>
+        <v>0.2346577703773906</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.189092923685995</v>
+        <v>0.1779164579331478</v>
       </c>
       <c r="C76">
-        <v>-9183.846116585126</v>
+        <v>-8987.866811997141</v>
       </c>
       <c r="D76">
-        <v>2329.639883414874</v>
+        <v>2525.619188002858</v>
       </c>
       <c r="E76">
         <v>691.7860000000001</v>
@@ -7525,37 +7525,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M76">
-        <v>3136.306122747248</v>
+        <v>2924.141832747248</v>
       </c>
       <c r="N76">
-        <v>-2459.406122747248</v>
+        <v>-2247.241832747248</v>
       </c>
       <c r="O76">
-        <v>-614.8515306868121</v>
+        <v>-561.8104581868121</v>
       </c>
       <c r="P76">
-        <v>-1844.554592060436</v>
+        <v>-1685.431374560436</v>
       </c>
       <c r="Q76">
-        <v>-1222.454592060436</v>
+        <v>-1063.331374560436</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1302358918206708</v>
+        <v>0.1299417927712585</v>
       </c>
       <c r="T76">
-        <v>1.645044081274521</v>
+        <v>1.640080154148355</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05395678654345363</v>
+        <v>0.05787167985658619</v>
       </c>
       <c r="W76">
-        <v>0.2097724213684062</v>
+        <v>0.1947724213684061</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2158271461738145</v>
+        <v>0.2314867194263447</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1908522898526203</v>
+        <v>0.1795258240997731</v>
       </c>
       <c r="C77">
-        <v>-9403.241751454287</v>
+        <v>-9209.401183260055</v>
       </c>
       <c r="D77">
-        <v>2301.383248545714</v>
+        <v>2495.223816739945</v>
       </c>
       <c r="E77">
         <v>882.9250000000011</v>
@@ -7607,37 +7607,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M77">
-        <v>3178.688637919508</v>
+        <v>2963.657262919508</v>
       </c>
       <c r="N77">
-        <v>-2501.788637919509</v>
+        <v>-2286.757262919508</v>
       </c>
       <c r="O77">
-        <v>-625.4471594798772</v>
+        <v>-571.6893157298771</v>
       </c>
       <c r="P77">
-        <v>-1876.341478439632</v>
+        <v>-1715.067947189631</v>
       </c>
       <c r="Q77">
-        <v>-1254.241478439631</v>
+        <v>-1092.967947189631</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1336133274934976</v>
+        <v>0.1333074644821089</v>
       </c>
       <c r="T77">
-        <v>1.710845844525502</v>
+        <v>1.70568336031429</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05323736272287424</v>
+        <v>0.05710005745849838</v>
       </c>
       <c r="W77">
-        <v>0.2099319439723279</v>
+        <v>0.1949319439723279</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.212949450891497</v>
+        <v>0.2284002298339934</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1926116560192456</v>
+        <v>0.1811351902663984</v>
       </c>
       <c r="C78">
-        <v>-9621.960140814208</v>
+        <v>-9430.21264894259</v>
       </c>
       <c r="D78">
-        <v>2273.803859185793</v>
+        <v>2465.551351057411</v>
       </c>
       <c r="E78">
         <v>1074.064000000002</v>
@@ -7689,37 +7689,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M78">
-        <v>3221.071153091769</v>
+        <v>3003.172693091768</v>
       </c>
       <c r="N78">
-        <v>-2544.171153091769</v>
+        <v>-2326.272693091769</v>
       </c>
       <c r="O78">
-        <v>-636.0427882729423</v>
+        <v>-581.5681732729422</v>
       </c>
       <c r="P78">
-        <v>-1908.128364818827</v>
+        <v>-1744.704519818827</v>
       </c>
       <c r="Q78">
-        <v>-1286.028364818827</v>
+        <v>-1122.604519818827</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.13727221613906</v>
+        <v>0.1369536088355301</v>
       </c>
       <c r="T78">
-        <v>1.782131088047398</v>
+        <v>1.776753500327385</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05253687110809958</v>
+        <v>0.05634874091299182</v>
       </c>
       <c r="W78">
-        <v>0.2100872686129885</v>
+        <v>0.1950872686129884</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2101474844323983</v>
+        <v>0.2253949636519672</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.194371022185871</v>
+        <v>0.1827445564330238</v>
       </c>
       <c r="C79">
-        <v>-9840.025344326417</v>
+        <v>-9650.326695704745</v>
       </c>
       <c r="D79">
-        <v>2246.877655673584</v>
+        <v>2436.576304295257</v>
       </c>
       <c r="E79">
         <v>1265.203000000001</v>
@@ -7771,37 +7771,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M79">
-        <v>3263.453668264029</v>
+        <v>3042.688123264028</v>
       </c>
       <c r="N79">
-        <v>-2586.553668264029</v>
+        <v>-2365.788123264029</v>
       </c>
       <c r="O79">
-        <v>-646.6384170660073</v>
+        <v>-591.4470308160072</v>
       </c>
       <c r="P79">
-        <v>-1939.915251198022</v>
+        <v>-1774.341092448022</v>
       </c>
       <c r="Q79">
-        <v>-1317.815251198022</v>
+        <v>-1152.241092448022</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1412492690146713</v>
+        <v>0.1409168092196836</v>
       </c>
       <c r="T79">
-        <v>1.859615048397285</v>
+        <v>1.854003652515533</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05185457408072167</v>
+        <v>0.05561693908295296</v>
       </c>
       <c r="W79">
-        <v>0.2102385588473981</v>
+        <v>0.1952385588473981</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2074182963228867</v>
+        <v>0.2224677563318118</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1961303883524963</v>
+        <v>0.1843539225996491</v>
       </c>
       <c r="C80">
-        <v>-10057.46029533979</v>
+        <v>-9869.767626050409</v>
       </c>
       <c r="D80">
-        <v>2220.581704660211</v>
+        <v>2408.274373949593</v>
       </c>
       <c r="E80">
         <v>1456.342000000002</v>
@@ -7853,37 +7853,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M80">
-        <v>3305.836183436289</v>
+        <v>3082.203553436289</v>
       </c>
       <c r="N80">
-        <v>-2628.936183436289</v>
+        <v>-2405.303553436289</v>
       </c>
       <c r="O80">
-        <v>-657.2340458590724</v>
+        <v>-601.3258883590722</v>
       </c>
       <c r="P80">
-        <v>-1971.702137577217</v>
+        <v>-1803.977665077217</v>
       </c>
       <c r="Q80">
-        <v>-1349.602137577217</v>
+        <v>-1181.877665077217</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1455878721517018</v>
+        <v>0.145240300547851</v>
       </c>
       <c r="T80">
-        <v>1.944143005142617</v>
+        <v>1.938276545811693</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05118977184891754</v>
+        <v>0.05490390140240228</v>
       </c>
       <c r="W80">
-        <v>0.2103859698450281</v>
+        <v>0.1953859698450281</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2047590873956701</v>
+        <v>0.2196156056096091</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1978897545191217</v>
+        <v>0.1859632887662745</v>
       </c>
       <c r="C81">
-        <v>-10274.28686603618</v>
+        <v>-10088.55862631025</v>
       </c>
       <c r="D81">
-        <v>2194.894133963822</v>
+        <v>2380.62237368975</v>
       </c>
       <c r="E81">
         <v>1647.481000000002</v>
@@ -7935,37 +7935,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M81">
-        <v>3348.218698608549</v>
+        <v>3121.718983608549</v>
       </c>
       <c r="N81">
-        <v>-2671.318698608549</v>
+        <v>-2444.818983608549</v>
       </c>
       <c r="O81">
-        <v>-667.8296746521373</v>
+        <v>-611.2047459021372</v>
       </c>
       <c r="P81">
-        <v>-2003.489023956412</v>
+        <v>-1833.614237706412</v>
       </c>
       <c r="Q81">
-        <v>-1381.389023956412</v>
+        <v>-1211.514237706412</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1503396755874972</v>
+        <v>0.1499755529548915</v>
       </c>
       <c r="T81">
-        <v>2.036721243482741</v>
+        <v>2.030575428945584</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05054180005336162</v>
+        <v>0.05420891530870098</v>
       </c>
       <c r="W81">
-        <v>0.2105296489186674</v>
+        <v>0.1955296489186674</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2021672002134465</v>
+        <v>0.2168356612348039</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2237579257999633</v>
+        <v>0.1875726549328998</v>
       </c>
       <c r="C82">
-        <v>-10784.47823274286</v>
+        <v>-10306.72182999425</v>
       </c>
       <c r="D82">
-        <v>1875.841767257138</v>
+        <v>2353.598170005754</v>
       </c>
       <c r="E82">
         <v>1838.620000000003</v>
@@ -8017,45 +8017,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M82">
-        <v>3849.334813780809</v>
+        <v>3161.234413780809</v>
       </c>
       <c r="N82">
-        <v>-3172.43481378081</v>
+        <v>-2484.334413780809</v>
       </c>
       <c r="O82">
-        <v>-793.1087034452024</v>
+        <v>-621.0836034452024</v>
       </c>
       <c r="P82">
-        <v>-2379.326110335607</v>
+        <v>-1863.250810335607</v>
       </c>
       <c r="Q82">
-        <v>-1757.226110335607</v>
+        <v>-1241.150810335607</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1561106849379534</v>
+        <v>0.1551843306026361</v>
       </c>
       <c r="T82">
-        <v>2.149156424425827</v>
+        <v>2.132104200392863</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04396214104165895</v>
+        <v>0.05353130386734222</v>
       </c>
       <c r="W82">
-        <v>0.2406697360154657</v>
+        <v>0.1956697360154658</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.1758485641666357</v>
+        <v>0.2141252154693688</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2258172919665886</v>
+        <v>0.1891820210995251</v>
       </c>
       <c r="C83">
-        <v>-10997.07653272027</v>
+        <v>-10524.27837687768</v>
       </c>
       <c r="D83">
-        <v>1854.382467279729</v>
+        <v>2327.180623122319</v>
       </c>
       <c r="E83">
         <v>2029.759000000002</v>
@@ -8099,45 +8099,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M83">
-        <v>3897.451498953069</v>
+        <v>3200.749843953069</v>
       </c>
       <c r="N83">
-        <v>-3220.551498953069</v>
+        <v>-2523.849843953069</v>
       </c>
       <c r="O83">
-        <v>-805.1378747382673</v>
+        <v>-630.9624609882673</v>
       </c>
       <c r="P83">
-        <v>-2415.413624214802</v>
+        <v>-1892.887382964802</v>
       </c>
       <c r="Q83">
-        <v>-1793.313624214802</v>
+        <v>-1270.787382964802</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1619165104610036</v>
+        <v>0.1609414006343538</v>
       </c>
       <c r="T83">
-        <v>2.262269920448239</v>
+        <v>2.244320210939855</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04341939855966317</v>
+        <v>0.05287042357268368</v>
       </c>
       <c r="W83">
-        <v>0.2408063641716024</v>
+        <v>0.1958063641716024</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.1736775942386526</v>
+        <v>0.2114816942907347</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2278766581332139</v>
+        <v>0.1907913872661505</v>
       </c>
       <c r="C84">
-        <v>-11209.18940467208</v>
+        <v>-10741.24846815212</v>
       </c>
       <c r="D84">
-        <v>1833.408595327921</v>
+        <v>2301.349531847883</v>
       </c>
       <c r="E84">
         <v>2220.898000000003</v>
@@ -8181,45 +8181,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M84">
-        <v>3945.568184125329</v>
+        <v>3240.265274125329</v>
       </c>
       <c r="N84">
-        <v>-3268.66818412533</v>
+        <v>-2563.36527412533</v>
       </c>
       <c r="O84">
-        <v>-817.1670460313325</v>
+        <v>-640.8413185313324</v>
       </c>
       <c r="P84">
-        <v>-2451.501138093997</v>
+        <v>-1922.523955593997</v>
       </c>
       <c r="Q84">
-        <v>-1829.401138093997</v>
+        <v>-1300.423955593997</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1683674277088371</v>
+        <v>0.1673381451140401</v>
       </c>
       <c r="T84">
-        <v>2.387951582695363</v>
+        <v>2.369004667103181</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04288989369917947</v>
+        <v>0.05222566230960217</v>
       </c>
       <c r="W84">
-        <v>0.2409396599336869</v>
+        <v>0.1959396599336869</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.1715595747967178</v>
+        <v>0.2089026492384086</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2299360242998393</v>
+        <v>0.1924007534327759</v>
       </c>
       <c r="C85">
-        <v>-11420.83313559138</v>
+        <v>-10957.65141794371</v>
       </c>
       <c r="D85">
-        <v>1812.903864408618</v>
+        <v>2276.085582056291</v>
       </c>
       <c r="E85">
         <v>2412.037000000002</v>
@@ -8263,45 +8263,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M85">
-        <v>3993.68486929759</v>
+        <v>3279.780704297589</v>
       </c>
       <c r="N85">
-        <v>-3316.78486929759</v>
+        <v>-2602.88070429759</v>
       </c>
       <c r="O85">
-        <v>-829.1962173243975</v>
+        <v>-650.7201760743974</v>
       </c>
       <c r="P85">
-        <v>-2487.588651973193</v>
+        <v>-1952.160528223192</v>
       </c>
       <c r="Q85">
-        <v>-1865.488651973193</v>
+        <v>-1330.060528223192</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1755772763975922</v>
+        <v>0.1744874477678072</v>
       </c>
       <c r="T85">
-        <v>2.528419322853914</v>
+        <v>2.508357882815133</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04237314799196044</v>
+        <v>0.05159643746249853</v>
       </c>
       <c r="W85">
-        <v>0.2410697437496971</v>
+        <v>0.1960697437496971</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.1694925919678417</v>
+        <v>0.206385749849994</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2319953904664646</v>
+        <v>0.1940101195994012</v>
       </c>
       <c r="C86">
-        <v>-11632.02329191891</v>
+        <v>-11173.505701475</v>
       </c>
       <c r="D86">
-        <v>1792.852708081094</v>
+        <v>2251.370298525003</v>
       </c>
       <c r="E86">
         <v>2603.176000000001</v>
@@ -8345,45 +8345,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M86">
-        <v>4041.801554469849</v>
+        <v>3319.296134469849</v>
       </c>
       <c r="N86">
-        <v>-3364.90155446985</v>
+        <v>-2642.39613446985</v>
       </c>
       <c r="O86">
-        <v>-841.2253886174624</v>
+        <v>-660.5990336174624</v>
       </c>
       <c r="P86">
-        <v>-2523.676165852387</v>
+        <v>-1981.797100852387</v>
       </c>
       <c r="Q86">
-        <v>-1901.576165852387</v>
+        <v>-1359.697100852387</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1836883561724417</v>
+        <v>0.1825304132532951</v>
       </c>
       <c r="T86">
-        <v>2.686445530532283</v>
+        <v>2.665130250491078</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04186870575396091</v>
+        <v>0.05098219415937354</v>
       </c>
       <c r="W86">
-        <v>0.2411967303319928</v>
+        <v>0.1961967303319928</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.1674748230158436</v>
+        <v>0.2039287766374942</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.23405475663309</v>
+        <v>0.1956194857660265</v>
       </c>
       <c r="C87">
-        <v>-11842.77475895452</v>
+        <v>-11388.82900012257</v>
       </c>
       <c r="D87">
-        <v>1773.240241045477</v>
+        <v>2227.185999877431</v>
       </c>
       <c r="E87">
         <v>2794.315000000001</v>
@@ -8427,45 +8427,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M87">
-        <v>4089.918239642109</v>
+        <v>3358.811564642109</v>
       </c>
       <c r="N87">
-        <v>-3413.01823964211</v>
+        <v>-2681.911564642109</v>
       </c>
       <c r="O87">
-        <v>-853.2545599105274</v>
+        <v>-670.4778911605273</v>
       </c>
       <c r="P87">
-        <v>-2559.763679731582</v>
+        <v>-2011.433673481582</v>
       </c>
       <c r="Q87">
-        <v>-1937.663679731582</v>
+        <v>-1389.333673481582</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1928809132506045</v>
+        <v>0.1916457741368481</v>
       </c>
       <c r="T87">
-        <v>2.865541899234435</v>
+        <v>2.842805600523816</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04137613274509078</v>
+        <v>0.05038240363985151</v>
       </c>
       <c r="W87">
-        <v>0.2413207289947051</v>
+        <v>0.1963207289947051</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.1655045309803631</v>
+        <v>0.201529614559406</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2361141227997153</v>
+        <v>0.227470567381039</v>
       </c>
       <c r="C88">
-        <v>-12053.10177770997</v>
+        <v>-11970.44557762208</v>
       </c>
       <c r="D88">
-        <v>1754.052222290028</v>
+        <v>1836.708422377924</v>
       </c>
       <c r="E88">
         <v>2985.454000000002</v>
@@ -8509,37 +8509,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M88">
-        <v>4138.034924814369</v>
+        <v>3973.655384814369</v>
       </c>
       <c r="N88">
-        <v>-3461.13492481437</v>
+        <v>-3296.75538481437</v>
       </c>
       <c r="O88">
-        <v>-865.2837312035924</v>
+        <v>-824.1888462035924</v>
       </c>
       <c r="P88">
-        <v>-2595.851193610777</v>
+        <v>-2472.566538610778</v>
       </c>
       <c r="Q88">
-        <v>-1973.751193610777</v>
+        <v>-1850.466538610778</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2033866927685048</v>
+        <v>0.2030755826351029</v>
       </c>
       <c r="T88">
-        <v>3.070223463465466</v>
+        <v>3.065593842446172</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04089501492247345</v>
+        <v>0.04258673277172105</v>
       </c>
       <c r="W88">
-        <v>0.2414418439675868</v>
+        <v>0.2314418439675868</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1635800596898938</v>
+        <v>0.1703469310868841</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2381734889663406</v>
+        <v>0.2294299335476644</v>
       </c>
       <c r="C89">
-        <v>-12263.0179793945</v>
+        <v>-12181.18260432304</v>
       </c>
       <c r="D89">
-        <v>1735.275020605496</v>
+        <v>1817.110395676961</v>
       </c>
       <c r="E89">
         <v>3176.593000000001</v>
@@ -8591,37 +8591,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M89">
-        <v>4186.151609986629</v>
+        <v>4019.860679986629</v>
       </c>
       <c r="N89">
-        <v>-3509.25160998663</v>
+        <v>-3342.96067998663</v>
       </c>
       <c r="O89">
-        <v>-877.3129024966574</v>
+        <v>-835.7401699966574</v>
       </c>
       <c r="P89">
-        <v>-2631.938707489972</v>
+        <v>-2507.220509989972</v>
       </c>
       <c r="Q89">
-        <v>-2009.838707489972</v>
+        <v>-1885.120509989972</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2155087460583898</v>
+        <v>0.2151737043762647</v>
       </c>
       <c r="T89">
-        <v>3.306394499116656</v>
+        <v>3.30140875340357</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0404249572796864</v>
+        <v>0.04209723009618403</v>
       </c>
       <c r="W89">
-        <v>0.2415601746882184</v>
+        <v>0.2315601746882184</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1616998291187456</v>
+        <v>0.1683889203847361</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.240232855132966</v>
+        <v>0.2313892997142897</v>
       </c>
       <c r="C90">
-        <v>-12472.53641770899</v>
+        <v>-12391.50581718334</v>
       </c>
       <c r="D90">
-        <v>1716.895582291013</v>
+        <v>1797.926182816663</v>
       </c>
       <c r="E90">
         <v>3367.732</v>
@@ -8673,37 +8673,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M90">
-        <v>4234.268295158889</v>
+        <v>4066.065975158889</v>
       </c>
       <c r="N90">
-        <v>-3557.36829515889</v>
+        <v>-3389.16597515889</v>
       </c>
       <c r="O90">
-        <v>-889.3420737897225</v>
+        <v>-847.2914937897224</v>
       </c>
       <c r="P90">
-        <v>-2668.026221369168</v>
+        <v>-2541.874481369167</v>
       </c>
       <c r="Q90">
-        <v>-2045.926221369168</v>
+        <v>-1919.774481369167</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2296511415632556</v>
+        <v>0.2292881797409534</v>
       </c>
       <c r="T90">
-        <v>3.581927374043044</v>
+        <v>3.576526149520534</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03996558276514451</v>
+        <v>0.04161885248145467</v>
       </c>
       <c r="W90">
-        <v>0.2416758160742901</v>
+        <v>0.2316758160742901</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.159862331060578</v>
+        <v>0.1664754099258187</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2422922212995914</v>
+        <v>0.2333486658809151</v>
       </c>
       <c r="C91">
-        <v>-12681.66959910922</v>
+        <v>-12601.42818584211</v>
       </c>
       <c r="D91">
-        <v>1698.901400890786</v>
+        <v>1779.142814157897</v>
       </c>
       <c r="E91">
         <v>3558.871000000003</v>
@@ -8755,37 +8755,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M91">
-        <v>4282.38498033115</v>
+        <v>4112.27127033115</v>
       </c>
       <c r="N91">
-        <v>-3605.484980331151</v>
+        <v>-3435.37127033115</v>
       </c>
       <c r="O91">
-        <v>-901.3712450827877</v>
+        <v>-858.8428175827876</v>
       </c>
       <c r="P91">
-        <v>-2704.113735248363</v>
+        <v>-2576.528452748363</v>
       </c>
       <c r="Q91">
-        <v>-2082.013735248363</v>
+        <v>-1954.428452748363</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2463648817053698</v>
+        <v>0.2459689233537674</v>
       </c>
       <c r="T91">
-        <v>3.907557135319685</v>
+        <v>3.901664890386038</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.0395165312734013</v>
+        <v>0.04115122492548326</v>
       </c>
       <c r="W91">
-        <v>0.2417888587775288</v>
+        <v>0.2317888587775288</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1580661250936052</v>
+        <v>0.164604899701933</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2443515874662167</v>
+        <v>0.2353080320475404</v>
       </c>
       <c r="C92">
-        <v>-12890.42951118589</v>
+        <v>-12810.9621435544</v>
       </c>
       <c r="D92">
-        <v>1681.280488814109</v>
+        <v>1760.747856445598</v>
       </c>
       <c r="E92">
         <v>3750.010000000002</v>
@@ -8837,37 +8837,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M92">
-        <v>4330.501665503411</v>
+        <v>4158.47656550341</v>
       </c>
       <c r="N92">
-        <v>-3653.601665503411</v>
+        <v>-3481.57656550341</v>
       </c>
       <c r="O92">
-        <v>-913.4004163758527</v>
+        <v>-870.3941413758525</v>
       </c>
       <c r="P92">
-        <v>-2740.201249127558</v>
+        <v>-2611.182424127558</v>
       </c>
       <c r="Q92">
-        <v>-2118.101249127558</v>
+        <v>-1989.082424127558</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2664213698759068</v>
+        <v>0.2659858156891441</v>
       </c>
       <c r="T92">
-        <v>4.298312848851654</v>
+        <v>4.291831379424642</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03907745870369685</v>
+        <v>0.0406939890929779</v>
       </c>
       <c r="W92">
-        <v>0.2418993894206956</v>
+        <v>0.2318993894206955</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1563098348147873</v>
+        <v>0.1627759563719116</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.246410953632842</v>
+        <v>0.2372673982141658</v>
       </c>
       <c r="C93">
-        <v>-13098.82764929661</v>
+        <v>-13020.11961463646</v>
       </c>
       <c r="D93">
-        <v>1664.021350703395</v>
+        <v>1742.729385363546</v>
       </c>
       <c r="E93">
         <v>3941.149000000001</v>
@@ -8919,37 +8919,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M93">
-        <v>4378.61835067567</v>
+        <v>4204.68186067567</v>
       </c>
       <c r="N93">
-        <v>-3701.71835067567</v>
+        <v>-3527.78186067567</v>
       </c>
       <c r="O93">
-        <v>-925.4295876689175</v>
+        <v>-881.9454651689175</v>
       </c>
       <c r="P93">
-        <v>-2776.288763006753</v>
+        <v>-2645.836395506753</v>
       </c>
       <c r="Q93">
-        <v>-2154.188763006753</v>
+        <v>-2023.736395506753</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2909348554176742</v>
+        <v>0.2904509063212712</v>
       </c>
       <c r="T93">
-        <v>4.775903165390726</v>
+        <v>4.768701532694047</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.0386480360805793</v>
+        <v>0.04024680239964847</v>
       </c>
       <c r="W93">
-        <v>0.2420074908189575</v>
+        <v>0.2320074908189575</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1545921443223172</v>
+        <v>0.1609872095985938</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2484703197994674</v>
+        <v>0.2392267643807911</v>
       </c>
       <c r="C94">
-        <v>-13306.87504157413</v>
+        <v>-13228.91204024276</v>
       </c>
       <c r="D94">
-        <v>1647.112958425869</v>
+        <v>1725.075959757238</v>
       </c>
       <c r="E94">
         <v>4132.288</v>
@@ -9001,37 +9001,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M94">
-        <v>4426.73503584793</v>
+        <v>4250.88715584793</v>
       </c>
       <c r="N94">
-        <v>-3749.83503584793</v>
+        <v>-3573.98715584793</v>
       </c>
       <c r="O94">
-        <v>-937.4587589619825</v>
+        <v>-893.4967889619825</v>
       </c>
       <c r="P94">
-        <v>-2812.376276885948</v>
+        <v>-2680.490366885947</v>
       </c>
       <c r="Q94">
-        <v>-2190.276276885948</v>
+        <v>-2058.390366885948</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3215767123448836</v>
+        <v>0.3210322696114302</v>
       </c>
       <c r="T94">
-        <v>5.372891061064569</v>
+        <v>5.364789224280805</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03822794873187736</v>
+        <v>0.03980933715617403</v>
       </c>
       <c r="W94">
-        <v>0.2421132421868225</v>
+        <v>0.2321132421868225</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1529117949275094</v>
+        <v>0.1592373486246961</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2505296859660927</v>
+        <v>0.2411861305474164</v>
       </c>
       <c r="C95">
-        <v>-13514.58227242539</v>
+        <v>-13437.35040259227</v>
       </c>
       <c r="D95">
-        <v>1630.544727574609</v>
+        <v>1707.776597407735</v>
       </c>
       <c r="E95">
         <v>4323.427000000003</v>
@@ -9083,37 +9083,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M95">
-        <v>4474.851721020191</v>
+        <v>4297.09245102019</v>
       </c>
       <c r="N95">
-        <v>-3797.951721020191</v>
+        <v>-3620.192451020191</v>
       </c>
       <c r="O95">
-        <v>-949.4879302550478</v>
+        <v>-905.0481127550477</v>
       </c>
       <c r="P95">
-        <v>-2848.463790765143</v>
+        <v>-2715.144338265143</v>
       </c>
       <c r="Q95">
-        <v>-2226.363790765143</v>
+        <v>-2093.044338265143</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3609733855370098</v>
+        <v>0.3603511652702061</v>
       </c>
       <c r="T95">
-        <v>6.140446926930936</v>
+        <v>6.13118768489235</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03781689551970663</v>
+        <v>0.03938127976739796</v>
       </c>
       <c r="W95">
-        <v>0.2422167193317226</v>
+        <v>0.2322167193317226</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1512675820788265</v>
+        <v>0.1575251190695918</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525890521327181</v>
+        <v>0.2431454967140418</v>
       </c>
       <c r="C96">
-        <v>-13721.9595046263</v>
+        <v>-13645.4452477513</v>
       </c>
       <c r="D96">
-        <v>1614.306495373702</v>
+        <v>1690.820752248704</v>
       </c>
       <c r="E96">
         <v>4514.566000000003</v>
@@ -9165,37 +9165,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M96">
-        <v>4522.968406192451</v>
+        <v>4343.29774619245</v>
       </c>
       <c r="N96">
-        <v>-3846.068406192451</v>
+        <v>-3666.397746192451</v>
       </c>
       <c r="O96">
-        <v>-961.5171015481128</v>
+        <v>-916.5994365481126</v>
       </c>
       <c r="P96">
-        <v>-2884.551304644338</v>
+        <v>-2749.798309644338</v>
       </c>
       <c r="Q96">
-        <v>-2262.451304644339</v>
+        <v>-2127.698309644338</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4135022831265115</v>
+        <v>0.4127763594819071</v>
       </c>
       <c r="T96">
-        <v>7.163854748086094</v>
+        <v>7.153052299041075</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03741458812056081</v>
+        <v>0.03896232998263841</v>
       </c>
       <c r="W96">
-        <v>0.2423179948352419</v>
+        <v>0.2323179948352419</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1496583524822432</v>
+        <v>0.1558493199305536</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2546484182993434</v>
+        <v>0.2451048628806671</v>
       </c>
       <c r="C97">
-        <v>-13929.01650010937</v>
+        <v>-13853.20670707266</v>
       </c>
       <c r="D97">
-        <v>1598.388499890628</v>
+        <v>1674.198292927339</v>
       </c>
       <c r="E97">
         <v>4705.705000000002</v>
@@ -9247,37 +9247,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M97">
-        <v>4571.085091364711</v>
+        <v>4389.50304136471</v>
       </c>
       <c r="N97">
-        <v>-3894.185091364711</v>
+        <v>-3712.60304136471</v>
       </c>
       <c r="O97">
-        <v>-973.5462728411778</v>
+        <v>-928.1507603411776</v>
       </c>
       <c r="P97">
-        <v>-2920.638818523534</v>
+        <v>-2784.452281023533</v>
       </c>
       <c r="Q97">
-        <v>-2298.538818523534</v>
+        <v>-2162.352281023533</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.487042739751814</v>
+        <v>0.4861716313782887</v>
       </c>
       <c r="T97">
-        <v>8.596625697703317</v>
+        <v>8.583662758849295</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.0370207503508707</v>
+        <v>0.03855220019334749</v>
       </c>
       <c r="W97">
-        <v>0.2424171382228976</v>
+        <v>0.2324171382228976</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1480830014034827</v>
+        <v>0.1542088007733899</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2567077844659687</v>
+        <v>0.2470642290472924</v>
       </c>
       <c r="C98">
-        <v>-14135.76263953352</v>
+        <v>-14060.64451738243</v>
       </c>
       <c r="D98">
-        <v>1582.781360466483</v>
+        <v>1657.899482617571</v>
       </c>
       <c r="E98">
         <v>4896.844000000001</v>
@@ -9329,37 +9329,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M98">
-        <v>4619.20177653697</v>
+        <v>4435.70833653697</v>
       </c>
       <c r="N98">
-        <v>-3942.30177653697</v>
+        <v>-3758.80833653697</v>
       </c>
       <c r="O98">
-        <v>-985.5754441342426</v>
+        <v>-939.7020841342426</v>
       </c>
       <c r="P98">
-        <v>-2956.726332402728</v>
+        <v>-2819.106252402727</v>
       </c>
       <c r="Q98">
-        <v>-2334.626332402728</v>
+        <v>-2197.006252402728</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5973534246897662</v>
+        <v>0.5962645392228596</v>
       </c>
       <c r="T98">
-        <v>10.74578212212912</v>
+        <v>10.7295784485616</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.0366351175347158</v>
+        <v>0.03815061477466678</v>
       </c>
       <c r="W98">
-        <v>0.2425142161233105</v>
+        <v>0.2325142161233105</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1465404701388632</v>
+        <v>0.1526024590986671</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.258767150632594</v>
+        <v>0.2490235952139178</v>
       </c>
       <c r="C99">
-        <v>-14342.20694071836</v>
+        <v>-14267.76803999895</v>
       </c>
       <c r="D99">
-        <v>1567.476059281641</v>
+        <v>1641.914960001054</v>
       </c>
       <c r="E99">
         <v>5087.983</v>
@@ -9411,37 +9411,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M99">
-        <v>4667.31846170923</v>
+        <v>4481.913631709231</v>
       </c>
       <c r="N99">
-        <v>-3990.418461709231</v>
+        <v>-3805.013631709231</v>
       </c>
       <c r="O99">
-        <v>-997.6046154273076</v>
+        <v>-951.2534079273078</v>
       </c>
       <c r="P99">
-        <v>-2992.813846281923</v>
+        <v>-2853.760223781923</v>
       </c>
       <c r="Q99">
-        <v>-2370.713846281923</v>
+        <v>-2231.660223781923</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7812045662530216</v>
+        <v>0.7797527189638128</v>
       </c>
       <c r="T99">
-        <v>14.32770949617216</v>
+        <v>14.30610459808213</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03625743591064657</v>
+        <v>0.03775730946771145</v>
       </c>
       <c r="W99">
-        <v>0.2426092924175293</v>
+        <v>0.2326092924175293</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1450297436425863</v>
+        <v>0.1510292378708458</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2608265167992194</v>
+        <v>0.2509829613805432</v>
       </c>
       <c r="C100">
-        <v>-14548.3580760193</v>
+        <v>-14474.58627866212</v>
       </c>
       <c r="D100">
-        <v>1552.463923980699</v>
+        <v>1626.235721337882</v>
       </c>
       <c r="E100">
         <v>5279.121999999999</v>
@@ -9493,37 +9493,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M100">
-        <v>4715.43514688149</v>
+        <v>4528.118926881491</v>
       </c>
       <c r="N100">
-        <v>-4038.535146881491</v>
+        <v>-3851.218926881491</v>
       </c>
       <c r="O100">
-        <v>-1009.633786720373</v>
+        <v>-962.8047317203727</v>
       </c>
       <c r="P100">
-        <v>-3028.901360161118</v>
+        <v>-2888.414195161118</v>
       </c>
       <c r="Q100">
-        <v>-2406.801360161118</v>
+        <v>-2266.314195161118</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.148906849379533</v>
+        <v>1.146729078445719</v>
       </c>
       <c r="T100">
-        <v>21.49156424425825</v>
+        <v>21.45915689712319</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03588746207482364</v>
+        <v>0.03737203079967358</v>
       </c>
       <c r="W100">
-        <v>0.242702428379213</v>
+        <v>0.232702428379213</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1435498482992945</v>
+        <v>0.1494881231986943</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2628858829658448</v>
+        <v>0.2529423275471684</v>
       </c>
       <c r="C101">
-        <v>-14754.22438871358</v>
+        <v>-14681.10789644516</v>
       </c>
       <c r="D101">
-        <v>1537.736611286418</v>
+        <v>1610.853103554844</v>
       </c>
       <c r="E101">
         <v>5470.261000000002</v>
@@ -9575,37 +9575,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M101">
-        <v>4763.551832053751</v>
+        <v>4574.324222053751</v>
       </c>
       <c r="N101">
-        <v>-4086.651832053752</v>
+        <v>-3897.424222053752</v>
       </c>
       <c r="O101">
-        <v>-1021.662958013438</v>
+        <v>-974.3560555134379</v>
       </c>
       <c r="P101">
-        <v>-3064.988874040314</v>
+        <v>-2923.068166540314</v>
       </c>
       <c r="Q101">
-        <v>-2442.888874040314</v>
+        <v>-2300.968166540314</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.252013698759065</v>
+        <v>2.247658156891438</v>
       </c>
       <c r="T101">
-        <v>42.98312848851648</v>
+        <v>42.91831379424638</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03552496245790623</v>
+        <v>0.03699453553907081</v>
       </c>
       <c r="W101">
-        <v>0.2427936828063172</v>
+        <v>0.2327936828063172</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1420998498316249</v>
+        <v>0.1479781421562832</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_power.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_power.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06865566077829674</v>
+        <v>0.06856229625132</v>
       </c>
       <c r="C2">
-        <v>17230.06555804425</v>
+        <v>17098.80863268141</v>
       </c>
       <c r="D2">
-        <v>14599.26555804425</v>
+        <v>14659.14763268141</v>
       </c>
       <c r="E2">
-        <v>-13452.5</v>
+        <v>-13261.361</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>191.139</v>
       </c>
       <c r="G2">
         <v>2630.8</v>
@@ -1457,28 +1457,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>10.74901067226011</v>
       </c>
       <c r="N2">
-        <v>676.8999999999997</v>
+        <v>666.1509893277397</v>
       </c>
       <c r="O2">
-        <v>169.2249999999999</v>
+        <v>166.5377473319349</v>
       </c>
       <c r="P2">
-        <v>507.6749999999998</v>
+        <v>499.6132419958047</v>
       </c>
       <c r="Q2">
-        <v>1129.775</v>
+        <v>1121.713241995805</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06865566077829674</v>
+        <v>0.06882880972358686</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880388</v>
+        <v>0.4488743650137058</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>62.97323731819066</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06856229625132</v>
+        <v>0.06846893172434326</v>
       </c>
       <c r="C3">
-        <v>17098.80863268141</v>
+        <v>16968.04496934263</v>
       </c>
       <c r="D3">
-        <v>14659.14763268141</v>
+        <v>14719.52296934263</v>
       </c>
       <c r="E3">
-        <v>-13261.361</v>
+        <v>-13070.222</v>
       </c>
       <c r="F3">
-        <v>191.139</v>
+        <v>382.278</v>
       </c>
       <c r="G3">
         <v>2630.8</v>
@@ -1539,28 +1539,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M3">
-        <v>10.74901067226011</v>
+        <v>21.49802134452021</v>
       </c>
       <c r="N3">
-        <v>666.1509893277397</v>
+        <v>655.4019786554795</v>
       </c>
       <c r="O3">
-        <v>166.5377473319349</v>
+        <v>163.8504946638699</v>
       </c>
       <c r="P3">
-        <v>499.6132419958047</v>
+        <v>491.5514839916096</v>
       </c>
       <c r="Q3">
-        <v>1121.713241995805</v>
+        <v>1113.65148399161</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06882880972358686</v>
+        <v>0.06900549232082169</v>
       </c>
       <c r="T3">
-        <v>0.4488743650137058</v>
+        <v>0.4523182376929578</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.97323731819066</v>
+        <v>31.48661865909533</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06846893172434326</v>
+        <v>0.06837556719736654</v>
       </c>
       <c r="C4">
-        <v>16968.04496934263</v>
+        <v>16837.78068789748</v>
       </c>
       <c r="D4">
-        <v>14719.52296934263</v>
+        <v>14780.39768789748</v>
       </c>
       <c r="E4">
-        <v>-13070.222</v>
+        <v>-12879.083</v>
       </c>
       <c r="F4">
-        <v>382.278</v>
+        <v>573.417</v>
       </c>
       <c r="G4">
         <v>2630.8</v>
@@ -1621,28 +1621,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M4">
-        <v>21.49802134452021</v>
+        <v>32.24703201678032</v>
       </c>
       <c r="N4">
-        <v>655.4019786554795</v>
+        <v>644.6529679832195</v>
       </c>
       <c r="O4">
-        <v>163.8504946638699</v>
+        <v>161.1632419958049</v>
       </c>
       <c r="P4">
-        <v>491.5514839916096</v>
+        <v>483.4897259874146</v>
       </c>
       <c r="Q4">
-        <v>1113.65148399161</v>
+        <v>1105.589725987415</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06900549232082169</v>
+        <v>0.06918581785820568</v>
       </c>
       <c r="T4">
-        <v>0.4523182376929578</v>
+        <v>0.455833118056318</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.48661865909533</v>
+        <v>20.99107910606356</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06837556719736654</v>
+        <v>0.0682822026703898</v>
       </c>
       <c r="C5">
-        <v>16837.78068789748</v>
+        <v>16708.02200987438</v>
       </c>
       <c r="D5">
-        <v>14780.39768789748</v>
+        <v>14841.77800987438</v>
       </c>
       <c r="E5">
-        <v>-12879.083</v>
+        <v>-12687.944</v>
       </c>
       <c r="F5">
-        <v>573.417</v>
+        <v>764.556</v>
       </c>
       <c r="G5">
         <v>2630.8</v>
@@ -1703,28 +1703,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M5">
-        <v>32.24703201678032</v>
+        <v>42.99604268904042</v>
       </c>
       <c r="N5">
-        <v>644.6529679832195</v>
+        <v>633.9039573109593</v>
       </c>
       <c r="O5">
-        <v>161.1632419958049</v>
+        <v>158.4759893277398</v>
       </c>
       <c r="P5">
-        <v>483.4897259874146</v>
+        <v>475.4279679832194</v>
       </c>
       <c r="Q5">
-        <v>1105.589725987415</v>
+        <v>1097.527967983219</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06918581785820568</v>
+        <v>0.06936990017761852</v>
       </c>
       <c r="T5">
-        <v>0.455833118056318</v>
+        <v>0.459421225093915</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.99107910606356</v>
+        <v>15.74330932954766</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0682822026703898</v>
+        <v>0.06818883814341306</v>
       </c>
       <c r="C6">
-        <v>16708.02200987438</v>
+        <v>16578.77526058027</v>
       </c>
       <c r="D6">
-        <v>14841.77800987438</v>
+        <v>14903.67026058027</v>
       </c>
       <c r="E6">
-        <v>-12687.944</v>
+        <v>-12496.805</v>
       </c>
       <c r="F6">
-        <v>764.556</v>
+        <v>955.6950000000002</v>
       </c>
       <c r="G6">
         <v>2630.8</v>
@@ -1785,28 +1785,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M6">
-        <v>42.99604268904042</v>
+        <v>53.74505336130053</v>
       </c>
       <c r="N6">
-        <v>633.9039573109593</v>
+        <v>623.1549466386992</v>
       </c>
       <c r="O6">
-        <v>158.4759893277398</v>
+        <v>155.7887366596748</v>
       </c>
       <c r="P6">
-        <v>475.4279679832194</v>
+        <v>467.3662099790245</v>
       </c>
       <c r="Q6">
-        <v>1097.527967983219</v>
+        <v>1089.466209979024</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06936990017761852</v>
+        <v>0.06955785791428214</v>
       </c>
       <c r="T6">
-        <v>0.459421225093915</v>
+        <v>0.4630848712270404</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.74330932954766</v>
+        <v>12.59464746363813</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06818883814341306</v>
+        <v>0.06809547361643632</v>
       </c>
       <c r="C7">
-        <v>16578.77526058027</v>
+        <v>16450.04687127349</v>
       </c>
       <c r="D7">
-        <v>14903.67026058027</v>
+        <v>14966.08087127349</v>
       </c>
       <c r="E7">
-        <v>-12496.805</v>
+        <v>-12305.666</v>
       </c>
       <c r="F7">
-        <v>955.6950000000002</v>
+        <v>1146.834</v>
       </c>
       <c r="G7">
         <v>2630.8</v>
@@ -1867,28 +1867,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M7">
-        <v>53.74505336130053</v>
+        <v>64.49406403356065</v>
       </c>
       <c r="N7">
-        <v>623.1549466386992</v>
+        <v>612.4059359664391</v>
       </c>
       <c r="O7">
-        <v>155.7887366596748</v>
+        <v>153.1014839916098</v>
       </c>
       <c r="P7">
-        <v>467.3662099790245</v>
+        <v>459.3044519748293</v>
       </c>
       <c r="Q7">
-        <v>1089.466209979024</v>
+        <v>1081.404451974829</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06955785791428214</v>
+        <v>0.06974981475172583</v>
       </c>
       <c r="T7">
-        <v>0.4630848712270404</v>
+        <v>0.4668264672778917</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.59464746363813</v>
+        <v>10.49553955303177</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06809547361643631</v>
+        <v>0.06800210908945958</v>
       </c>
       <c r="C8">
-        <v>16450.0468712735</v>
+        <v>16321.84338139156</v>
       </c>
       <c r="D8">
-        <v>14966.0808712735</v>
+        <v>15029.01638139156</v>
       </c>
       <c r="E8">
-        <v>-12305.666</v>
+        <v>-12114.527</v>
       </c>
       <c r="F8">
-        <v>1146.834</v>
+        <v>1337.973</v>
       </c>
       <c r="G8">
         <v>2630.8</v>
@@ -1949,28 +1949,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M8">
-        <v>64.49406403356063</v>
+        <v>75.24307470582073</v>
       </c>
       <c r="N8">
-        <v>612.4059359664391</v>
+        <v>601.656925294179</v>
       </c>
       <c r="O8">
-        <v>153.1014839916098</v>
+        <v>150.4142313235448</v>
       </c>
       <c r="P8">
-        <v>459.3044519748293</v>
+        <v>451.2426939706343</v>
       </c>
       <c r="Q8">
-        <v>1081.404451974829</v>
+        <v>1073.342693970634</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06974981475172583</v>
+        <v>0.06994589969320059</v>
       </c>
       <c r="T8">
-        <v>0.4668264672778917</v>
+        <v>0.4706485277599443</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.49553955303178</v>
+        <v>8.996176759741523</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06800210908945957</v>
+        <v>0.06799874456248285</v>
       </c>
       <c r="C9">
-        <v>16321.84338139157</v>
+        <v>16132.98223683093</v>
       </c>
       <c r="D9">
-        <v>15029.01638139157</v>
+        <v>15031.29423683093</v>
       </c>
       <c r="E9">
-        <v>-12114.527</v>
+        <v>-11923.388</v>
       </c>
       <c r="F9">
-        <v>1337.973</v>
+        <v>1529.112</v>
       </c>
       <c r="G9">
         <v>2630.8</v>
@@ -2031,45 +2031,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M9">
-        <v>75.24307470582075</v>
+        <v>88.28575337808084</v>
       </c>
       <c r="N9">
-        <v>601.656925294179</v>
+        <v>588.6142466219189</v>
       </c>
       <c r="O9">
-        <v>150.4142313235448</v>
+        <v>147.1535616554797</v>
       </c>
       <c r="P9">
-        <v>451.2426939706343</v>
+        <v>441.4606849664392</v>
       </c>
       <c r="Q9">
-        <v>1073.342693970634</v>
+        <v>1063.560684966439</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06994589969320059</v>
+        <v>0.07014624735079435</v>
       </c>
       <c r="T9">
-        <v>0.4706485277599443</v>
+        <v>0.4745536765133457</v>
       </c>
       <c r="U9">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.996176759741523</v>
+        <v>7.667148708593987</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06799874456248285</v>
+        <v>0.0679166300355061</v>
       </c>
       <c r="C10">
-        <v>16132.98223683093</v>
+        <v>15997.65136013562</v>
       </c>
       <c r="D10">
-        <v>15031.29423683093</v>
+        <v>15087.10236013562</v>
       </c>
       <c r="E10">
-        <v>-11923.388</v>
+        <v>-11732.249</v>
       </c>
       <c r="F10">
-        <v>1529.112</v>
+        <v>1720.251</v>
       </c>
       <c r="G10">
         <v>2630.8</v>
@@ -2113,28 +2113,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M10">
-        <v>88.28575337808084</v>
+        <v>99.32147255034094</v>
       </c>
       <c r="N10">
-        <v>588.6142466219189</v>
+        <v>577.5785274496588</v>
       </c>
       <c r="O10">
-        <v>147.1535616554797</v>
+        <v>144.3946318624147</v>
       </c>
       <c r="P10">
-        <v>441.4606849664392</v>
+        <v>433.1838955872441</v>
       </c>
       <c r="Q10">
-        <v>1063.560684966439</v>
+        <v>1055.283895587244</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07014624735079435</v>
+        <v>0.07035099825360995</v>
       </c>
       <c r="T10">
-        <v>0.4745536765133457</v>
+        <v>0.4785446527118769</v>
       </c>
       <c r="U10">
         <v>0.05773661666253409</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.667148708593987</v>
+        <v>6.815243296527989</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0679166300355061</v>
+        <v>0.06796201550852937</v>
       </c>
       <c r="C11">
-        <v>15997.65136013562</v>
+        <v>15775.61556390778</v>
       </c>
       <c r="D11">
-        <v>15087.10236013562</v>
+        <v>15056.20556390778</v>
       </c>
       <c r="E11">
-        <v>-11732.249</v>
+        <v>-11541.11</v>
       </c>
       <c r="F11">
-        <v>1720.251</v>
+        <v>1911.39</v>
       </c>
       <c r="G11">
         <v>2630.8</v>
@@ -2195,45 +2195,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M11">
-        <v>99.32147255034094</v>
+        <v>113.606554722601</v>
       </c>
       <c r="N11">
-        <v>577.5785274496588</v>
+        <v>563.2934452773987</v>
       </c>
       <c r="O11">
-        <v>144.3946318624147</v>
+        <v>140.8233613193497</v>
       </c>
       <c r="P11">
-        <v>433.1838955872441</v>
+        <v>422.470083958049</v>
       </c>
       <c r="Q11">
-        <v>1055.283895587244</v>
+        <v>1044.570083958049</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07035099825360995</v>
+        <v>0.07056029917648812</v>
       </c>
       <c r="T11">
-        <v>0.4785446527118769</v>
+        <v>0.4826243172703754</v>
       </c>
       <c r="U11">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.815243296527989</v>
+        <v>5.95828296749973</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06796201550852937</v>
+        <v>0.06795865098155264</v>
       </c>
       <c r="C12">
-        <v>15775.61556390778</v>
+        <v>15586.762669223</v>
       </c>
       <c r="D12">
-        <v>15056.20556390778</v>
+        <v>15058.491669223</v>
       </c>
       <c r="E12">
-        <v>-11541.11</v>
+        <v>-11349.971</v>
       </c>
       <c r="F12">
-        <v>1911.39</v>
+        <v>2102.529</v>
       </c>
       <c r="G12">
         <v>2630.8</v>
@@ -2277,45 +2277,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M12">
-        <v>113.6065547226011</v>
+        <v>126.6492333948612</v>
       </c>
       <c r="N12">
-        <v>563.2934452773986</v>
+        <v>550.2507666051386</v>
       </c>
       <c r="O12">
-        <v>140.8233613193497</v>
+        <v>137.5626916512846</v>
       </c>
       <c r="P12">
-        <v>422.470083958049</v>
+        <v>412.6880749538539</v>
       </c>
       <c r="Q12">
-        <v>1044.570083958049</v>
+        <v>1034.788074953854</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07056029917648812</v>
+        <v>0.07077430349089166</v>
       </c>
       <c r="T12">
-        <v>0.4826243172703754</v>
+        <v>0.4867956596841211</v>
       </c>
       <c r="U12">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.958282967499728</v>
+        <v>5.34468296298006</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06795865098155264</v>
+        <v>0.0678952864545759</v>
       </c>
       <c r="C13">
-        <v>15586.762669223</v>
+        <v>15438.80818296828</v>
       </c>
       <c r="D13">
-        <v>15058.491669223</v>
+        <v>15101.67618296827</v>
       </c>
       <c r="E13">
-        <v>-11349.971</v>
+        <v>-11158.832</v>
       </c>
       <c r="F13">
-        <v>2102.529</v>
+        <v>2293.668</v>
       </c>
       <c r="G13">
         <v>2630.8</v>
@@ -2359,28 +2359,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M13">
-        <v>126.6492333948612</v>
+        <v>138.1628000671213</v>
       </c>
       <c r="N13">
-        <v>550.2507666051386</v>
+        <v>538.7371999328785</v>
       </c>
       <c r="O13">
-        <v>137.5626916512846</v>
+        <v>134.6842999832196</v>
       </c>
       <c r="P13">
-        <v>412.6880749538539</v>
+        <v>404.0528999496589</v>
       </c>
       <c r="Q13">
-        <v>1034.788074953854</v>
+        <v>1026.152899949659</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07077430349089166</v>
+        <v>0.07099317153971345</v>
       </c>
       <c r="T13">
-        <v>0.4867956596841211</v>
+        <v>0.4910618053345428</v>
       </c>
       <c r="U13">
         <v>0.0602366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.34468296298006</v>
+        <v>4.899292716065056</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0678952864545759</v>
+        <v>0.06783192192759915</v>
       </c>
       <c r="C14">
-        <v>15438.80818296828</v>
+        <v>15291.10209685724</v>
       </c>
       <c r="D14">
-        <v>15101.67618296827</v>
+        <v>15145.10909685724</v>
       </c>
       <c r="E14">
-        <v>-11158.832</v>
+        <v>-10967.693</v>
       </c>
       <c r="F14">
-        <v>2293.668</v>
+        <v>2484.807</v>
       </c>
       <c r="G14">
         <v>2630.8</v>
@@ -2441,28 +2441,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M14">
-        <v>138.1628000671213</v>
+        <v>149.6763667393814</v>
       </c>
       <c r="N14">
-        <v>538.7371999328785</v>
+        <v>527.2236332606184</v>
       </c>
       <c r="O14">
-        <v>134.6842999832196</v>
+        <v>131.8059083151546</v>
       </c>
       <c r="P14">
-        <v>404.0528999496589</v>
+        <v>395.4177249454638</v>
       </c>
       <c r="Q14">
-        <v>1026.152899949659</v>
+        <v>1017.517724945464</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07099317153971345</v>
+        <v>0.07121707103793343</v>
       </c>
       <c r="T14">
-        <v>0.4910618053345428</v>
+        <v>0.4954260232987673</v>
       </c>
       <c r="U14">
         <v>0.0602366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.899292716065056</v>
+        <v>4.522424045598513</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06783192192759915</v>
+        <v>0.06787355740062243</v>
       </c>
       <c r="C15">
-        <v>15291.10209685724</v>
+        <v>15071.39616630807</v>
       </c>
       <c r="D15">
-        <v>15145.10909685724</v>
+        <v>15116.54216630807</v>
       </c>
       <c r="E15">
-        <v>-10967.693</v>
+        <v>-10776.554</v>
       </c>
       <c r="F15">
-        <v>2484.807</v>
+        <v>2675.946</v>
       </c>
       <c r="G15">
         <v>2630.8</v>
@@ -2523,45 +2523,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M15">
-        <v>149.6763667393814</v>
+        <v>163.8658794116415</v>
       </c>
       <c r="N15">
-        <v>527.2236332606184</v>
+        <v>513.0341205883583</v>
       </c>
       <c r="O15">
-        <v>131.8059083151546</v>
+        <v>128.2585301470896</v>
       </c>
       <c r="P15">
-        <v>395.4177249454638</v>
+        <v>384.7755904412687</v>
       </c>
       <c r="Q15">
-        <v>1017.517724945464</v>
+        <v>1006.875590441269</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07121707103793343</v>
+        <v>0.07144617750122831</v>
       </c>
       <c r="T15">
-        <v>0.4954260232987673</v>
+        <v>0.4998917347040203</v>
       </c>
       <c r="U15">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.522424045598513</v>
+        <v>4.130817241700354</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06787355740062243</v>
+        <v>0.0678176928736457</v>
       </c>
       <c r="C16">
-        <v>15071.39616630807</v>
+        <v>14918.61170610889</v>
       </c>
       <c r="D16">
-        <v>15116.54216630807</v>
+        <v>15154.8967061089</v>
       </c>
       <c r="E16">
-        <v>-10776.554</v>
+        <v>-10585.415</v>
       </c>
       <c r="F16">
-        <v>2675.946</v>
+        <v>2867.085</v>
       </c>
       <c r="G16">
         <v>2630.8</v>
@@ -2605,28 +2605,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M16">
-        <v>163.8658794116415</v>
+        <v>175.5705850839016</v>
       </c>
       <c r="N16">
-        <v>513.0341205883583</v>
+        <v>501.3294149160981</v>
       </c>
       <c r="O16">
-        <v>128.2585301470896</v>
+        <v>125.3323537290245</v>
       </c>
       <c r="P16">
-        <v>384.7755904412687</v>
+        <v>375.9970611870736</v>
       </c>
       <c r="Q16">
-        <v>1006.875590441269</v>
+        <v>998.0970611870737</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07144617750122831</v>
+        <v>0.07168067470483601</v>
       </c>
       <c r="T16">
-        <v>0.4998917347040203</v>
+        <v>0.5044625216717499</v>
       </c>
       <c r="U16">
         <v>0.0612366166625341</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.130817241700354</v>
+        <v>3.855429425586997</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0678176928736457</v>
+        <v>0.06776182834666895</v>
       </c>
       <c r="C17">
-        <v>14918.6117061089</v>
+        <v>14766.02237157865</v>
       </c>
       <c r="D17">
-        <v>15154.8967061089</v>
+        <v>15193.44637157865</v>
       </c>
       <c r="E17">
-        <v>-10585.415</v>
+        <v>-10394.276</v>
       </c>
       <c r="F17">
-        <v>2867.085</v>
+        <v>3058.224</v>
       </c>
       <c r="G17">
         <v>2630.8</v>
@@ -2687,28 +2687,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M17">
-        <v>175.5705850839016</v>
+        <v>187.2752907561617</v>
       </c>
       <c r="N17">
-        <v>501.3294149160982</v>
+        <v>489.6247092438381</v>
       </c>
       <c r="O17">
-        <v>125.3323537290245</v>
+        <v>122.4061773109595</v>
       </c>
       <c r="P17">
-        <v>375.9970611870737</v>
+        <v>367.2185319328786</v>
       </c>
       <c r="Q17">
-        <v>998.0970611870737</v>
+        <v>989.3185319328786</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07168067470483601</v>
+        <v>0.07192075517519628</v>
       </c>
       <c r="T17">
-        <v>0.5044625216717499</v>
+        <v>0.5091421369006158</v>
       </c>
       <c r="U17">
         <v>0.0612366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.855429425586998</v>
+        <v>3.61446508648781</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06776182834666895</v>
+        <v>0.06770596381969222</v>
       </c>
       <c r="C18">
-        <v>14766.02237157865</v>
+        <v>14613.62965554409</v>
       </c>
       <c r="D18">
-        <v>15193.44637157865</v>
+        <v>15232.19265554409</v>
       </c>
       <c r="E18">
-        <v>-10394.276</v>
+        <v>-10203.137</v>
       </c>
       <c r="F18">
-        <v>3058.224</v>
+        <v>3249.363</v>
       </c>
       <c r="G18">
         <v>2630.8</v>
@@ -2769,28 +2769,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M18">
-        <v>187.2752907561617</v>
+        <v>198.9799964284218</v>
       </c>
       <c r="N18">
-        <v>489.6247092438381</v>
+        <v>477.9200035715779</v>
       </c>
       <c r="O18">
-        <v>122.4061773109595</v>
+        <v>119.4800008928945</v>
       </c>
       <c r="P18">
-        <v>367.2185319328786</v>
+        <v>358.4400026786834</v>
       </c>
       <c r="Q18">
-        <v>989.3185319328786</v>
+        <v>980.5400026786834</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07192075517519628</v>
+        <v>0.07216662071713148</v>
       </c>
       <c r="T18">
-        <v>0.5091421369006158</v>
+        <v>0.5139345139422256</v>
       </c>
       <c r="U18">
         <v>0.0612366166625341</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.61446508648781</v>
+        <v>3.401849493164998</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06770596381969222</v>
+        <v>0.06765009929271548</v>
       </c>
       <c r="C19">
-        <v>14613.62965554409</v>
+        <v>14461.43506609898</v>
       </c>
       <c r="D19">
-        <v>15232.19265554409</v>
+        <v>15271.13706609898</v>
       </c>
       <c r="E19">
-        <v>-10203.137</v>
+        <v>-10011.998</v>
       </c>
       <c r="F19">
-        <v>3249.363</v>
+        <v>3440.502000000001</v>
       </c>
       <c r="G19">
         <v>2630.8</v>
@@ -2851,28 +2851,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M19">
-        <v>198.9799964284218</v>
+        <v>210.6847021006819</v>
       </c>
       <c r="N19">
-        <v>477.9200035715779</v>
+        <v>466.2152978993178</v>
       </c>
       <c r="O19">
-        <v>119.4800008928945</v>
+        <v>116.5538244748295</v>
       </c>
       <c r="P19">
-        <v>358.4400026786834</v>
+        <v>349.6614734244883</v>
       </c>
       <c r="Q19">
-        <v>980.5400026786834</v>
+        <v>971.7614734244884</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07216662071713148</v>
+        <v>0.07241848297960168</v>
       </c>
       <c r="T19">
-        <v>0.5139345139422256</v>
+        <v>0.5188437782287525</v>
       </c>
       <c r="U19">
         <v>0.0612366166625341</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.401849493164998</v>
+        <v>3.212857854655831</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06765009929271548</v>
+        <v>0.06759423476573875</v>
       </c>
       <c r="C20">
-        <v>14461.43506609898</v>
+        <v>14309.44012679964</v>
       </c>
       <c r="D20">
-        <v>15271.13706609898</v>
+        <v>15310.28112679963</v>
       </c>
       <c r="E20">
-        <v>-10011.998</v>
+        <v>-9820.859</v>
       </c>
       <c r="F20">
-        <v>3440.502</v>
+        <v>3631.641000000001</v>
       </c>
       <c r="G20">
         <v>2630.8</v>
@@ -2933,28 +2933,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M20">
-        <v>210.6847021006819</v>
+        <v>222.389407772942</v>
       </c>
       <c r="N20">
-        <v>466.2152978993179</v>
+        <v>454.5105922270577</v>
       </c>
       <c r="O20">
-        <v>116.5538244748295</v>
+        <v>113.6276480567644</v>
       </c>
       <c r="P20">
-        <v>349.6614734244884</v>
+        <v>340.8829441702933</v>
       </c>
       <c r="Q20">
-        <v>971.7614734244885</v>
+        <v>962.9829441702933</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07241848297960168</v>
+        <v>0.07267656406336746</v>
       </c>
       <c r="T20">
-        <v>0.5188437782287525</v>
+        <v>0.5238742589174161</v>
       </c>
       <c r="U20">
         <v>0.0612366166625341</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.212857854655832</v>
+        <v>3.04376007283184</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06759423476573875</v>
+        <v>0.06791337023876201</v>
       </c>
       <c r="C21">
-        <v>14309.44012679964</v>
+        <v>13897.34639413045</v>
       </c>
       <c r="D21">
-        <v>15310.28112679963</v>
+        <v>15089.32639413045</v>
       </c>
       <c r="E21">
-        <v>-9820.859</v>
+        <v>-9629.719999999999</v>
       </c>
       <c r="F21">
-        <v>3631.641000000001</v>
+        <v>3822.780000000001</v>
       </c>
       <c r="G21">
         <v>2630.8</v>
@@ -3015,45 +3015,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M21">
-        <v>222.389407772942</v>
+        <v>243.6510634452021</v>
       </c>
       <c r="N21">
-        <v>454.5105922270577</v>
+        <v>433.2489365547976</v>
       </c>
       <c r="O21">
-        <v>113.6276480567644</v>
+        <v>108.3122341386994</v>
       </c>
       <c r="P21">
-        <v>340.8829441702933</v>
+        <v>324.9367024160982</v>
       </c>
       <c r="Q21">
-        <v>962.9829441702933</v>
+        <v>947.0367024160983</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07267656406336746</v>
+        <v>0.07294109717422737</v>
       </c>
       <c r="T21">
-        <v>0.5238742589174161</v>
+        <v>0.5290305016232961</v>
       </c>
       <c r="U21">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.04376007283184</v>
+        <v>2.778153275543723</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06791337023876201</v>
+        <v>0.06787625571178528</v>
       </c>
       <c r="C22">
-        <v>13897.34639413045</v>
+        <v>13731.57551899851</v>
       </c>
       <c r="D22">
-        <v>15089.32639413045</v>
+        <v>15114.69451899851</v>
       </c>
       <c r="E22">
-        <v>-9629.719999999999</v>
+        <v>-9438.580999999998</v>
       </c>
       <c r="F22">
-        <v>3822.780000000001</v>
+        <v>4013.919000000001</v>
       </c>
       <c r="G22">
         <v>2630.8</v>
@@ -3097,28 +3097,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M22">
-        <v>243.6510634452021</v>
+        <v>255.8336166174622</v>
       </c>
       <c r="N22">
-        <v>433.2489365547976</v>
+        <v>421.0663833825375</v>
       </c>
       <c r="O22">
-        <v>108.3122341386994</v>
+        <v>105.2665958456344</v>
       </c>
       <c r="P22">
-        <v>324.9367024160982</v>
+        <v>315.7997875369032</v>
       </c>
       <c r="Q22">
-        <v>947.0367024160983</v>
+        <v>937.8997875369032</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07294109717422737</v>
+        <v>0.07321232732586855</v>
       </c>
       <c r="T22">
-        <v>0.5290305016232961</v>
+        <v>0.5343172821191985</v>
       </c>
       <c r="U22">
         <v>0.06373661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.778153275543723</v>
+        <v>2.645860262422593</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06787625571178527</v>
+        <v>0.06783914118480854</v>
       </c>
       <c r="C23">
-        <v>13731.57551899852</v>
+        <v>13565.89008512282</v>
       </c>
       <c r="D23">
-        <v>15114.69451899852</v>
+        <v>15140.14808512282</v>
       </c>
       <c r="E23">
-        <v>-9438.581</v>
+        <v>-9247.441999999999</v>
       </c>
       <c r="F23">
-        <v>4013.919</v>
+        <v>4205.058</v>
       </c>
       <c r="G23">
         <v>2630.8</v>
@@ -3179,28 +3179,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M23">
-        <v>255.8336166174622</v>
+        <v>268.0161697897223</v>
       </c>
       <c r="N23">
-        <v>421.0663833825375</v>
+        <v>408.8838302102774</v>
       </c>
       <c r="O23">
-        <v>105.2665958456344</v>
+        <v>102.2209575525694</v>
       </c>
       <c r="P23">
-        <v>315.7997875369032</v>
+        <v>306.6628726577081</v>
       </c>
       <c r="Q23">
-        <v>937.8997875369032</v>
+        <v>928.7628726577082</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07321232732586855</v>
+        <v>0.07349051209678258</v>
       </c>
       <c r="T23">
-        <v>0.5343172821191985</v>
+        <v>0.5397396210893547</v>
       </c>
       <c r="U23">
         <v>0.06373661666253409</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.645860262422594</v>
+        <v>2.52559388685793</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06783914118480854</v>
+        <v>0.0684057766578318</v>
       </c>
       <c r="C24">
-        <v>13565.89008512282</v>
+        <v>12995.24875252397</v>
       </c>
       <c r="D24">
-        <v>15140.14808512282</v>
+        <v>14760.64575252397</v>
       </c>
       <c r="E24">
-        <v>-9247.441999999999</v>
+        <v>-9056.303</v>
       </c>
       <c r="F24">
-        <v>4205.058</v>
+        <v>4396.197</v>
       </c>
       <c r="G24">
         <v>2630.8</v>
@@ -3261,45 +3261,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M24">
-        <v>268.0161697897223</v>
+        <v>295.5854124619824</v>
       </c>
       <c r="N24">
-        <v>408.8838302102774</v>
+        <v>381.3145875380173</v>
       </c>
       <c r="O24">
-        <v>102.2209575525694</v>
+        <v>95.32864688450434</v>
       </c>
       <c r="P24">
-        <v>306.6628726577081</v>
+        <v>285.985940653513</v>
       </c>
       <c r="Q24">
-        <v>928.7628726577082</v>
+        <v>908.085940653513</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07349051209678258</v>
+        <v>0.07377592244616191</v>
       </c>
       <c r="T24">
-        <v>0.5397396210893547</v>
+        <v>0.5453028000327618</v>
       </c>
       <c r="U24">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.52559388685793</v>
+        <v>2.290031819777511</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0684057766578318</v>
+        <v>0.06889891213085507</v>
       </c>
       <c r="C25">
-        <v>12995.24875252397</v>
+        <v>12488.98677252974</v>
       </c>
       <c r="D25">
-        <v>14760.64575252397</v>
+        <v>14445.52277252974</v>
       </c>
       <c r="E25">
-        <v>-9056.303</v>
+        <v>-8865.163999999999</v>
       </c>
       <c r="F25">
-        <v>4396.197</v>
+        <v>4587.336000000001</v>
       </c>
       <c r="G25">
         <v>2630.8</v>
@@ -3343,45 +3343,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M25">
-        <v>295.5854124619824</v>
+        <v>321.2814929342426</v>
       </c>
       <c r="N25">
-        <v>381.3145875380173</v>
+        <v>355.6185070657572</v>
       </c>
       <c r="O25">
-        <v>95.32864688450434</v>
+        <v>88.90462676643929</v>
       </c>
       <c r="P25">
-        <v>285.985940653513</v>
+        <v>266.7138802993179</v>
       </c>
       <c r="Q25">
-        <v>908.085940653513</v>
+        <v>888.8138802993179</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07377592244616191</v>
+        <v>0.07406884359420912</v>
       </c>
       <c r="T25">
-        <v>0.5453028000327618</v>
+        <v>0.5510123784220481</v>
       </c>
       <c r="U25">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.290031819777511</v>
+        <v>2.106875169864025</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06889891213085507</v>
+        <v>0.06890904760387834</v>
       </c>
       <c r="C26">
-        <v>12488.98677252974</v>
+        <v>12291.51206329249</v>
       </c>
       <c r="D26">
-        <v>14445.52277252974</v>
+        <v>14439.18706329249</v>
       </c>
       <c r="E26">
-        <v>-8865.164000000001</v>
+        <v>-8674.025</v>
       </c>
       <c r="F26">
-        <v>4587.336</v>
+        <v>4778.475</v>
       </c>
       <c r="G26">
         <v>2630.8</v>
@@ -3425,28 +3425,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M26">
-        <v>321.2814929342425</v>
+        <v>334.6682218065026</v>
       </c>
       <c r="N26">
-        <v>355.6185070657572</v>
+        <v>342.2317781934971</v>
       </c>
       <c r="O26">
-        <v>88.90462676643931</v>
+        <v>85.55794454837428</v>
       </c>
       <c r="P26">
-        <v>266.7138802993179</v>
+        <v>256.6738336451228</v>
       </c>
       <c r="Q26">
-        <v>888.8138802993179</v>
+        <v>878.7738336451229</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07406884359420912</v>
+        <v>0.07436957597287092</v>
       </c>
       <c r="T26">
-        <v>0.5510123784220481</v>
+        <v>0.5568742122350485</v>
       </c>
       <c r="U26">
         <v>0.07003661666253409</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.106875169864025</v>
+        <v>2.022600163069464</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06890904760387834</v>
+        <v>0.07120068307690161</v>
       </c>
       <c r="C27">
-        <v>12291.51206329249</v>
+        <v>10797.67765247694</v>
       </c>
       <c r="D27">
-        <v>14439.18706329249</v>
+        <v>13136.49165247695</v>
       </c>
       <c r="E27">
-        <v>-8674.025</v>
+        <v>-8482.885999999999</v>
       </c>
       <c r="F27">
-        <v>4778.475</v>
+        <v>4969.614</v>
       </c>
       <c r="G27">
         <v>2630.8</v>
@@ -3507,45 +3507,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M27">
-        <v>334.6682218065026</v>
+        <v>406.1994344787628</v>
       </c>
       <c r="N27">
-        <v>342.2317781934971</v>
+        <v>270.700565521237</v>
       </c>
       <c r="O27">
-        <v>85.55794454837428</v>
+        <v>67.67514138030924</v>
       </c>
       <c r="P27">
-        <v>256.6738336451228</v>
+        <v>203.0254241409277</v>
       </c>
       <c r="Q27">
-        <v>878.7738336451229</v>
+        <v>825.1254241409277</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07436957597287092</v>
+        <v>0.07467843625365872</v>
       </c>
       <c r="T27">
-        <v>0.5568742122350485</v>
+        <v>0.562894473988941</v>
       </c>
       <c r="U27">
-        <v>0.07003661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05252746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.022600163069464</v>
+        <v>1.666422802554123</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07120068307690161</v>
+        <v>0.07129856854992486</v>
       </c>
       <c r="C28">
-        <v>10797.67765247694</v>
+        <v>10556.10948047261</v>
       </c>
       <c r="D28">
-        <v>13136.49165247695</v>
+        <v>13086.0624804726</v>
       </c>
       <c r="E28">
-        <v>-8482.885999999999</v>
+        <v>-8291.746999999999</v>
       </c>
       <c r="F28">
-        <v>4969.614</v>
+        <v>5160.753000000001</v>
       </c>
       <c r="G28">
         <v>2630.8</v>
@@ -3589,28 +3589,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M28">
-        <v>406.1994344787628</v>
+        <v>421.8224896510229</v>
       </c>
       <c r="N28">
-        <v>270.700565521237</v>
+        <v>255.0775103489769</v>
       </c>
       <c r="O28">
-        <v>67.67514138030924</v>
+        <v>63.76937758724422</v>
       </c>
       <c r="P28">
-        <v>203.0254241409277</v>
+        <v>191.3081327617327</v>
       </c>
       <c r="Q28">
-        <v>825.1254241409277</v>
+        <v>813.4081327617328</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07467843625365872</v>
+        <v>0.07499575845994755</v>
       </c>
       <c r="T28">
-        <v>0.562894473988941</v>
+        <v>0.5690796744210223</v>
       </c>
       <c r="U28">
         <v>0.0817366166625341</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.666422802554123</v>
+        <v>1.604703439496563</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07129856854992486</v>
+        <v>0.07139645402294813</v>
       </c>
       <c r="C29">
-        <v>10556.10948047261</v>
+        <v>10314.92700903064</v>
       </c>
       <c r="D29">
-        <v>13086.0624804726</v>
+        <v>13036.01900903064</v>
       </c>
       <c r="E29">
-        <v>-8291.746999999999</v>
+        <v>-8100.607999999999</v>
       </c>
       <c r="F29">
-        <v>5160.753000000001</v>
+        <v>5351.892000000001</v>
       </c>
       <c r="G29">
         <v>2630.8</v>
@@ -3671,28 +3671,28 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M29">
-        <v>421.8224896510229</v>
+        <v>437.445544823283</v>
       </c>
       <c r="N29">
-        <v>255.0775103489769</v>
+        <v>239.4544551767167</v>
       </c>
       <c r="O29">
-        <v>63.76937758724422</v>
+        <v>59.86361379417919</v>
       </c>
       <c r="P29">
-        <v>191.3081327617327</v>
+        <v>179.5908413825376</v>
       </c>
       <c r="Q29">
-        <v>813.4081327617328</v>
+        <v>801.6908413825377</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07499575845994755</v>
+        <v>0.07532189517196662</v>
       </c>
       <c r="T29">
-        <v>0.5690796744210223</v>
+        <v>0.5754366859762169</v>
       </c>
       <c r="U29">
         <v>0.0817366166625341</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.604703439496563</v>
+        <v>1.547392602371686</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07139645402294813</v>
+        <v>0.07458283949597139</v>
       </c>
       <c r="C30">
-        <v>10314.92700903064</v>
+        <v>8680.644027275668</v>
       </c>
       <c r="D30">
-        <v>13036.01900903064</v>
+        <v>11592.87502727567</v>
       </c>
       <c r="E30">
-        <v>-8100.607999999999</v>
+        <v>-7909.468999999999</v>
       </c>
       <c r="F30">
-        <v>5351.892000000001</v>
+        <v>5543.031000000001</v>
       </c>
       <c r="G30">
         <v>2630.8</v>
@@ -3753,45 +3753,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M30">
-        <v>437.445544823283</v>
+        <v>531.7796401955432</v>
       </c>
       <c r="N30">
-        <v>239.4544551767167</v>
+        <v>145.1203598044566</v>
       </c>
       <c r="O30">
-        <v>59.86361379417919</v>
+        <v>36.28008995111415</v>
       </c>
       <c r="P30">
-        <v>179.5908413825376</v>
+        <v>108.8402698533424</v>
       </c>
       <c r="Q30">
-        <v>801.6908413825377</v>
+        <v>730.9402698533424</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07532189517196662</v>
+        <v>0.07565721883362003</v>
       </c>
       <c r="T30">
-        <v>0.5754366859762169</v>
+        <v>0.5819727682794451</v>
       </c>
       <c r="U30">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.547392602371686</v>
+        <v>1.272895667369089</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07458283949597139</v>
+        <v>0.08179829628306119</v>
       </c>
       <c r="C31">
-        <v>8680.64402727567</v>
+        <v>6165.842592262035</v>
       </c>
       <c r="D31">
-        <v>11592.87502727567</v>
+        <v>9269.212592262036</v>
       </c>
       <c r="E31">
-        <v>-7909.469</v>
+        <v>-7718.33</v>
       </c>
       <c r="F31">
-        <v>5543.031</v>
+        <v>5734.17</v>
       </c>
       <c r="G31">
         <v>2630.8</v>
@@ -3835,45 +3835,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M31">
-        <v>531.779640195543</v>
+        <v>714.1141311678032</v>
       </c>
       <c r="N31">
-        <v>145.1203598044567</v>
+        <v>-37.21413116780343</v>
       </c>
       <c r="O31">
-        <v>36.28008995111418</v>
+        <v>-9.303532791950857</v>
       </c>
       <c r="P31">
-        <v>108.8402698533425</v>
+        <v>-27.91059837585257</v>
       </c>
       <c r="Q31">
-        <v>730.9402698533426</v>
+        <v>594.1894016241474</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07565721883362003</v>
+        <v>0.07612973685993665</v>
       </c>
       <c r="T31">
-        <v>0.5819727682794451</v>
+        <v>0.5911830241096959</v>
       </c>
       <c r="U31">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V31">
-        <v>0.25</v>
+        <v>0.2369719245343365</v>
       </c>
       <c r="W31">
-        <v>0.07195246249690057</v>
+        <v>0.09502493493701848</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.272895667369089</v>
+        <v>0.9478876981373461</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08179829628306119</v>
+        <v>0.08258566244968653</v>
       </c>
       <c r="C32">
-        <v>6165.842592262035</v>
+        <v>5776.303892477187</v>
       </c>
       <c r="D32">
-        <v>9269.212592262036</v>
+        <v>9070.812892477188</v>
       </c>
       <c r="E32">
-        <v>-7718.33</v>
+        <v>-7527.191</v>
       </c>
       <c r="F32">
-        <v>5734.17</v>
+        <v>5925.309</v>
       </c>
       <c r="G32">
         <v>2630.8</v>
@@ -3917,37 +3917,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M32">
-        <v>714.1141311678032</v>
+        <v>737.9179355400632</v>
       </c>
       <c r="N32">
-        <v>-37.21413116780343</v>
+        <v>-61.01793554006349</v>
       </c>
       <c r="O32">
-        <v>-9.303532791950857</v>
+        <v>-15.25448388501587</v>
       </c>
       <c r="P32">
-        <v>-27.91059837585257</v>
+        <v>-45.76345165504762</v>
       </c>
       <c r="Q32">
-        <v>594.1894016241474</v>
+        <v>576.3365483449525</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07612973685993665</v>
+        <v>0.07656929826370384</v>
       </c>
       <c r="T32">
-        <v>0.5911830241096959</v>
+        <v>0.5997508940243291</v>
       </c>
       <c r="U32">
         <v>0.1245366166625341</v>
       </c>
       <c r="V32">
-        <v>0.2369719245343365</v>
+        <v>0.2293276689041966</v>
       </c>
       <c r="W32">
-        <v>0.09502493493701848</v>
+        <v>0.09597692467009962</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9478876981373461</v>
+        <v>0.9173106756167866</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08258566244968653</v>
+        <v>0.08337302861631186</v>
       </c>
       <c r="C33">
-        <v>5776.303892477187</v>
+        <v>5395.080370724667</v>
       </c>
       <c r="D33">
-        <v>9070.812892477188</v>
+        <v>8880.728370724666</v>
       </c>
       <c r="E33">
-        <v>-7527.191</v>
+        <v>-7336.052</v>
       </c>
       <c r="F33">
-        <v>5925.309</v>
+        <v>6116.448</v>
       </c>
       <c r="G33">
         <v>2630.8</v>
@@ -3999,37 +3999,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M33">
-        <v>737.9179355400632</v>
+        <v>761.7217399123234</v>
       </c>
       <c r="N33">
-        <v>-61.01793554006349</v>
+        <v>-84.82173991232366</v>
       </c>
       <c r="O33">
-        <v>-15.25448388501587</v>
+        <v>-21.20543497808092</v>
       </c>
       <c r="P33">
-        <v>-45.76345165504762</v>
+        <v>-63.61630493424275</v>
       </c>
       <c r="Q33">
-        <v>576.3365483449525</v>
+        <v>558.4836950657573</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07656929826370384</v>
+        <v>0.07702178794405243</v>
       </c>
       <c r="T33">
-        <v>0.5997508940243291</v>
+        <v>0.6085707601129222</v>
       </c>
       <c r="U33">
         <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.2293276689041966</v>
+        <v>0.2221611792509405</v>
       </c>
       <c r="W33">
-        <v>0.09597692467009962</v>
+        <v>0.0968694150448632</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9173106756167866</v>
+        <v>0.8886447170037619</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08337302861631186</v>
+        <v>0.08416039478293721</v>
       </c>
       <c r="C34">
-        <v>5395.080370724667</v>
+        <v>5021.660007520116</v>
       </c>
       <c r="D34">
-        <v>8880.728370724666</v>
+        <v>8698.447007520117</v>
       </c>
       <c r="E34">
-        <v>-7336.052</v>
+        <v>-7144.913</v>
       </c>
       <c r="F34">
-        <v>6116.448</v>
+        <v>6307.587</v>
       </c>
       <c r="G34">
         <v>2630.8</v>
@@ -4081,37 +4081,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M34">
-        <v>761.7217399123234</v>
+        <v>785.5255442845835</v>
       </c>
       <c r="N34">
-        <v>-84.82173991232366</v>
+        <v>-108.6255442845837</v>
       </c>
       <c r="O34">
-        <v>-21.20543497808092</v>
+        <v>-27.15638607114593</v>
       </c>
       <c r="P34">
-        <v>-63.61630493424275</v>
+        <v>-81.46915821343779</v>
       </c>
       <c r="Q34">
-        <v>558.4836950657573</v>
+        <v>540.6308417865622</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07702178794405243</v>
+        <v>0.07748778477903828</v>
       </c>
       <c r="T34">
-        <v>0.6085707601129222</v>
+        <v>0.6176539057862495</v>
       </c>
       <c r="U34">
         <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.2221611792509405</v>
+        <v>0.2154290223039423</v>
       </c>
       <c r="W34">
-        <v>0.0968694150448632</v>
+        <v>0.09770781509388353</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8886447170037619</v>
+        <v>0.8617160892157691</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08416039478293721</v>
+        <v>0.08494776094956256</v>
       </c>
       <c r="C35">
-        <v>5021.660007520116</v>
+        <v>4655.571975703739</v>
       </c>
       <c r="D35">
-        <v>8698.447007520117</v>
+        <v>8523.49797570374</v>
       </c>
       <c r="E35">
-        <v>-7144.913</v>
+        <v>-6953.773999999999</v>
       </c>
       <c r="F35">
-        <v>6307.587</v>
+        <v>6498.726000000001</v>
       </c>
       <c r="G35">
         <v>2630.8</v>
@@ -4163,37 +4163,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M35">
-        <v>785.5255442845835</v>
+        <v>809.3293486568436</v>
       </c>
       <c r="N35">
-        <v>-108.6255442845837</v>
+        <v>-132.4293486568439</v>
       </c>
       <c r="O35">
-        <v>-27.15638607114593</v>
+        <v>-33.10733716421097</v>
       </c>
       <c r="P35">
-        <v>-81.46915821343779</v>
+        <v>-99.32201149263292</v>
       </c>
       <c r="Q35">
-        <v>540.6308417865622</v>
+        <v>522.7779885073671</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07748778477903828</v>
+        <v>0.07796790273023585</v>
       </c>
       <c r="T35">
-        <v>0.6176539057862495</v>
+        <v>0.6270122982981624</v>
       </c>
       <c r="U35">
         <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.2154290223039423</v>
+        <v>0.2090928745891204</v>
       </c>
       <c r="W35">
-        <v>0.09770781509388353</v>
+        <v>0.09849689749296149</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8617160892157691</v>
+        <v>0.8363714983564817</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08494776094956256</v>
+        <v>0.08573512711618791</v>
       </c>
       <c r="C36">
-        <v>4655.571975703739</v>
+        <v>4296.382579674116</v>
       </c>
       <c r="D36">
-        <v>8523.49797570374</v>
+        <v>8355.447579674115</v>
       </c>
       <c r="E36">
-        <v>-6953.773999999999</v>
+        <v>-6762.634999999999</v>
       </c>
       <c r="F36">
-        <v>6498.726000000001</v>
+        <v>6689.865000000001</v>
       </c>
       <c r="G36">
         <v>2630.8</v>
@@ -4245,37 +4245,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M36">
-        <v>809.3293486568436</v>
+        <v>833.1331530291038</v>
       </c>
       <c r="N36">
-        <v>-132.4293486568439</v>
+        <v>-156.2331530291041</v>
       </c>
       <c r="O36">
-        <v>-33.10733716421097</v>
+        <v>-39.05828825727602</v>
       </c>
       <c r="P36">
-        <v>-99.32201149263292</v>
+        <v>-117.1748647718281</v>
       </c>
       <c r="Q36">
-        <v>522.7779885073671</v>
+        <v>504.9251352281719</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07796790273023585</v>
+        <v>0.07846279354147025</v>
       </c>
       <c r="T36">
-        <v>0.6270122982981624</v>
+        <v>0.6366586413489034</v>
       </c>
       <c r="U36">
         <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.2090928745891204</v>
+        <v>0.2031187924580027</v>
       </c>
       <c r="W36">
-        <v>0.09849689749296149</v>
+        <v>0.099240889469235</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8363714983564817</v>
+        <v>0.8124751698320107</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08573512711618791</v>
+        <v>0.1167605436013848</v>
       </c>
       <c r="C37">
-        <v>4296.382579674116</v>
+        <v>452.0691827045721</v>
       </c>
       <c r="D37">
-        <v>8355.447579674115</v>
+        <v>4702.273182704574</v>
       </c>
       <c r="E37">
-        <v>-6762.634999999999</v>
+        <v>-6571.495999999998</v>
       </c>
       <c r="F37">
-        <v>6689.865000000001</v>
+        <v>6881.004000000002</v>
       </c>
       <c r="G37">
         <v>2630.8</v>
@@ -4327,45 +4327,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M37">
-        <v>833.1331530291038</v>
+        <v>1422.555486201364</v>
       </c>
       <c r="N37">
-        <v>-156.2331530291041</v>
+        <v>-745.6554862013644</v>
       </c>
       <c r="O37">
-        <v>-39.05828825727602</v>
+        <v>-186.4138715503411</v>
       </c>
       <c r="P37">
-        <v>-117.1748647718281</v>
+        <v>-559.2416146510233</v>
       </c>
       <c r="Q37">
-        <v>504.9251352281719</v>
+        <v>62.85838534897675</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07846279354147025</v>
+        <v>0.07998260331332377</v>
       </c>
       <c r="T37">
-        <v>0.6366586413489034</v>
+        <v>0.6662825626227695</v>
       </c>
       <c r="U37">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V37">
-        <v>0.2031187924580027</v>
+        <v>0.1189584530385383</v>
       </c>
       <c r="W37">
-        <v>0.099240889469235</v>
+        <v>0.1821435485579377</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8124751698320107</v>
+        <v>0.475833812154153</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1167605436013848</v>
+        <v>0.1183699097680101</v>
       </c>
       <c r="C38">
-        <v>452.0691827045739</v>
+        <v>156.6489538775522</v>
       </c>
       <c r="D38">
-        <v>4702.273182704574</v>
+        <v>4597.991953877552</v>
       </c>
       <c r="E38">
-        <v>-6571.496</v>
+        <v>-6380.357</v>
       </c>
       <c r="F38">
-        <v>6881.004</v>
+        <v>7072.143</v>
       </c>
       <c r="G38">
         <v>2630.8</v>
@@ -4409,37 +4409,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M38">
-        <v>1422.555486201364</v>
+        <v>1462.070916373624</v>
       </c>
       <c r="N38">
-        <v>-745.6554862013639</v>
+        <v>-785.1709163736242</v>
       </c>
       <c r="O38">
-        <v>-186.413871550341</v>
+        <v>-196.2927290934061</v>
       </c>
       <c r="P38">
-        <v>-559.2416146510229</v>
+        <v>-588.8781872802182</v>
       </c>
       <c r="Q38">
-        <v>62.85838534897709</v>
+        <v>33.22181271978184</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07998260331332377</v>
+        <v>0.08052518431829717</v>
       </c>
       <c r="T38">
-        <v>0.6662825626227695</v>
+        <v>0.6768584763151944</v>
       </c>
       <c r="U38">
         <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.1189584530385383</v>
+        <v>0.1157433597131724</v>
       </c>
       <c r="W38">
-        <v>0.1821435485579377</v>
+        <v>0.1828082260742782</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4758338121541532</v>
+        <v>0.4629734388526895</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1183699097680101</v>
+        <v>0.1199792759346355</v>
       </c>
       <c r="C39">
-        <v>156.6489538775522</v>
+        <v>-134.2463809174506</v>
       </c>
       <c r="D39">
-        <v>4597.991953877552</v>
+        <v>4498.23561908255</v>
       </c>
       <c r="E39">
-        <v>-6380.357</v>
+        <v>-6189.217999999999</v>
       </c>
       <c r="F39">
-        <v>7072.143</v>
+        <v>7263.282000000001</v>
       </c>
       <c r="G39">
         <v>2630.8</v>
@@ -4491,37 +4491,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M39">
-        <v>1462.070916373624</v>
+        <v>1501.586346545884</v>
       </c>
       <c r="N39">
-        <v>-785.1709163736242</v>
+        <v>-824.6863465458845</v>
       </c>
       <c r="O39">
-        <v>-196.2927290934061</v>
+        <v>-206.1715866364711</v>
       </c>
       <c r="P39">
-        <v>-588.8781872802182</v>
+        <v>-618.5147599094133</v>
       </c>
       <c r="Q39">
-        <v>33.22181271978184</v>
+        <v>3.585240090586694</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08052518431829717</v>
+        <v>0.08108526793633422</v>
       </c>
       <c r="T39">
-        <v>0.6768584763151944</v>
+        <v>0.6877755485138266</v>
       </c>
       <c r="U39">
         <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1157433597131724</v>
+        <v>0.1126974818259836</v>
       </c>
       <c r="W39">
-        <v>0.1828082260742782</v>
+        <v>0.1834379205634428</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4629734388526895</v>
+        <v>0.4507899273039345</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1199792759346355</v>
+        <v>0.1215886421012608</v>
       </c>
       <c r="C40">
-        <v>-134.2463809174506</v>
+        <v>-420.9050790430319</v>
       </c>
       <c r="D40">
-        <v>4498.23561908255</v>
+        <v>4402.715920956969</v>
       </c>
       <c r="E40">
-        <v>-6189.217999999999</v>
+        <v>-5998.078999999999</v>
       </c>
       <c r="F40">
-        <v>7263.282000000001</v>
+        <v>7454.421000000001</v>
       </c>
       <c r="G40">
         <v>2630.8</v>
@@ -4573,37 +4573,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M40">
-        <v>1501.586346545884</v>
+        <v>1541.101776718144</v>
       </c>
       <c r="N40">
-        <v>-824.6863465458845</v>
+        <v>-864.2017767181445</v>
       </c>
       <c r="O40">
-        <v>-206.1715866364711</v>
+        <v>-216.0504441795361</v>
       </c>
       <c r="P40">
-        <v>-618.5147599094133</v>
+        <v>-648.1513325386084</v>
       </c>
       <c r="Q40">
-        <v>3.585240090586694</v>
+        <v>-26.05133253860834</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08108526793633422</v>
+        <v>0.08166371495168395</v>
       </c>
       <c r="T40">
-        <v>0.6877755485138266</v>
+        <v>0.6990505575058564</v>
       </c>
       <c r="U40">
         <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.1126974818259836</v>
+        <v>0.1098078028048046</v>
       </c>
       <c r="W40">
-        <v>0.1834379205634428</v>
+        <v>0.1840353230275221</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4507899273039345</v>
+        <v>0.4392312112192183</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1215886421012608</v>
+        <v>0.1231980082678862</v>
       </c>
       <c r="C41">
-        <v>-420.9050790430319</v>
+        <v>-703.5914224827593</v>
       </c>
       <c r="D41">
-        <v>4402.715920956969</v>
+        <v>4311.168577517242</v>
       </c>
       <c r="E41">
-        <v>-5998.078999999999</v>
+        <v>-5806.939999999999</v>
       </c>
       <c r="F41">
-        <v>7454.421000000001</v>
+        <v>7645.560000000001</v>
       </c>
       <c r="G41">
         <v>2630.8</v>
@@ -4655,37 +4655,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M41">
-        <v>1541.101776718144</v>
+        <v>1580.617206890405</v>
       </c>
       <c r="N41">
-        <v>-864.2017767181445</v>
+        <v>-903.7172068904048</v>
       </c>
       <c r="O41">
-        <v>-216.0504441795361</v>
+        <v>-225.9293017226012</v>
       </c>
       <c r="P41">
-        <v>-648.1513325386084</v>
+        <v>-677.7879051678036</v>
       </c>
       <c r="Q41">
-        <v>-26.05133253860834</v>
+        <v>-55.68790516780359</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08166371495168395</v>
+        <v>0.08226144353421203</v>
       </c>
       <c r="T41">
-        <v>0.6990505575058564</v>
+        <v>0.7107014001309542</v>
       </c>
       <c r="U41">
         <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1098078028048046</v>
+        <v>0.1070626077346844</v>
       </c>
       <c r="W41">
-        <v>0.1840353230275221</v>
+        <v>0.1846028553683974</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4392312112192183</v>
+        <v>0.4282504309387377</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1231980082678862</v>
+        <v>0.1248073744345115</v>
       </c>
       <c r="C42">
-        <v>-703.5914224827593</v>
+        <v>-982.5481597121588</v>
       </c>
       <c r="D42">
-        <v>4311.168577517242</v>
+        <v>4223.350840287842</v>
       </c>
       <c r="E42">
-        <v>-5806.939999999999</v>
+        <v>-5615.800999999999</v>
       </c>
       <c r="F42">
-        <v>7645.560000000001</v>
+        <v>7836.699000000001</v>
       </c>
       <c r="G42">
         <v>2630.8</v>
@@ -4737,37 +4737,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M42">
-        <v>1580.617206890405</v>
+        <v>1620.132637062665</v>
       </c>
       <c r="N42">
-        <v>-903.7172068904048</v>
+        <v>-943.2326370626648</v>
       </c>
       <c r="O42">
-        <v>-225.9293017226012</v>
+        <v>-235.8081592656662</v>
       </c>
       <c r="P42">
-        <v>-677.7879051678036</v>
+        <v>-707.4244777969986</v>
       </c>
       <c r="Q42">
-        <v>-55.68790516780359</v>
+        <v>-85.32447779699862</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08226144353421203</v>
+        <v>0.0828794341025885</v>
       </c>
       <c r="T42">
-        <v>0.7107014001309542</v>
+        <v>0.7227471865738516</v>
       </c>
       <c r="U42">
         <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.1070626077346844</v>
+        <v>0.1044513246192043</v>
       </c>
       <c r="W42">
-        <v>0.1846028553683974</v>
+        <v>0.1851427032048397</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4282504309387377</v>
+        <v>0.4178052984768174</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1248073744345115</v>
+        <v>0.1264167406011369</v>
       </c>
       <c r="C43">
-        <v>-982.5481597121588</v>
+        <v>-1257.998655084773</v>
       </c>
       <c r="D43">
-        <v>4223.350840287842</v>
+        <v>4139.039344915228</v>
       </c>
       <c r="E43">
-        <v>-5615.800999999999</v>
+        <v>-5424.661999999998</v>
       </c>
       <c r="F43">
-        <v>7836.699000000001</v>
+        <v>8027.838000000002</v>
       </c>
       <c r="G43">
         <v>2630.8</v>
@@ -4819,37 +4819,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M43">
-        <v>1620.132637062665</v>
+        <v>1659.648067234925</v>
       </c>
       <c r="N43">
-        <v>-943.2326370626648</v>
+        <v>-982.7480672349249</v>
       </c>
       <c r="O43">
-        <v>-235.8081592656662</v>
+        <v>-245.6870168087312</v>
       </c>
       <c r="P43">
-        <v>-707.4244777969986</v>
+        <v>-737.0610504261937</v>
       </c>
       <c r="Q43">
-        <v>-85.32447779699862</v>
+        <v>-114.9610504261937</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0828794341025885</v>
+        <v>0.08351873469056417</v>
       </c>
       <c r="T43">
-        <v>0.7227471865738516</v>
+        <v>0.7352083449630561</v>
       </c>
       <c r="U43">
         <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1044513246192043</v>
+        <v>0.1019643883187471</v>
       </c>
       <c r="W43">
-        <v>0.1851427032048397</v>
+        <v>0.1856568440014515</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4178052984768174</v>
+        <v>0.4078575532749884</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1264167406011368</v>
+        <v>0.1280261067677622</v>
       </c>
       <c r="C44">
-        <v>-1257.998655084771</v>
+        <v>-1530.148785805717</v>
       </c>
       <c r="D44">
-        <v>4139.03934491523</v>
+        <v>4058.028214194283</v>
       </c>
       <c r="E44">
-        <v>-5424.661999999999</v>
+        <v>-5233.522999999999</v>
       </c>
       <c r="F44">
-        <v>8027.838000000001</v>
+        <v>8218.977000000001</v>
       </c>
       <c r="G44">
         <v>2630.8</v>
@@ -4901,37 +4901,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M44">
-        <v>1659.648067234925</v>
+        <v>1699.163497407185</v>
       </c>
       <c r="N44">
-        <v>-982.7480672349249</v>
+        <v>-1022.263497407185</v>
       </c>
       <c r="O44">
-        <v>-245.6870168087312</v>
+        <v>-255.5658743517962</v>
       </c>
       <c r="P44">
-        <v>-737.0610504261937</v>
+        <v>-766.6976230553887</v>
       </c>
       <c r="Q44">
-        <v>-114.9610504261937</v>
+        <v>-144.5976230553887</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08351873469056416</v>
+        <v>0.08418046687811792</v>
       </c>
       <c r="T44">
-        <v>0.7352083449630559</v>
+        <v>0.7481067369799517</v>
       </c>
       <c r="U44">
         <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1019643883187471</v>
+        <v>0.09959312347412508</v>
       </c>
       <c r="W44">
-        <v>0.1856568440014515</v>
+        <v>0.1861470712726395</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4078575532749884</v>
+        <v>0.3983724938965003</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1280261067677622</v>
+        <v>0.1296354729343875</v>
       </c>
       <c r="C45">
-        <v>-1530.148785805717</v>
+        <v>-1799.188620411216</v>
       </c>
       <c r="D45">
-        <v>4058.028214194283</v>
+        <v>3980.127379588784</v>
       </c>
       <c r="E45">
-        <v>-5233.522999999999</v>
+        <v>-5042.384</v>
       </c>
       <c r="F45">
-        <v>8218.977000000001</v>
+        <v>8410.116</v>
       </c>
       <c r="G45">
         <v>2630.8</v>
@@ -4983,37 +4983,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M45">
-        <v>1699.163497407185</v>
+        <v>1738.678927579445</v>
       </c>
       <c r="N45">
-        <v>-1022.263497407185</v>
+        <v>-1061.778927579445</v>
       </c>
       <c r="O45">
-        <v>-255.5658743517962</v>
+        <v>-265.4447318948612</v>
       </c>
       <c r="P45">
-        <v>-766.6976230553887</v>
+        <v>-796.3341956845836</v>
       </c>
       <c r="Q45">
-        <v>-144.5976230553887</v>
+        <v>-174.2341956845836</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08418046687811792</v>
+        <v>0.08486583235808431</v>
       </c>
       <c r="T45">
-        <v>0.7481067369799517</v>
+        <v>0.7614657858545937</v>
       </c>
       <c r="U45">
         <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.09959312347412508</v>
+        <v>0.09732964339516768</v>
       </c>
       <c r="W45">
-        <v>0.1861470712726395</v>
+        <v>0.1866150154860462</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3983724938965003</v>
+        <v>0.3893185735806708</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1296354729343875</v>
+        <v>0.1312448391010129</v>
       </c>
       <c r="C46">
-        <v>-1799.188620411216</v>
+        <v>-2065.29390756165</v>
       </c>
       <c r="D46">
-        <v>3980.127379588784</v>
+        <v>3905.16109243835</v>
       </c>
       <c r="E46">
-        <v>-5042.384</v>
+        <v>-4851.244999999999</v>
       </c>
       <c r="F46">
-        <v>8410.116</v>
+        <v>8601.255000000001</v>
       </c>
       <c r="G46">
         <v>2630.8</v>
@@ -5065,37 +5065,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M46">
-        <v>1738.678927579445</v>
+        <v>1778.194357751705</v>
       </c>
       <c r="N46">
-        <v>-1061.778927579445</v>
+        <v>-1101.294357751705</v>
       </c>
       <c r="O46">
-        <v>-265.4447318948612</v>
+        <v>-275.3235894379263</v>
       </c>
       <c r="P46">
-        <v>-796.3341956845836</v>
+        <v>-825.970768313779</v>
       </c>
       <c r="Q46">
-        <v>-174.2341956845836</v>
+        <v>-203.870768313779</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08486583235808431</v>
+        <v>0.08557612021914038</v>
       </c>
       <c r="T46">
-        <v>0.7614657858545937</v>
+        <v>0.7753106183246771</v>
       </c>
       <c r="U46">
         <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.09732964339516768</v>
+        <v>0.09516676243083062</v>
       </c>
       <c r="W46">
-        <v>0.1866150154860462</v>
+        <v>0.187062162178857</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3893185735806708</v>
+        <v>0.3806670497233224</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1312448391010129</v>
+        <v>0.1328542052676382</v>
       </c>
       <c r="C47">
-        <v>-2065.29390756165</v>
+        <v>-2328.627399695259</v>
       </c>
       <c r="D47">
-        <v>3905.16109243835</v>
+        <v>3832.966600304742</v>
       </c>
       <c r="E47">
-        <v>-4851.244999999999</v>
+        <v>-4660.106</v>
       </c>
       <c r="F47">
-        <v>8601.255000000001</v>
+        <v>8792.394</v>
       </c>
       <c r="G47">
         <v>2630.8</v>
@@ -5147,37 +5147,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M47">
-        <v>1778.194357751705</v>
+        <v>1817.709787923965</v>
       </c>
       <c r="N47">
-        <v>-1101.294357751705</v>
+        <v>-1140.809787923965</v>
       </c>
       <c r="O47">
-        <v>-275.3235894379263</v>
+        <v>-285.2024469809912</v>
       </c>
       <c r="P47">
-        <v>-825.970768313779</v>
+        <v>-855.6073409429737</v>
       </c>
       <c r="Q47">
-        <v>-203.870768313779</v>
+        <v>-233.5073409429737</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08557612021914038</v>
+        <v>0.08631271503801335</v>
       </c>
       <c r="T47">
-        <v>0.7753106183246771</v>
+        <v>0.7896682223677267</v>
       </c>
       <c r="U47">
         <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.09516676243083062</v>
+        <v>0.09309791976929084</v>
       </c>
       <c r="W47">
-        <v>0.187062162178857</v>
+        <v>0.1874898677111109</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3806670497233224</v>
+        <v>0.3723916790771634</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1328542052676382</v>
+        <v>0.1344635714342635</v>
       </c>
       <c r="C48">
-        <v>-2328.627399695259</v>
+        <v>-2589.340032524937</v>
       </c>
       <c r="D48">
-        <v>3832.966600304742</v>
+        <v>3763.392967475065</v>
       </c>
       <c r="E48">
-        <v>-4660.106</v>
+        <v>-4468.966999999999</v>
       </c>
       <c r="F48">
-        <v>8792.394</v>
+        <v>8983.533000000001</v>
       </c>
       <c r="G48">
         <v>2630.8</v>
@@ -5229,37 +5229,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M48">
-        <v>1817.709787923965</v>
+        <v>1857.225218096225</v>
       </c>
       <c r="N48">
-        <v>-1140.809787923965</v>
+        <v>-1180.325218096225</v>
       </c>
       <c r="O48">
-        <v>-285.2024469809912</v>
+        <v>-295.0813045240563</v>
       </c>
       <c r="P48">
-        <v>-855.6073409429737</v>
+        <v>-885.243913572169</v>
       </c>
       <c r="Q48">
-        <v>-233.5073409429737</v>
+        <v>-263.143913572169</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08631271503801335</v>
+        <v>0.08707710588778719</v>
       </c>
       <c r="T48">
-        <v>0.7896682223677267</v>
+        <v>0.8045676227897594</v>
       </c>
       <c r="U48">
         <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.09309791976929084</v>
+        <v>0.09111711296568889</v>
       </c>
       <c r="W48">
-        <v>0.1874898677111109</v>
+        <v>0.1878993730079496</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3723916790771634</v>
+        <v>0.3644684518627556</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1344635714342635</v>
+        <v>0.1360729376008889</v>
       </c>
       <c r="C49">
-        <v>-2589.340032524937</v>
+        <v>-2847.571978368217</v>
       </c>
       <c r="D49">
-        <v>3763.392967475065</v>
+        <v>3696.300021631785</v>
       </c>
       <c r="E49">
-        <v>-4468.966999999999</v>
+        <v>-4277.827999999998</v>
       </c>
       <c r="F49">
-        <v>8983.533000000001</v>
+        <v>9174.672000000002</v>
       </c>
       <c r="G49">
         <v>2630.8</v>
@@ -5311,37 +5311,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M49">
-        <v>1857.225218096225</v>
+        <v>1896.740648268486</v>
       </c>
       <c r="N49">
-        <v>-1180.325218096225</v>
+        <v>-1219.840648268486</v>
       </c>
       <c r="O49">
-        <v>-295.0813045240563</v>
+        <v>-304.9601620671215</v>
       </c>
       <c r="P49">
-        <v>-885.243913572169</v>
+        <v>-914.8804862013644</v>
       </c>
       <c r="Q49">
-        <v>-263.143913572169</v>
+        <v>-292.7804862013644</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08707710588778719</v>
+        <v>0.08787089638562925</v>
       </c>
       <c r="T49">
-        <v>0.8045676227897594</v>
+        <v>0.8200400770741778</v>
       </c>
       <c r="U49">
         <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.09111711296568889</v>
+        <v>0.0892188397789037</v>
       </c>
       <c r="W49">
-        <v>0.1878993730079496</v>
+        <v>0.1882918155840868</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3644684518627556</v>
+        <v>0.3568753591156147</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1360729376008889</v>
+        <v>0.1376823037675142</v>
       </c>
       <c r="C50">
-        <v>-2847.571978368215</v>
+        <v>-3103.453588779492</v>
       </c>
       <c r="D50">
-        <v>3696.300021631785</v>
+        <v>3631.557411220508</v>
       </c>
       <c r="E50">
-        <v>-4277.828</v>
+        <v>-4086.689</v>
       </c>
       <c r="F50">
-        <v>9174.672</v>
+        <v>9365.811</v>
       </c>
       <c r="G50">
         <v>2630.8</v>
@@ -5393,37 +5393,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M50">
-        <v>1896.740648268485</v>
+        <v>1936.256078440745</v>
       </c>
       <c r="N50">
-        <v>-1219.840648268485</v>
+        <v>-1259.356078440745</v>
       </c>
       <c r="O50">
-        <v>-304.9601620671214</v>
+        <v>-314.8390196101864</v>
       </c>
       <c r="P50">
-        <v>-914.8804862013641</v>
+        <v>-944.5170588305591</v>
       </c>
       <c r="Q50">
-        <v>-292.7804862013641</v>
+        <v>-322.4170588305591</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08787089638562925</v>
+        <v>0.08869581592260239</v>
       </c>
       <c r="T50">
-        <v>0.8200400770741777</v>
+        <v>0.8361192942717107</v>
       </c>
       <c r="U50">
         <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.08921883977890371</v>
+        <v>0.08739804713035466</v>
       </c>
       <c r="W50">
-        <v>0.1882918155840868</v>
+        <v>0.1886682400958919</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3568753591156149</v>
+        <v>0.3495921885214186</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1376823037675142</v>
+        <v>0.1392916699341396</v>
       </c>
       <c r="C51">
-        <v>-3103.453588779492</v>
+        <v>-3357.106239823406</v>
       </c>
       <c r="D51">
-        <v>3631.557411220508</v>
+        <v>3569.043760176594</v>
       </c>
       <c r="E51">
-        <v>-4086.689</v>
+        <v>-3895.549999999999</v>
       </c>
       <c r="F51">
-        <v>9365.811</v>
+        <v>9556.950000000001</v>
       </c>
       <c r="G51">
         <v>2630.8</v>
@@ -5475,37 +5475,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M51">
-        <v>1936.256078440745</v>
+        <v>1975.771508613005</v>
       </c>
       <c r="N51">
-        <v>-1259.356078440745</v>
+        <v>-1298.871508613006</v>
       </c>
       <c r="O51">
-        <v>-314.8390196101864</v>
+        <v>-324.7178771532514</v>
       </c>
       <c r="P51">
-        <v>-944.5170588305591</v>
+        <v>-974.1536314597541</v>
       </c>
       <c r="Q51">
-        <v>-322.4170588305591</v>
+        <v>-352.0536314597541</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08869581592260239</v>
+        <v>0.08955373224105442</v>
       </c>
       <c r="T51">
-        <v>0.8361192942717107</v>
+        <v>0.8528416801571449</v>
       </c>
       <c r="U51">
         <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.08739804713035466</v>
+        <v>0.08565008618774757</v>
       </c>
       <c r="W51">
-        <v>0.1886682400958919</v>
+        <v>0.1890296076272247</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3495921885214186</v>
+        <v>0.3426003447509903</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1392916699341396</v>
+        <v>0.1409010361007649</v>
       </c>
       <c r="C52">
-        <v>-3357.106239823406</v>
+        <v>-3608.64309152239</v>
       </c>
       <c r="D52">
-        <v>3569.043760176594</v>
+        <v>3508.645908477611</v>
       </c>
       <c r="E52">
-        <v>-3895.549999999999</v>
+        <v>-3704.410999999998</v>
       </c>
       <c r="F52">
-        <v>9556.950000000001</v>
+        <v>9748.089000000002</v>
       </c>
       <c r="G52">
         <v>2630.8</v>
@@ -5557,37 +5557,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M52">
-        <v>1975.771508613005</v>
+        <v>2015.286938785266</v>
       </c>
       <c r="N52">
-        <v>-1298.871508613006</v>
+        <v>-1338.386938785266</v>
       </c>
       <c r="O52">
-        <v>-324.7178771532514</v>
+        <v>-334.5967346963165</v>
       </c>
       <c r="P52">
-        <v>-974.1536314597541</v>
+        <v>-1003.79020408895</v>
       </c>
       <c r="Q52">
-        <v>-352.0536314597541</v>
+        <v>-381.6902040889495</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08955373224105442</v>
+        <v>0.09044666555209635</v>
       </c>
       <c r="T52">
-        <v>0.8528416801571449</v>
+        <v>0.8702466124052499</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.08565008618774757</v>
+        <v>0.08397067273308584</v>
       </c>
       <c r="W52">
-        <v>0.1890296076272247</v>
+        <v>0.189376803882819</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3426003447509903</v>
+        <v>0.3358826909323434</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1409010361007649</v>
+        <v>0.1425104022673903</v>
       </c>
       <c r="C53">
-        <v>-3608.64309152239</v>
+        <v>-3858.16977147599</v>
       </c>
       <c r="D53">
-        <v>3508.645908477611</v>
+        <v>3450.258228524011</v>
       </c>
       <c r="E53">
-        <v>-3704.410999999998</v>
+        <v>-3513.271999999999</v>
       </c>
       <c r="F53">
-        <v>9748.089000000002</v>
+        <v>9939.228000000001</v>
       </c>
       <c r="G53">
         <v>2630.8</v>
@@ -5639,37 +5639,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M53">
-        <v>2015.286938785266</v>
+        <v>2054.802368957526</v>
       </c>
       <c r="N53">
-        <v>-1338.386938785266</v>
+        <v>-1377.902368957526</v>
       </c>
       <c r="O53">
-        <v>-334.5967346963165</v>
+        <v>-344.4755922393815</v>
       </c>
       <c r="P53">
-        <v>-1003.79020408895</v>
+        <v>-1033.426776718145</v>
       </c>
       <c r="Q53">
-        <v>-381.6902040889495</v>
+        <v>-411.3267767181445</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09044666555209635</v>
+        <v>0.09137680441776505</v>
       </c>
       <c r="T53">
-        <v>0.8702466124052499</v>
+        <v>0.8883767501636928</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.08397067273308584</v>
+        <v>0.08235585210360342</v>
       </c>
       <c r="W53">
-        <v>0.189376803882819</v>
+        <v>0.1897106464362751</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3358826909323434</v>
+        <v>0.3294234084144136</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1425104022673903</v>
+        <v>0.1441197684340156</v>
       </c>
       <c r="C54">
-        <v>-3858.16977147599</v>
+        <v>-4105.784991340502</v>
       </c>
       <c r="D54">
-        <v>3450.258228524011</v>
+        <v>3393.7820086595</v>
       </c>
       <c r="E54">
-        <v>-3513.271999999999</v>
+        <v>-3322.132999999998</v>
       </c>
       <c r="F54">
-        <v>9939.228000000001</v>
+        <v>10130.367</v>
       </c>
       <c r="G54">
         <v>2630.8</v>
@@ -5721,37 +5721,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M54">
-        <v>2054.802368957526</v>
+        <v>2094.317799129786</v>
       </c>
       <c r="N54">
-        <v>-1377.902368957526</v>
+        <v>-1417.417799129786</v>
       </c>
       <c r="O54">
-        <v>-344.4755922393815</v>
+        <v>-354.3544497824465</v>
       </c>
       <c r="P54">
-        <v>-1033.426776718145</v>
+        <v>-1063.06334934734</v>
       </c>
       <c r="Q54">
-        <v>-411.3267767181445</v>
+        <v>-440.9633493473397</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09137680441776505</v>
+        <v>0.09234652366069621</v>
       </c>
       <c r="T54">
-        <v>0.8883767501636928</v>
+        <v>0.9072783831458988</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.08235585210360342</v>
+        <v>0.08080196810164865</v>
       </c>
       <c r="W54">
-        <v>0.1897106464362751</v>
+        <v>0.1900318911575253</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3294234084144136</v>
+        <v>0.3232078724065945</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1441197684340156</v>
+        <v>0.1457291346006409</v>
       </c>
       <c r="C55">
-        <v>-4105.784991340502</v>
+        <v>-4351.581103737863</v>
       </c>
       <c r="D55">
-        <v>3393.7820086595</v>
+        <v>3339.124896262138</v>
       </c>
       <c r="E55">
-        <v>-3322.132999999998</v>
+        <v>-3130.993999999999</v>
       </c>
       <c r="F55">
-        <v>10130.367</v>
+        <v>10321.506</v>
       </c>
       <c r="G55">
         <v>2630.8</v>
@@ -5803,37 +5803,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M55">
-        <v>2094.317799129786</v>
+        <v>2133.833229302046</v>
       </c>
       <c r="N55">
-        <v>-1417.417799129786</v>
+        <v>-1456.933229302046</v>
       </c>
       <c r="O55">
-        <v>-354.3544497824465</v>
+        <v>-364.2333073255115</v>
       </c>
       <c r="P55">
-        <v>-1063.06334934734</v>
+        <v>-1092.699921976535</v>
       </c>
       <c r="Q55">
-        <v>-440.9633493473397</v>
+        <v>-470.5999219765346</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09234652366069621</v>
+        <v>0.09335840460984177</v>
       </c>
       <c r="T55">
-        <v>0.9072783831458988</v>
+        <v>0.9270018262577662</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.08080196810164865</v>
+        <v>0.07930563535902552</v>
       </c>
       <c r="W55">
-        <v>0.1900318911575253</v>
+        <v>0.1903412379261365</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3232078724065945</v>
+        <v>0.3172225414361021</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1457291346006409</v>
+        <v>0.1473385007672663</v>
       </c>
       <c r="C56">
-        <v>-4351.581103737863</v>
+        <v>-4595.64460620317</v>
       </c>
       <c r="D56">
-        <v>3339.124896262138</v>
+        <v>3286.200393796832</v>
       </c>
       <c r="E56">
-        <v>-3130.993999999999</v>
+        <v>-2939.854999999998</v>
       </c>
       <c r="F56">
-        <v>10321.506</v>
+        <v>10512.645</v>
       </c>
       <c r="G56">
         <v>2630.8</v>
@@ -5885,37 +5885,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M56">
-        <v>2133.833229302046</v>
+        <v>2173.348659474306</v>
       </c>
       <c r="N56">
-        <v>-1456.933229302046</v>
+        <v>-1496.448659474307</v>
       </c>
       <c r="O56">
-        <v>-364.2333073255115</v>
+        <v>-374.1121648685767</v>
       </c>
       <c r="P56">
-        <v>-1092.699921976535</v>
+        <v>-1122.33649460573</v>
       </c>
       <c r="Q56">
-        <v>-470.5999219765346</v>
+        <v>-500.2364946057299</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09335840460984177</v>
+        <v>0.09441525804561604</v>
       </c>
       <c r="T56">
-        <v>0.9270018262577662</v>
+        <v>0.9476018668412723</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.07930563535902552</v>
+        <v>0.07786371471613414</v>
       </c>
       <c r="W56">
-        <v>0.1903412379261365</v>
+        <v>0.1906393357213438</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3172225414361021</v>
+        <v>0.3114548588645365</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1473385007672663</v>
+        <v>0.1489478669338916</v>
       </c>
       <c r="C57">
-        <v>-4595.64460620317</v>
+        <v>-4838.056597955068</v>
       </c>
       <c r="D57">
-        <v>3286.200393796832</v>
+        <v>3234.927402044933</v>
       </c>
       <c r="E57">
-        <v>-2939.854999999998</v>
+        <v>-2748.715999999999</v>
       </c>
       <c r="F57">
-        <v>10512.645</v>
+        <v>10703.784</v>
       </c>
       <c r="G57">
         <v>2630.8</v>
@@ -5967,37 +5967,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M57">
-        <v>2173.348659474306</v>
+        <v>2212.864089646566</v>
       </c>
       <c r="N57">
-        <v>-1496.448659474307</v>
+        <v>-1535.964089646567</v>
       </c>
       <c r="O57">
-        <v>-374.1121648685767</v>
+        <v>-383.9910224116417</v>
       </c>
       <c r="P57">
-        <v>-1122.33649460573</v>
+        <v>-1151.973067234925</v>
       </c>
       <c r="Q57">
-        <v>-500.2364946057299</v>
+        <v>-529.8730672349251</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09441525804561604</v>
+        <v>0.09552015027392549</v>
       </c>
       <c r="T57">
-        <v>0.9476018668412723</v>
+        <v>0.9691382729058464</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.07786371471613414</v>
+        <v>0.07647329123906031</v>
       </c>
       <c r="W57">
-        <v>0.1906393357213438</v>
+        <v>0.1909267871667222</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3114548588645365</v>
+        <v>0.3058931649562412</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1489478669338916</v>
+        <v>0.150557233100517</v>
       </c>
       <c r="C58">
-        <v>-4838.056597955068</v>
+        <v>-5078.893194562503</v>
       </c>
       <c r="D58">
-        <v>3234.927402044933</v>
+        <v>3185.229805437499</v>
       </c>
       <c r="E58">
-        <v>-2748.715999999999</v>
+        <v>-2557.576999999997</v>
       </c>
       <c r="F58">
-        <v>10703.784</v>
+        <v>10894.923</v>
       </c>
       <c r="G58">
         <v>2630.8</v>
@@ -6049,37 +6049,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M58">
-        <v>2212.864089646566</v>
+        <v>2252.379519818826</v>
       </c>
       <c r="N58">
-        <v>-1535.964089646567</v>
+        <v>-1575.479519818827</v>
       </c>
       <c r="O58">
-        <v>-383.9910224116417</v>
+        <v>-393.8698799547067</v>
       </c>
       <c r="P58">
-        <v>-1151.973067234925</v>
+        <v>-1181.60963986412</v>
       </c>
       <c r="Q58">
-        <v>-529.8730672349251</v>
+        <v>-559.50963986412</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09552015027392549</v>
+        <v>0.0966764328384354</v>
       </c>
       <c r="T58">
-        <v>0.9691382729058464</v>
+        <v>0.9916763722757501</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.07647329123906031</v>
+        <v>0.07513165455065575</v>
       </c>
       <c r="W58">
-        <v>0.1909267871667222</v>
+        <v>0.1912041525964732</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3058931649562412</v>
+        <v>0.3005266182026229</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.150557233100517</v>
+        <v>0.1521665992671423</v>
       </c>
       <c r="C59">
-        <v>-5078.893194562503</v>
+        <v>-5318.225904967056</v>
       </c>
       <c r="D59">
-        <v>3185.229805437499</v>
+        <v>3137.036095032946</v>
       </c>
       <c r="E59">
-        <v>-2557.576999999997</v>
+        <v>-2366.437999999998</v>
       </c>
       <c r="F59">
-        <v>10894.923</v>
+        <v>11086.062</v>
       </c>
       <c r="G59">
         <v>2630.8</v>
@@ -6131,37 +6131,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M59">
-        <v>2252.379519818826</v>
+        <v>2291.894949991086</v>
       </c>
       <c r="N59">
-        <v>-1575.479519818827</v>
+        <v>-1614.994949991087</v>
       </c>
       <c r="O59">
-        <v>-393.8698799547067</v>
+        <v>-403.7487374977717</v>
       </c>
       <c r="P59">
-        <v>-1181.60963986412</v>
+        <v>-1211.246212493315</v>
       </c>
       <c r="Q59">
-        <v>-559.50963986412</v>
+        <v>-589.1462124933149</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.0966764328384354</v>
+        <v>0.09788777647744576</v>
       </c>
       <c r="T59">
-        <v>0.9916763722757501</v>
+        <v>1.015287714472792</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.07513165455065575</v>
+        <v>0.07383628119633411</v>
       </c>
       <c r="W59">
-        <v>0.1912041525964732</v>
+        <v>0.1914719537010605</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3005266182026229</v>
+        <v>0.2953451247853364</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1521665992671423</v>
+        <v>0.1537759654337676</v>
       </c>
       <c r="C60">
-        <v>-5318.225904967054</v>
+        <v>-5556.121974788535</v>
       </c>
       <c r="D60">
-        <v>3137.036095032946</v>
+        <v>3090.279025211466</v>
       </c>
       <c r="E60">
-        <v>-2366.438</v>
+        <v>-2175.298999999999</v>
       </c>
       <c r="F60">
-        <v>11086.062</v>
+        <v>11277.201</v>
       </c>
       <c r="G60">
         <v>2630.8</v>
@@ -6213,37 +6213,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M60">
-        <v>2291.894949991086</v>
+        <v>2331.410380163346</v>
       </c>
       <c r="N60">
-        <v>-1614.994949991086</v>
+        <v>-1654.510380163347</v>
       </c>
       <c r="O60">
-        <v>-403.7487374977716</v>
+        <v>-413.6275950408367</v>
       </c>
       <c r="P60">
-        <v>-1211.246212493315</v>
+        <v>-1240.88278512251</v>
       </c>
       <c r="Q60">
-        <v>-589.1462124933147</v>
+        <v>-618.7827851225101</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09788777647744576</v>
+        <v>0.09915821005006636</v>
       </c>
       <c r="T60">
-        <v>1.015287714472792</v>
+        <v>1.040050829459933</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.07383628119633412</v>
+        <v>0.0725848188031759</v>
       </c>
       <c r="W60">
-        <v>0.1914719537010605</v>
+        <v>0.1917306768021024</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2953451247853364</v>
+        <v>0.2903392752127035</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1537759654337676</v>
+        <v>0.155385331600393</v>
       </c>
       <c r="C61">
-        <v>-5556.121974788535</v>
+        <v>-5792.644699379915</v>
       </c>
       <c r="D61">
-        <v>3090.279025211466</v>
+        <v>3044.895300620086</v>
       </c>
       <c r="E61">
-        <v>-2175.298999999999</v>
+        <v>-1984.16</v>
       </c>
       <c r="F61">
-        <v>11277.201</v>
+        <v>11468.34</v>
       </c>
       <c r="G61">
         <v>2630.8</v>
@@ -6295,37 +6295,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M61">
-        <v>2331.410380163346</v>
+        <v>2370.925810335606</v>
       </c>
       <c r="N61">
-        <v>-1654.510380163347</v>
+        <v>-1694.025810335607</v>
       </c>
       <c r="O61">
-        <v>-413.6275950408367</v>
+        <v>-423.5064525839017</v>
       </c>
       <c r="P61">
-        <v>-1240.88278512251</v>
+        <v>-1270.519357751705</v>
       </c>
       <c r="Q61">
-        <v>-618.7827851225101</v>
+        <v>-648.4193577517052</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09915821005006636</v>
+        <v>0.100492165301318</v>
       </c>
       <c r="T61">
-        <v>1.040050829459933</v>
+        <v>1.066052100196431</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.0725848188031759</v>
+        <v>0.07137507182312297</v>
       </c>
       <c r="W61">
-        <v>0.1917306768021024</v>
+        <v>0.1919807757997763</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2903392752127035</v>
+        <v>0.2855002872924919</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.155385331600393</v>
+        <v>0.1569946977670183</v>
       </c>
       <c r="C62">
-        <v>-5792.644699379915</v>
+        <v>-6027.853709696432</v>
       </c>
       <c r="D62">
-        <v>3044.895300620086</v>
+        <v>3000.82529030357</v>
       </c>
       <c r="E62">
-        <v>-1984.16</v>
+        <v>-1793.020999999999</v>
       </c>
       <c r="F62">
-        <v>11468.34</v>
+        <v>11659.479</v>
       </c>
       <c r="G62">
         <v>2630.8</v>
@@ -6377,37 +6377,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M62">
-        <v>2370.925810335606</v>
+        <v>2410.441240507866</v>
       </c>
       <c r="N62">
-        <v>-1694.025810335607</v>
+        <v>-1733.541240507867</v>
       </c>
       <c r="O62">
-        <v>-423.5064525839017</v>
+        <v>-433.3853101269667</v>
       </c>
       <c r="P62">
-        <v>-1270.519357751705</v>
+        <v>-1300.1559303809</v>
       </c>
       <c r="Q62">
-        <v>-648.4193577517052</v>
+        <v>-678.0559303809001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.100492165301318</v>
+        <v>0.1018945285141724</v>
       </c>
       <c r="T62">
-        <v>1.066052100196431</v>
+        <v>1.093386769432237</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.07137507182312297</v>
+        <v>0.07020498867848161</v>
       </c>
       <c r="W62">
-        <v>0.1919807757997763</v>
+        <v>0.1922226748303133</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2855002872924919</v>
+        <v>0.2808199547139264</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1569946977670183</v>
+        <v>0.1586040639336437</v>
       </c>
       <c r="C63">
-        <v>-6027.853709696432</v>
+        <v>-6261.805233693875</v>
       </c>
       <c r="D63">
-        <v>3000.82529030357</v>
+        <v>2958.012766306125</v>
       </c>
       <c r="E63">
-        <v>-1793.020999999999</v>
+        <v>-1601.882</v>
       </c>
       <c r="F63">
-        <v>11659.479</v>
+        <v>11850.618</v>
       </c>
       <c r="G63">
         <v>2630.8</v>
@@ -6459,37 +6459,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M63">
-        <v>2410.441240507866</v>
+        <v>2449.956670680127</v>
       </c>
       <c r="N63">
-        <v>-1733.541240507867</v>
+        <v>-1773.056670680127</v>
       </c>
       <c r="O63">
-        <v>-433.3853101269667</v>
+        <v>-443.2641676700317</v>
       </c>
       <c r="P63">
-        <v>-1300.1559303809</v>
+        <v>-1329.792503010095</v>
       </c>
       <c r="Q63">
-        <v>-678.0559303809001</v>
+        <v>-707.692503010095</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1018945285141724</v>
+        <v>0.1033707003171769</v>
       </c>
       <c r="T63">
-        <v>1.093386769432237</v>
+        <v>1.122160105469928</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.07020498867848161</v>
+        <v>0.06907265015140933</v>
       </c>
       <c r="W63">
-        <v>0.1922226748303133</v>
+        <v>0.1924567706663169</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2808199547139264</v>
+        <v>0.2762906006056373</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1586040639336437</v>
+        <v>0.160213430100269</v>
       </c>
       <c r="C64">
-        <v>-6261.805233693875</v>
+        <v>-6494.552335665532</v>
       </c>
       <c r="D64">
-        <v>2958.012766306125</v>
+        <v>2916.404664334469</v>
       </c>
       <c r="E64">
-        <v>-1601.882</v>
+        <v>-1410.742999999999</v>
       </c>
       <c r="F64">
-        <v>11850.618</v>
+        <v>12041.757</v>
       </c>
       <c r="G64">
         <v>2630.8</v>
@@ -6541,37 +6541,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M64">
-        <v>2449.956670680127</v>
+        <v>2489.472100852387</v>
       </c>
       <c r="N64">
-        <v>-1773.056670680127</v>
+        <v>-1812.572100852387</v>
       </c>
       <c r="O64">
-        <v>-443.2641676700317</v>
+        <v>-453.1430252130968</v>
       </c>
       <c r="P64">
-        <v>-1329.792503010095</v>
+        <v>-1359.429075639291</v>
       </c>
       <c r="Q64">
-        <v>-707.692503010095</v>
+        <v>-737.3290756392906</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1033707003171769</v>
+        <v>0.1049266651906141</v>
       </c>
       <c r="T64">
-        <v>1.122160105469928</v>
+        <v>1.152488756969115</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.06907265015140933</v>
+        <v>0.06797625887916472</v>
       </c>
       <c r="W64">
-        <v>0.1924567706663169</v>
+        <v>0.1926834348884791</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2762906006056373</v>
+        <v>0.2719050355166589</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.160213430100269</v>
+        <v>0.1618227962668943</v>
       </c>
       <c r="C65">
-        <v>-6494.552335665532</v>
+        <v>-6726.145135659897</v>
       </c>
       <c r="D65">
-        <v>2916.404664334469</v>
+        <v>2875.950864340103</v>
       </c>
       <c r="E65">
-        <v>-1410.742999999999</v>
+        <v>-1219.603999999999</v>
       </c>
       <c r="F65">
-        <v>12041.757</v>
+        <v>12232.896</v>
       </c>
       <c r="G65">
         <v>2630.8</v>
@@ -6623,37 +6623,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M65">
-        <v>2489.472100852387</v>
+        <v>2528.987531024647</v>
       </c>
       <c r="N65">
-        <v>-1812.572100852387</v>
+        <v>-1852.087531024647</v>
       </c>
       <c r="O65">
-        <v>-453.1430252130968</v>
+        <v>-463.0218827561617</v>
       </c>
       <c r="P65">
-        <v>-1359.429075639291</v>
+        <v>-1389.065648268485</v>
       </c>
       <c r="Q65">
-        <v>-737.3290756392906</v>
+        <v>-766.9656482684853</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1049266651906141</v>
+        <v>0.10656907255702</v>
       </c>
       <c r="T65">
-        <v>1.152488756969115</v>
+        <v>1.18450233355159</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.06797625887916472</v>
+        <v>0.06691412983417779</v>
       </c>
       <c r="W65">
-        <v>0.1926834348884791</v>
+        <v>0.1929030158536987</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2719050355166589</v>
+        <v>0.2676565193367111</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1618227962668943</v>
+        <v>0.1634321624335197</v>
       </c>
       <c r="C66">
-        <v>-6726.145135659897</v>
+        <v>-6956.631010886831</v>
       </c>
       <c r="D66">
-        <v>2875.950864340103</v>
+        <v>2836.60398911317</v>
       </c>
       <c r="E66">
-        <v>-1219.603999999999</v>
+        <v>-1028.464999999998</v>
       </c>
       <c r="F66">
-        <v>12232.896</v>
+        <v>12424.035</v>
       </c>
       <c r="G66">
         <v>2630.8</v>
@@ -6705,37 +6705,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M66">
-        <v>2528.987531024647</v>
+        <v>2568.502961196907</v>
       </c>
       <c r="N66">
-        <v>-1852.087531024647</v>
+        <v>-1891.602961196907</v>
       </c>
       <c r="O66">
-        <v>-463.0218827561617</v>
+        <v>-472.9007402992269</v>
       </c>
       <c r="P66">
-        <v>-1389.065648268485</v>
+        <v>-1418.70222089768</v>
       </c>
       <c r="Q66">
-        <v>-766.9656482684853</v>
+        <v>-796.6022208976805</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.10656907255702</v>
+        <v>0.1083053317729349</v>
       </c>
       <c r="T66">
-        <v>1.18450233355159</v>
+        <v>1.21834525736735</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06691412983417779</v>
+        <v>0.06588468168288274</v>
       </c>
       <c r="W66">
-        <v>0.1929030158536987</v>
+        <v>0.1931158404815269</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2676565193367111</v>
+        <v>0.2635387267315309</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1634321624335197</v>
+        <v>0.1650415286001451</v>
       </c>
       <c r="C67">
-        <v>-6956.631010886831</v>
+        <v>-7186.054780813771</v>
       </c>
       <c r="D67">
-        <v>2836.60398911317</v>
+        <v>2798.31921918623</v>
       </c>
       <c r="E67">
-        <v>-1028.464999999998</v>
+        <v>-837.3259999999991</v>
       </c>
       <c r="F67">
-        <v>12424.035</v>
+        <v>12615.174</v>
       </c>
       <c r="G67">
         <v>2630.8</v>
@@ -6787,37 +6787,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M67">
-        <v>2568.502961196907</v>
+        <v>2608.018391369167</v>
       </c>
       <c r="N67">
-        <v>-1891.602961196907</v>
+        <v>-1931.118391369168</v>
       </c>
       <c r="O67">
-        <v>-472.9007402992269</v>
+        <v>-482.7795978422919</v>
       </c>
       <c r="P67">
-        <v>-1418.70222089768</v>
+        <v>-1448.338793526876</v>
       </c>
       <c r="Q67">
-        <v>-796.6022208976805</v>
+        <v>-826.2387935268756</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1083053317729349</v>
+        <v>0.1101437238839036</v>
       </c>
       <c r="T67">
-        <v>1.21834525736735</v>
+        <v>1.254178941407566</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.06588468168288274</v>
+        <v>0.06488642893011179</v>
       </c>
       <c r="W67">
-        <v>0.1931158404815269</v>
+        <v>0.1933222158782088</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2635387267315309</v>
+        <v>0.2595457157204472</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1650415286001451</v>
+        <v>0.1666508947667704</v>
       </c>
       <c r="C68">
-        <v>-7186.054780813771</v>
+        <v>-7414.458877472485</v>
       </c>
       <c r="D68">
-        <v>2798.31921918623</v>
+        <v>2761.054122527516</v>
       </c>
       <c r="E68">
-        <v>-837.3259999999991</v>
+        <v>-646.1869999999981</v>
       </c>
       <c r="F68">
-        <v>12615.174</v>
+        <v>12806.313</v>
       </c>
       <c r="G68">
         <v>2630.8</v>
@@ -6869,37 +6869,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M68">
-        <v>2608.018391369167</v>
+        <v>2647.533821541427</v>
       </c>
       <c r="N68">
-        <v>-1931.118391369168</v>
+        <v>-1970.633821541428</v>
       </c>
       <c r="O68">
-        <v>-482.7795978422919</v>
+        <v>-492.6584553853569</v>
       </c>
       <c r="P68">
-        <v>-1448.338793526876</v>
+        <v>-1477.975366156071</v>
       </c>
       <c r="Q68">
-        <v>-826.2387935268756</v>
+        <v>-855.8753661560708</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1101437238839036</v>
+        <v>0.1120935336985673</v>
       </c>
       <c r="T68">
-        <v>1.254178941407566</v>
+        <v>1.292184363874462</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.06488642893011179</v>
+        <v>0.06391797476697579</v>
       </c>
       <c r="W68">
-        <v>0.1933222158782088</v>
+        <v>0.1935224308152883</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2595457157204472</v>
+        <v>0.2556718990679031</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1666508947667704</v>
+        <v>0.1682602609333957</v>
       </c>
       <c r="C69">
-        <v>-7414.458877472485</v>
+        <v>-7641.883502336816</v>
       </c>
       <c r="D69">
-        <v>2761.054122527516</v>
+        <v>2724.768497663185</v>
       </c>
       <c r="E69">
-        <v>-646.1869999999981</v>
+        <v>-455.0479999999989</v>
       </c>
       <c r="F69">
-        <v>12806.313</v>
+        <v>12997.452</v>
       </c>
       <c r="G69">
         <v>2630.8</v>
@@ -6951,37 +6951,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M69">
-        <v>2647.533821541427</v>
+        <v>2687.049251713687</v>
       </c>
       <c r="N69">
-        <v>-1970.633821541428</v>
+        <v>-2010.149251713688</v>
       </c>
       <c r="O69">
-        <v>-492.6584553853569</v>
+        <v>-502.5373129284219</v>
       </c>
       <c r="P69">
-        <v>-1477.975366156071</v>
+        <v>-1507.611938785266</v>
       </c>
       <c r="Q69">
-        <v>-855.8753661560708</v>
+        <v>-885.5119387852657</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1120935336985673</v>
+        <v>0.1141652066266476</v>
       </c>
       <c r="T69">
-        <v>1.292184363874462</v>
+        <v>1.332565125245539</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.06391797476697579</v>
+        <v>0.06297800454981439</v>
       </c>
       <c r="W69">
-        <v>0.1935224308152883</v>
+        <v>0.1937167570777478</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2556718990679031</v>
+        <v>0.2519120181992575</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1682602609333957</v>
+        <v>0.1698696271000211</v>
       </c>
       <c r="C70">
-        <v>-7641.883502336816</v>
+        <v>-7868.366770990823</v>
       </c>
       <c r="D70">
-        <v>2724.768497663185</v>
+        <v>2689.424229009179</v>
       </c>
       <c r="E70">
-        <v>-455.0479999999989</v>
+        <v>-263.9089999999978</v>
       </c>
       <c r="F70">
-        <v>12997.452</v>
+        <v>13188.591</v>
       </c>
       <c r="G70">
         <v>2630.8</v>
@@ -7033,37 +7033,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M70">
-        <v>2687.049251713687</v>
+        <v>2726.564681885948</v>
       </c>
       <c r="N70">
-        <v>-2010.149251713688</v>
+        <v>-2049.664681885948</v>
       </c>
       <c r="O70">
-        <v>-502.5373129284219</v>
+        <v>-512.416170471487</v>
       </c>
       <c r="P70">
-        <v>-1507.611938785266</v>
+        <v>-1537.248511414461</v>
       </c>
       <c r="Q70">
-        <v>-885.5119387852657</v>
+        <v>-915.148511414461</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1141652066266476</v>
+        <v>0.1163705358726685</v>
       </c>
       <c r="T70">
-        <v>1.332565125245539</v>
+        <v>1.375551097027653</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.06297800454981439</v>
+        <v>0.06206527984619388</v>
       </c>
       <c r="W70">
-        <v>0.1937167570777478</v>
+        <v>0.1939054506949186</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2519120181992575</v>
+        <v>0.2482611193847755</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1698696271000211</v>
+        <v>0.1714789932666464</v>
       </c>
       <c r="C71">
-        <v>-7868.366770990823</v>
+        <v>-8093.944846681753</v>
       </c>
       <c r="D71">
-        <v>2689.424229009179</v>
+        <v>2654.985153318248</v>
       </c>
       <c r="E71">
-        <v>-263.9089999999978</v>
+        <v>-72.76999999999862</v>
       </c>
       <c r="F71">
-        <v>13188.591</v>
+        <v>13379.73</v>
       </c>
       <c r="G71">
         <v>2630.8</v>
@@ -7115,37 +7115,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M71">
-        <v>2726.564681885948</v>
+        <v>2766.080112058208</v>
       </c>
       <c r="N71">
-        <v>-2049.664681885948</v>
+        <v>-2089.180112058208</v>
       </c>
       <c r="O71">
-        <v>-512.416170471487</v>
+        <v>-522.295028014552</v>
       </c>
       <c r="P71">
-        <v>-1537.248511414461</v>
+        <v>-1566.885084043656</v>
       </c>
       <c r="Q71">
-        <v>-915.148511414461</v>
+        <v>-944.7850840436562</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1163705358726685</v>
+        <v>0.1187228870684241</v>
       </c>
       <c r="T71">
-        <v>1.375551097027653</v>
+        <v>1.421402800261909</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.06206527984619388</v>
+        <v>0.06117863299124825</v>
       </c>
       <c r="W71">
-        <v>0.1939054506949186</v>
+        <v>0.1940887530658846</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2482611193847755</v>
+        <v>0.2447145319649929</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1714789932666464</v>
+        <v>0.1730883594332717</v>
       </c>
       <c r="C72">
-        <v>-8093.944846681753</v>
+        <v>-8318.652063741562</v>
       </c>
       <c r="D72">
-        <v>2654.985153318248</v>
+        <v>2621.416936258441</v>
       </c>
       <c r="E72">
-        <v>-72.76999999999862</v>
+        <v>118.3690000000024</v>
       </c>
       <c r="F72">
-        <v>13379.73</v>
+        <v>13570.869</v>
       </c>
       <c r="G72">
         <v>2630.8</v>
@@ -7197,37 +7197,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M72">
-        <v>2766.080112058208</v>
+        <v>2805.595542230468</v>
       </c>
       <c r="N72">
-        <v>-2089.180112058208</v>
+        <v>-2128.695542230468</v>
       </c>
       <c r="O72">
-        <v>-522.295028014552</v>
+        <v>-532.173885557617</v>
       </c>
       <c r="P72">
-        <v>-1566.885084043656</v>
+        <v>-1596.521656672851</v>
       </c>
       <c r="Q72">
-        <v>-944.7850840436562</v>
+        <v>-974.4216566728511</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1187228870684241</v>
+        <v>0.1212374693811284</v>
       </c>
       <c r="T72">
-        <v>1.421402800261909</v>
+        <v>1.470416689926112</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.06117863299124825</v>
+        <v>0.06031696210404758</v>
       </c>
       <c r="W72">
-        <v>0.1940887530658846</v>
+        <v>0.194266891989781</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2447145319649929</v>
+        <v>0.2412678484161903</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1730883594332717</v>
+        <v>0.1746977255998971</v>
       </c>
       <c r="C73">
-        <v>-8318.65206374156</v>
+        <v>-8542.521041762491</v>
       </c>
       <c r="D73">
-        <v>2621.416936258441</v>
+        <v>2588.686958237507</v>
       </c>
       <c r="E73">
-        <v>118.3690000000006</v>
+        <v>309.5079999999998</v>
       </c>
       <c r="F73">
-        <v>13570.869</v>
+        <v>13762.008</v>
       </c>
       <c r="G73">
         <v>2630.8</v>
@@ -7279,37 +7279,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M73">
-        <v>2805.595542230467</v>
+        <v>2845.110972402727</v>
       </c>
       <c r="N73">
-        <v>-2128.695542230468</v>
+        <v>-2168.210972402728</v>
       </c>
       <c r="O73">
-        <v>-532.1738855576169</v>
+        <v>-542.0527431006819</v>
       </c>
       <c r="P73">
-        <v>-1596.521656672851</v>
+        <v>-1626.158229302046</v>
       </c>
       <c r="Q73">
-        <v>-974.4216566728509</v>
+        <v>-1004.058229302046</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1212374693811283</v>
+        <v>0.1239316647161686</v>
       </c>
       <c r="T73">
-        <v>1.470416689926112</v>
+        <v>1.522931571709187</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.06031696210404758</v>
+        <v>0.05947922651926915</v>
       </c>
       <c r="W73">
-        <v>0.194266891989781</v>
+        <v>0.1944400826102359</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2412678484161903</v>
+        <v>0.2379169060770766</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1746977255998971</v>
+        <v>0.1763070917665224</v>
       </c>
       <c r="C74">
-        <v>-8542.521041762491</v>
+        <v>-8765.582791324832</v>
       </c>
       <c r="D74">
-        <v>2588.686958237507</v>
+        <v>2556.764208675169</v>
       </c>
       <c r="E74">
-        <v>309.5079999999998</v>
+        <v>500.6470000000008</v>
       </c>
       <c r="F74">
-        <v>13762.008</v>
+        <v>13953.147</v>
       </c>
       <c r="G74">
         <v>2630.8</v>
@@ -7361,37 +7361,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M74">
-        <v>2845.110972402727</v>
+        <v>2884.626402574988</v>
       </c>
       <c r="N74">
-        <v>-2168.210972402728</v>
+        <v>-2207.726402574988</v>
       </c>
       <c r="O74">
-        <v>-542.0527431006819</v>
+        <v>-551.9316006437471</v>
       </c>
       <c r="P74">
-        <v>-1626.158229302046</v>
+        <v>-1655.794801931241</v>
       </c>
       <c r="Q74">
-        <v>-1004.058229302046</v>
+        <v>-1033.694801931241</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1239316647161686</v>
+        <v>0.1268254300760267</v>
       </c>
       <c r="T74">
-        <v>1.522931571709187</v>
+        <v>1.579336444735453</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05947922651926915</v>
+        <v>0.05866444259434764</v>
       </c>
       <c r="W74">
-        <v>0.1944400826102359</v>
+        <v>0.1946085282821852</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2379169060770766</v>
+        <v>0.2346577703773906</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1763070917665224</v>
+        <v>0.1779164579331478</v>
       </c>
       <c r="C75">
-        <v>-8765.582791324832</v>
+        <v>-8987.866811997141</v>
       </c>
       <c r="D75">
-        <v>2556.764208675169</v>
+        <v>2525.619188002858</v>
       </c>
       <c r="E75">
-        <v>500.6470000000008</v>
+        <v>691.7860000000001</v>
       </c>
       <c r="F75">
-        <v>13953.147</v>
+        <v>14144.286</v>
       </c>
       <c r="G75">
         <v>2630.8</v>
@@ -7443,37 +7443,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M75">
-        <v>2884.626402574988</v>
+        <v>2924.141832747248</v>
       </c>
       <c r="N75">
-        <v>-2207.726402574988</v>
+        <v>-2247.241832747248</v>
       </c>
       <c r="O75">
-        <v>-551.9316006437471</v>
+        <v>-561.8104581868121</v>
       </c>
       <c r="P75">
-        <v>-1655.794801931241</v>
+        <v>-1685.431374560436</v>
       </c>
       <c r="Q75">
-        <v>-1033.694801931241</v>
+        <v>-1063.331374560436</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1268254300760267</v>
+        <v>0.1299417927712585</v>
       </c>
       <c r="T75">
-        <v>1.579336444735453</v>
+        <v>1.640080154148355</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05866444259434764</v>
+        <v>0.05787167985658619</v>
       </c>
       <c r="W75">
-        <v>0.1946085282821852</v>
+        <v>0.1947724213684061</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2346577703773906</v>
+        <v>0.2314867194263447</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1779164579331478</v>
+        <v>0.1795258240997731</v>
       </c>
       <c r="C76">
-        <v>-8987.866811997141</v>
+        <v>-9209.401183260055</v>
       </c>
       <c r="D76">
-        <v>2525.619188002858</v>
+        <v>2495.223816739945</v>
       </c>
       <c r="E76">
-        <v>691.7860000000001</v>
+        <v>882.9250000000011</v>
       </c>
       <c r="F76">
-        <v>14144.286</v>
+        <v>14335.425</v>
       </c>
       <c r="G76">
         <v>2630.8</v>
@@ -7525,37 +7525,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M76">
-        <v>2924.141832747248</v>
+        <v>2963.657262919508</v>
       </c>
       <c r="N76">
-        <v>-2247.241832747248</v>
+        <v>-2286.757262919508</v>
       </c>
       <c r="O76">
-        <v>-561.8104581868121</v>
+        <v>-571.6893157298771</v>
       </c>
       <c r="P76">
-        <v>-1685.431374560436</v>
+        <v>-1715.067947189631</v>
       </c>
       <c r="Q76">
-        <v>-1063.331374560436</v>
+        <v>-1092.967947189631</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1299417927712585</v>
+        <v>0.1333074644821089</v>
       </c>
       <c r="T76">
-        <v>1.640080154148355</v>
+        <v>1.70568336031429</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05787167985658619</v>
+        <v>0.05710005745849838</v>
       </c>
       <c r="W76">
-        <v>0.1947724213684061</v>
+        <v>0.1949319439723279</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2314867194263447</v>
+        <v>0.2284002298339934</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1795258240997731</v>
+        <v>0.1811351902663984</v>
       </c>
       <c r="C77">
-        <v>-9209.401183260055</v>
+        <v>-9430.21264894259</v>
       </c>
       <c r="D77">
-        <v>2495.223816739945</v>
+        <v>2465.551351057411</v>
       </c>
       <c r="E77">
-        <v>882.9250000000011</v>
+        <v>1074.064000000002</v>
       </c>
       <c r="F77">
-        <v>14335.425</v>
+        <v>14526.564</v>
       </c>
       <c r="G77">
         <v>2630.8</v>
@@ -7607,37 +7607,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M77">
-        <v>2963.657262919508</v>
+        <v>3003.172693091768</v>
       </c>
       <c r="N77">
-        <v>-2286.757262919508</v>
+        <v>-2326.272693091769</v>
       </c>
       <c r="O77">
-        <v>-571.6893157298771</v>
+        <v>-581.5681732729422</v>
       </c>
       <c r="P77">
-        <v>-1715.067947189631</v>
+        <v>-1744.704519818827</v>
       </c>
       <c r="Q77">
-        <v>-1092.967947189631</v>
+        <v>-1122.604519818827</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1333074644821089</v>
+        <v>0.1369536088355301</v>
       </c>
       <c r="T77">
-        <v>1.70568336031429</v>
+        <v>1.776753500327385</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05710005745849838</v>
+        <v>0.05634874091299182</v>
       </c>
       <c r="W77">
-        <v>0.1949319439723279</v>
+        <v>0.1950872686129884</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2284002298339934</v>
+        <v>0.2253949636519672</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1811351902663984</v>
+        <v>0.1827445564330238</v>
       </c>
       <c r="C78">
-        <v>-9430.21264894259</v>
+        <v>-9650.326695704745</v>
       </c>
       <c r="D78">
-        <v>2465.551351057411</v>
+        <v>2436.576304295257</v>
       </c>
       <c r="E78">
-        <v>1074.064000000002</v>
+        <v>1265.203000000001</v>
       </c>
       <c r="F78">
-        <v>14526.564</v>
+        <v>14717.703</v>
       </c>
       <c r="G78">
         <v>2630.8</v>
@@ -7689,37 +7689,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M78">
-        <v>3003.172693091768</v>
+        <v>3042.688123264028</v>
       </c>
       <c r="N78">
-        <v>-2326.272693091769</v>
+        <v>-2365.788123264029</v>
       </c>
       <c r="O78">
-        <v>-581.5681732729422</v>
+        <v>-591.4470308160072</v>
       </c>
       <c r="P78">
-        <v>-1744.704519818827</v>
+        <v>-1774.341092448022</v>
       </c>
       <c r="Q78">
-        <v>-1122.604519818827</v>
+        <v>-1152.241092448022</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1369536088355301</v>
+        <v>0.1409168092196836</v>
       </c>
       <c r="T78">
-        <v>1.776753500327385</v>
+        <v>1.854003652515533</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05634874091299182</v>
+        <v>0.05561693908295296</v>
       </c>
       <c r="W78">
-        <v>0.1950872686129884</v>
+        <v>0.1952385588473981</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2253949636519672</v>
+        <v>0.2224677563318118</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1827445564330238</v>
+        <v>0.1843539225996491</v>
       </c>
       <c r="C79">
-        <v>-9650.326695704745</v>
+        <v>-9869.767626050409</v>
       </c>
       <c r="D79">
-        <v>2436.576304295257</v>
+        <v>2408.274373949593</v>
       </c>
       <c r="E79">
-        <v>1265.203000000001</v>
+        <v>1456.342000000002</v>
       </c>
       <c r="F79">
-        <v>14717.703</v>
+        <v>14908.842</v>
       </c>
       <c r="G79">
         <v>2630.8</v>
@@ -7771,37 +7771,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M79">
-        <v>3042.688123264028</v>
+        <v>3082.203553436289</v>
       </c>
       <c r="N79">
-        <v>-2365.788123264029</v>
+        <v>-2405.303553436289</v>
       </c>
       <c r="O79">
-        <v>-591.4470308160072</v>
+        <v>-601.3258883590722</v>
       </c>
       <c r="P79">
-        <v>-1774.341092448022</v>
+        <v>-1803.977665077217</v>
       </c>
       <c r="Q79">
-        <v>-1152.241092448022</v>
+        <v>-1181.877665077217</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1409168092196836</v>
+        <v>0.145240300547851</v>
       </c>
       <c r="T79">
-        <v>1.854003652515533</v>
+        <v>1.938276545811693</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05561693908295296</v>
+        <v>0.05490390140240228</v>
       </c>
       <c r="W79">
-        <v>0.1952385588473981</v>
+        <v>0.1953859698450281</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2224677563318118</v>
+        <v>0.2196156056096091</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1843539225996491</v>
+        <v>0.1859632887662745</v>
       </c>
       <c r="C80">
-        <v>-9869.767626050409</v>
+        <v>-10088.55862631025</v>
       </c>
       <c r="D80">
-        <v>2408.274373949593</v>
+        <v>2380.62237368975</v>
       </c>
       <c r="E80">
-        <v>1456.342000000002</v>
+        <v>1647.481000000002</v>
       </c>
       <c r="F80">
-        <v>14908.842</v>
+        <v>15099.981</v>
       </c>
       <c r="G80">
         <v>2630.8</v>
@@ -7853,37 +7853,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M80">
-        <v>3082.203553436289</v>
+        <v>3121.718983608549</v>
       </c>
       <c r="N80">
-        <v>-2405.303553436289</v>
+        <v>-2444.818983608549</v>
       </c>
       <c r="O80">
-        <v>-601.3258883590722</v>
+        <v>-611.2047459021372</v>
       </c>
       <c r="P80">
-        <v>-1803.977665077217</v>
+        <v>-1833.614237706412</v>
       </c>
       <c r="Q80">
-        <v>-1181.877665077217</v>
+        <v>-1211.514237706412</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.145240300547851</v>
+        <v>0.1499755529548915</v>
       </c>
       <c r="T80">
-        <v>1.938276545811693</v>
+        <v>2.030575428945584</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05490390140240228</v>
+        <v>0.05420891530870098</v>
       </c>
       <c r="W80">
-        <v>0.1953859698450281</v>
+        <v>0.1955296489186674</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2196156056096091</v>
+        <v>0.2168356612348039</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1859632887662745</v>
+        <v>0.1875726549328998</v>
       </c>
       <c r="C81">
-        <v>-10088.55862631025</v>
+        <v>-10306.72182999425</v>
       </c>
       <c r="D81">
-        <v>2380.62237368975</v>
+        <v>2353.598170005754</v>
       </c>
       <c r="E81">
-        <v>1647.481000000002</v>
+        <v>1838.620000000003</v>
       </c>
       <c r="F81">
-        <v>15099.981</v>
+        <v>15291.12</v>
       </c>
       <c r="G81">
         <v>2630.8</v>
@@ -7935,37 +7935,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M81">
-        <v>3121.718983608549</v>
+        <v>3161.234413780809</v>
       </c>
       <c r="N81">
-        <v>-2444.818983608549</v>
+        <v>-2484.334413780809</v>
       </c>
       <c r="O81">
-        <v>-611.2047459021372</v>
+        <v>-621.0836034452024</v>
       </c>
       <c r="P81">
-        <v>-1833.614237706412</v>
+        <v>-1863.250810335607</v>
       </c>
       <c r="Q81">
-        <v>-1211.514237706412</v>
+        <v>-1241.150810335607</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1499755529548915</v>
+        <v>0.1551843306026361</v>
       </c>
       <c r="T81">
-        <v>2.030575428945584</v>
+        <v>2.132104200392863</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05420891530870098</v>
+        <v>0.05353130386734222</v>
       </c>
       <c r="W81">
-        <v>0.1955296489186674</v>
+        <v>0.1956697360154658</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2168356612348039</v>
+        <v>0.2141252154693688</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1875726549328998</v>
+        <v>0.1891820210995251</v>
       </c>
       <c r="C82">
-        <v>-10306.72182999425</v>
+        <v>-10524.27837687768</v>
       </c>
       <c r="D82">
-        <v>2353.598170005754</v>
+        <v>2327.180623122319</v>
       </c>
       <c r="E82">
-        <v>1838.620000000003</v>
+        <v>2029.759000000002</v>
       </c>
       <c r="F82">
-        <v>15291.12</v>
+        <v>15482.259</v>
       </c>
       <c r="G82">
         <v>2630.8</v>
@@ -8017,37 +8017,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M82">
-        <v>3161.234413780809</v>
+        <v>3200.749843953069</v>
       </c>
       <c r="N82">
-        <v>-2484.334413780809</v>
+        <v>-2523.849843953069</v>
       </c>
       <c r="O82">
-        <v>-621.0836034452024</v>
+        <v>-630.9624609882673</v>
       </c>
       <c r="P82">
-        <v>-1863.250810335607</v>
+        <v>-1892.887382964802</v>
       </c>
       <c r="Q82">
-        <v>-1241.150810335607</v>
+        <v>-1270.787382964802</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1551843306026361</v>
+        <v>0.1609414006343538</v>
       </c>
       <c r="T82">
-        <v>2.132104200392863</v>
+        <v>2.244320210939855</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.05353130386734222</v>
+        <v>0.05287042357268368</v>
       </c>
       <c r="W82">
-        <v>0.1956697360154658</v>
+        <v>0.1958063641716024</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2141252154693688</v>
+        <v>0.2114816942907347</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1891820210995251</v>
+        <v>0.1907913872661505</v>
       </c>
       <c r="C83">
-        <v>-10524.27837687768</v>
+        <v>-10741.24846815212</v>
       </c>
       <c r="D83">
-        <v>2327.180623122319</v>
+        <v>2301.349531847883</v>
       </c>
       <c r="E83">
-        <v>2029.759000000002</v>
+        <v>2220.898000000003</v>
       </c>
       <c r="F83">
-        <v>15482.259</v>
+        <v>15673.398</v>
       </c>
       <c r="G83">
         <v>2630.8</v>
@@ -8099,37 +8099,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M83">
-        <v>3200.749843953069</v>
+        <v>3240.265274125329</v>
       </c>
       <c r="N83">
-        <v>-2523.849843953069</v>
+        <v>-2563.36527412533</v>
       </c>
       <c r="O83">
-        <v>-630.9624609882673</v>
+        <v>-640.8413185313324</v>
       </c>
       <c r="P83">
-        <v>-1892.887382964802</v>
+        <v>-1922.523955593997</v>
       </c>
       <c r="Q83">
-        <v>-1270.787382964802</v>
+        <v>-1300.423955593997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1609414006343538</v>
+        <v>0.1673381451140401</v>
       </c>
       <c r="T83">
-        <v>2.244320210939855</v>
+        <v>2.369004667103181</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.05287042357268368</v>
+        <v>0.05222566230960217</v>
       </c>
       <c r="W83">
-        <v>0.1958063641716024</v>
+        <v>0.1959396599336869</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2114816942907347</v>
+        <v>0.2089026492384086</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1907913872661505</v>
+        <v>0.1924007534327759</v>
       </c>
       <c r="C84">
-        <v>-10741.24846815212</v>
+        <v>-10957.65141794371</v>
       </c>
       <c r="D84">
-        <v>2301.349531847883</v>
+        <v>2276.085582056291</v>
       </c>
       <c r="E84">
-        <v>2220.898000000003</v>
+        <v>2412.037000000002</v>
       </c>
       <c r="F84">
-        <v>15673.398</v>
+        <v>15864.537</v>
       </c>
       <c r="G84">
         <v>2630.8</v>
@@ -8181,37 +8181,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M84">
-        <v>3240.265274125329</v>
+        <v>3279.780704297589</v>
       </c>
       <c r="N84">
-        <v>-2563.36527412533</v>
+        <v>-2602.88070429759</v>
       </c>
       <c r="O84">
-        <v>-640.8413185313324</v>
+        <v>-650.7201760743974</v>
       </c>
       <c r="P84">
-        <v>-1922.523955593997</v>
+        <v>-1952.160528223192</v>
       </c>
       <c r="Q84">
-        <v>-1300.423955593997</v>
+        <v>-1330.060528223192</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1673381451140401</v>
+        <v>0.1744874477678072</v>
       </c>
       <c r="T84">
-        <v>2.369004667103181</v>
+        <v>2.508357882815133</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.05222566230960217</v>
+        <v>0.05159643746249853</v>
       </c>
       <c r="W84">
-        <v>0.1959396599336869</v>
+        <v>0.1960697437496971</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2089026492384086</v>
+        <v>0.206385749849994</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1924007534327759</v>
+        <v>0.1940101195994012</v>
       </c>
       <c r="C85">
-        <v>-10957.65141794371</v>
+        <v>-11173.505701475</v>
       </c>
       <c r="D85">
-        <v>2276.085582056291</v>
+        <v>2251.370298525003</v>
       </c>
       <c r="E85">
-        <v>2412.037000000002</v>
+        <v>2603.176000000003</v>
       </c>
       <c r="F85">
-        <v>15864.537</v>
+        <v>16055.676</v>
       </c>
       <c r="G85">
         <v>2630.8</v>
@@ -8263,37 +8263,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M85">
-        <v>3279.780704297589</v>
+        <v>3319.296134469849</v>
       </c>
       <c r="N85">
-        <v>-2602.88070429759</v>
+        <v>-2642.39613446985</v>
       </c>
       <c r="O85">
-        <v>-650.7201760743974</v>
+        <v>-660.5990336174624</v>
       </c>
       <c r="P85">
-        <v>-1952.160528223192</v>
+        <v>-1981.797100852387</v>
       </c>
       <c r="Q85">
-        <v>-1330.060528223192</v>
+        <v>-1359.697100852387</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1744874477678072</v>
+        <v>0.1825304132532952</v>
       </c>
       <c r="T85">
-        <v>2.508357882815133</v>
+        <v>2.665130250491079</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.05159643746249853</v>
+        <v>0.05098219415937354</v>
       </c>
       <c r="W85">
-        <v>0.1960697437496971</v>
+        <v>0.1961967303319928</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.206385749849994</v>
+        <v>0.2039287766374942</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1940101195994012</v>
+        <v>0.1956194857660265</v>
       </c>
       <c r="C86">
-        <v>-11173.505701475</v>
+        <v>-11388.82900012257</v>
       </c>
       <c r="D86">
-        <v>2251.370298525003</v>
+        <v>2227.185999877431</v>
       </c>
       <c r="E86">
-        <v>2603.176000000001</v>
+        <v>2794.315000000001</v>
       </c>
       <c r="F86">
-        <v>16055.676</v>
+        <v>16246.815</v>
       </c>
       <c r="G86">
         <v>2630.8</v>
@@ -8345,37 +8345,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M86">
-        <v>3319.296134469849</v>
+        <v>3358.811564642109</v>
       </c>
       <c r="N86">
-        <v>-2642.39613446985</v>
+        <v>-2681.911564642109</v>
       </c>
       <c r="O86">
-        <v>-660.5990336174624</v>
+        <v>-670.4778911605273</v>
       </c>
       <c r="P86">
-        <v>-1981.797100852387</v>
+        <v>-2011.433673481582</v>
       </c>
       <c r="Q86">
-        <v>-1359.697100852387</v>
+        <v>-1389.333673481582</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1825304132532951</v>
+        <v>0.1916457741368481</v>
       </c>
       <c r="T86">
-        <v>2.665130250491078</v>
+        <v>2.842805600523816</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.05098219415937354</v>
+        <v>0.05038240363985151</v>
       </c>
       <c r="W86">
-        <v>0.1961967303319928</v>
+        <v>0.1963207289947051</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2039287766374942</v>
+        <v>0.201529614559406</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1956194857660265</v>
+        <v>0.227470567381039</v>
       </c>
       <c r="C87">
-        <v>-11388.82900012257</v>
+        <v>-11970.44557762208</v>
       </c>
       <c r="D87">
-        <v>2227.185999877431</v>
+        <v>1836.708422377924</v>
       </c>
       <c r="E87">
-        <v>2794.315000000001</v>
+        <v>2985.454000000002</v>
       </c>
       <c r="F87">
-        <v>16246.815</v>
+        <v>16437.954</v>
       </c>
       <c r="G87">
         <v>2630.8</v>
@@ -8427,45 +8427,45 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M87">
-        <v>3358.811564642109</v>
+        <v>3973.655384814369</v>
       </c>
       <c r="N87">
-        <v>-2681.911564642109</v>
+        <v>-3296.75538481437</v>
       </c>
       <c r="O87">
-        <v>-670.4778911605273</v>
+        <v>-824.1888462035924</v>
       </c>
       <c r="P87">
-        <v>-2011.433673481582</v>
+        <v>-2472.566538610778</v>
       </c>
       <c r="Q87">
-        <v>-1389.333673481582</v>
+        <v>-1850.466538610778</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1916457741368481</v>
+        <v>0.2030755826351029</v>
       </c>
       <c r="T87">
-        <v>2.842805600523816</v>
+        <v>3.065593842446172</v>
       </c>
       <c r="U87">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.05038240363985151</v>
+        <v>0.04258673277172105</v>
       </c>
       <c r="W87">
-        <v>0.1963207289947051</v>
+        <v>0.2314418439675868</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.201529614559406</v>
+        <v>0.1703469310868841</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.227470567381039</v>
+        <v>0.2294299335476644</v>
       </c>
       <c r="C88">
-        <v>-11970.44557762208</v>
+        <v>-12181.18260432304</v>
       </c>
       <c r="D88">
-        <v>1836.708422377924</v>
+        <v>1817.110395676961</v>
       </c>
       <c r="E88">
-        <v>2985.454000000002</v>
+        <v>3176.593000000001</v>
       </c>
       <c r="F88">
-        <v>16437.954</v>
+        <v>16629.093</v>
       </c>
       <c r="G88">
         <v>2630.8</v>
@@ -8509,37 +8509,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M88">
-        <v>3973.655384814369</v>
+        <v>4019.860679986629</v>
       </c>
       <c r="N88">
-        <v>-3296.75538481437</v>
+        <v>-3342.96067998663</v>
       </c>
       <c r="O88">
-        <v>-824.1888462035924</v>
+        <v>-835.7401699966574</v>
       </c>
       <c r="P88">
-        <v>-2472.566538610778</v>
+        <v>-2507.220509989972</v>
       </c>
       <c r="Q88">
-        <v>-1850.466538610778</v>
+        <v>-1885.120509989972</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2030755826351029</v>
+        <v>0.2151737043762647</v>
       </c>
       <c r="T88">
-        <v>3.065593842446172</v>
+        <v>3.30140875340357</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04258673277172105</v>
+        <v>0.04209723009618403</v>
       </c>
       <c r="W88">
-        <v>0.2314418439675868</v>
+        <v>0.2315601746882184</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1703469310868841</v>
+        <v>0.1683889203847361</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2294299335476644</v>
+        <v>0.2313892997142897</v>
       </c>
       <c r="C89">
-        <v>-12181.18260432304</v>
+        <v>-12391.50581718334</v>
       </c>
       <c r="D89">
-        <v>1817.110395676961</v>
+        <v>1797.926182816663</v>
       </c>
       <c r="E89">
-        <v>3176.593000000001</v>
+        <v>3367.732</v>
       </c>
       <c r="F89">
-        <v>16629.093</v>
+        <v>16820.232</v>
       </c>
       <c r="G89">
         <v>2630.8</v>
@@ -8591,37 +8591,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M89">
-        <v>4019.860679986629</v>
+        <v>4066.065975158889</v>
       </c>
       <c r="N89">
-        <v>-3342.96067998663</v>
+        <v>-3389.16597515889</v>
       </c>
       <c r="O89">
-        <v>-835.7401699966574</v>
+        <v>-847.2914937897224</v>
       </c>
       <c r="P89">
-        <v>-2507.220509989972</v>
+        <v>-2541.874481369167</v>
       </c>
       <c r="Q89">
-        <v>-1885.120509989972</v>
+        <v>-1919.774481369167</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2151737043762647</v>
+        <v>0.2292881797409534</v>
       </c>
       <c r="T89">
-        <v>3.30140875340357</v>
+        <v>3.576526149520534</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04209723009618403</v>
+        <v>0.04161885248145467</v>
       </c>
       <c r="W89">
-        <v>0.2315601746882184</v>
+        <v>0.2316758160742901</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1683889203847361</v>
+        <v>0.1664754099258187</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2313892997142897</v>
+        <v>0.2333486658809151</v>
       </c>
       <c r="C90">
-        <v>-12391.50581718334</v>
+        <v>-12601.42818584211</v>
       </c>
       <c r="D90">
-        <v>1797.926182816663</v>
+        <v>1779.142814157897</v>
       </c>
       <c r="E90">
-        <v>3367.732</v>
+        <v>3558.871000000003</v>
       </c>
       <c r="F90">
-        <v>16820.232</v>
+        <v>17011.371</v>
       </c>
       <c r="G90">
         <v>2630.8</v>
@@ -8673,37 +8673,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M90">
-        <v>4066.065975158889</v>
+        <v>4112.27127033115</v>
       </c>
       <c r="N90">
-        <v>-3389.16597515889</v>
+        <v>-3435.37127033115</v>
       </c>
       <c r="O90">
-        <v>-847.2914937897224</v>
+        <v>-858.8428175827876</v>
       </c>
       <c r="P90">
-        <v>-2541.874481369167</v>
+        <v>-2576.528452748363</v>
       </c>
       <c r="Q90">
-        <v>-1919.774481369167</v>
+        <v>-1954.428452748363</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2292881797409534</v>
+        <v>0.2459689233537674</v>
       </c>
       <c r="T90">
-        <v>3.576526149520534</v>
+        <v>3.901664890386038</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04161885248145467</v>
+        <v>0.04115122492548326</v>
       </c>
       <c r="W90">
-        <v>0.2316758160742901</v>
+        <v>0.2317888587775288</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1664754099258187</v>
+        <v>0.164604899701933</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2333486658809151</v>
+        <v>0.2353080320475404</v>
       </c>
       <c r="C91">
-        <v>-12601.42818584211</v>
+        <v>-12810.9621435544</v>
       </c>
       <c r="D91">
-        <v>1779.142814157897</v>
+        <v>1760.747856445598</v>
       </c>
       <c r="E91">
-        <v>3558.871000000003</v>
+        <v>3750.010000000002</v>
       </c>
       <c r="F91">
-        <v>17011.371</v>
+        <v>17202.51</v>
       </c>
       <c r="G91">
         <v>2630.8</v>
@@ -8755,37 +8755,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M91">
-        <v>4112.27127033115</v>
+        <v>4158.47656550341</v>
       </c>
       <c r="N91">
-        <v>-3435.37127033115</v>
+        <v>-3481.57656550341</v>
       </c>
       <c r="O91">
-        <v>-858.8428175827876</v>
+        <v>-870.3941413758525</v>
       </c>
       <c r="P91">
-        <v>-2576.528452748363</v>
+        <v>-2611.182424127558</v>
       </c>
       <c r="Q91">
-        <v>-1954.428452748363</v>
+        <v>-1989.082424127558</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2459689233537674</v>
+        <v>0.2659858156891441</v>
       </c>
       <c r="T91">
-        <v>3.901664890386038</v>
+        <v>4.291831379424642</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04115122492548326</v>
+        <v>0.0406939890929779</v>
       </c>
       <c r="W91">
-        <v>0.2317888587775288</v>
+        <v>0.2318993894206955</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.164604899701933</v>
+        <v>0.1627759563719116</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2353080320475404</v>
+        <v>0.2372673982141658</v>
       </c>
       <c r="C92">
-        <v>-12810.9621435544</v>
+        <v>-13020.11961463646</v>
       </c>
       <c r="D92">
-        <v>1760.747856445598</v>
+        <v>1742.729385363546</v>
       </c>
       <c r="E92">
-        <v>3750.010000000002</v>
+        <v>3941.149000000001</v>
       </c>
       <c r="F92">
-        <v>17202.51</v>
+        <v>17393.649</v>
       </c>
       <c r="G92">
         <v>2630.8</v>
@@ -8837,37 +8837,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M92">
-        <v>4158.47656550341</v>
+        <v>4204.68186067567</v>
       </c>
       <c r="N92">
-        <v>-3481.57656550341</v>
+        <v>-3527.78186067567</v>
       </c>
       <c r="O92">
-        <v>-870.3941413758525</v>
+        <v>-881.9454651689175</v>
       </c>
       <c r="P92">
-        <v>-2611.182424127558</v>
+        <v>-2645.836395506753</v>
       </c>
       <c r="Q92">
-        <v>-1989.082424127558</v>
+        <v>-2023.736395506753</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2659858156891441</v>
+        <v>0.2904509063212712</v>
       </c>
       <c r="T92">
-        <v>4.291831379424642</v>
+        <v>4.768701532694047</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.0406939890929779</v>
+        <v>0.04024680239964847</v>
       </c>
       <c r="W92">
-        <v>0.2318993894206955</v>
+        <v>0.2320074908189575</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1627759563719116</v>
+        <v>0.1609872095985938</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2372673982141658</v>
+        <v>0.2392267643807911</v>
       </c>
       <c r="C93">
-        <v>-13020.11961463646</v>
+        <v>-13228.91204024276</v>
       </c>
       <c r="D93">
-        <v>1742.729385363546</v>
+        <v>1725.075959757238</v>
       </c>
       <c r="E93">
-        <v>3941.149000000001</v>
+        <v>4132.288</v>
       </c>
       <c r="F93">
-        <v>17393.649</v>
+        <v>17584.788</v>
       </c>
       <c r="G93">
         <v>2630.8</v>
@@ -8919,37 +8919,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M93">
-        <v>4204.68186067567</v>
+        <v>4250.88715584793</v>
       </c>
       <c r="N93">
-        <v>-3527.78186067567</v>
+        <v>-3573.98715584793</v>
       </c>
       <c r="O93">
-        <v>-881.9454651689175</v>
+        <v>-893.4967889619825</v>
       </c>
       <c r="P93">
-        <v>-2645.836395506753</v>
+        <v>-2680.490366885947</v>
       </c>
       <c r="Q93">
-        <v>-2023.736395506753</v>
+        <v>-2058.390366885948</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2904509063212712</v>
+        <v>0.3210322696114302</v>
       </c>
       <c r="T93">
-        <v>4.768701532694047</v>
+        <v>5.364789224280805</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04024680239964847</v>
+        <v>0.03980933715617403</v>
       </c>
       <c r="W93">
-        <v>0.2320074908189575</v>
+        <v>0.2321132421868225</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1609872095985938</v>
+        <v>0.1592373486246961</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2392267643807911</v>
+        <v>0.2411861305474164</v>
       </c>
       <c r="C94">
-        <v>-13228.91204024276</v>
+        <v>-13437.35040259227</v>
       </c>
       <c r="D94">
-        <v>1725.075959757238</v>
+        <v>1707.776597407735</v>
       </c>
       <c r="E94">
-        <v>4132.288</v>
+        <v>4323.427000000003</v>
       </c>
       <c r="F94">
-        <v>17584.788</v>
+        <v>17775.927</v>
       </c>
       <c r="G94">
         <v>2630.8</v>
@@ -9001,37 +9001,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M94">
-        <v>4250.88715584793</v>
+        <v>4297.09245102019</v>
       </c>
       <c r="N94">
-        <v>-3573.98715584793</v>
+        <v>-3620.192451020191</v>
       </c>
       <c r="O94">
-        <v>-893.4967889619825</v>
+        <v>-905.0481127550477</v>
       </c>
       <c r="P94">
-        <v>-2680.490366885947</v>
+        <v>-2715.144338265143</v>
       </c>
       <c r="Q94">
-        <v>-2058.390366885948</v>
+        <v>-2093.044338265143</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3210322696114302</v>
+        <v>0.3603511652702061</v>
       </c>
       <c r="T94">
-        <v>5.364789224280805</v>
+        <v>6.13118768489235</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03980933715617403</v>
+        <v>0.03938127976739796</v>
       </c>
       <c r="W94">
-        <v>0.2321132421868225</v>
+        <v>0.2322167193317226</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1592373486246961</v>
+        <v>0.1575251190695918</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2411861305474164</v>
+        <v>0.2431454967140418</v>
       </c>
       <c r="C95">
-        <v>-13437.35040259227</v>
+        <v>-13645.4452477513</v>
       </c>
       <c r="D95">
-        <v>1707.776597407735</v>
+        <v>1690.820752248704</v>
       </c>
       <c r="E95">
-        <v>4323.427000000003</v>
+        <v>4514.566000000003</v>
       </c>
       <c r="F95">
-        <v>17775.927</v>
+        <v>17967.066</v>
       </c>
       <c r="G95">
         <v>2630.8</v>
@@ -9083,37 +9083,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M95">
-        <v>4297.09245102019</v>
+        <v>4343.29774619245</v>
       </c>
       <c r="N95">
-        <v>-3620.192451020191</v>
+        <v>-3666.397746192451</v>
       </c>
       <c r="O95">
-        <v>-905.0481127550477</v>
+        <v>-916.5994365481126</v>
       </c>
       <c r="P95">
-        <v>-2715.144338265143</v>
+        <v>-2749.798309644338</v>
       </c>
       <c r="Q95">
-        <v>-2093.044338265143</v>
+        <v>-2127.698309644338</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3603511652702061</v>
+        <v>0.4127763594819071</v>
       </c>
       <c r="T95">
-        <v>6.13118768489235</v>
+        <v>7.153052299041075</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03938127976739796</v>
+        <v>0.03896232998263841</v>
       </c>
       <c r="W95">
-        <v>0.2322167193317226</v>
+        <v>0.2323179948352419</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1575251190695918</v>
+        <v>0.1558493199305536</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2431454967140418</v>
+        <v>0.2451048628806671</v>
       </c>
       <c r="C96">
-        <v>-13645.4452477513</v>
+        <v>-13853.20670707266</v>
       </c>
       <c r="D96">
-        <v>1690.820752248704</v>
+        <v>1674.198292927339</v>
       </c>
       <c r="E96">
-        <v>4514.566000000003</v>
+        <v>4705.705000000002</v>
       </c>
       <c r="F96">
-        <v>17967.066</v>
+        <v>18158.205</v>
       </c>
       <c r="G96">
         <v>2630.8</v>
@@ -9165,37 +9165,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M96">
-        <v>4343.29774619245</v>
+        <v>4389.50304136471</v>
       </c>
       <c r="N96">
-        <v>-3666.397746192451</v>
+        <v>-3712.60304136471</v>
       </c>
       <c r="O96">
-        <v>-916.5994365481126</v>
+        <v>-928.1507603411776</v>
       </c>
       <c r="P96">
-        <v>-2749.798309644338</v>
+        <v>-2784.452281023533</v>
       </c>
       <c r="Q96">
-        <v>-2127.698309644338</v>
+        <v>-2162.352281023533</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4127763594819071</v>
+        <v>0.4861716313782887</v>
       </c>
       <c r="T96">
-        <v>7.153052299041075</v>
+        <v>8.583662758849295</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03896232998263841</v>
+        <v>0.03855220019334749</v>
       </c>
       <c r="W96">
-        <v>0.2323179948352419</v>
+        <v>0.2324171382228976</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1558493199305536</v>
+        <v>0.1542088007733899</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2451048628806671</v>
+        <v>0.2470642290472925</v>
       </c>
       <c r="C97">
-        <v>-13853.20670707266</v>
+        <v>-14060.64451738244</v>
       </c>
       <c r="D97">
-        <v>1674.198292927339</v>
+        <v>1657.899482617569</v>
       </c>
       <c r="E97">
-        <v>4705.705000000002</v>
+        <v>4896.844000000005</v>
       </c>
       <c r="F97">
-        <v>18158.205</v>
+        <v>18349.344</v>
       </c>
       <c r="G97">
         <v>2630.8</v>
@@ -9247,37 +9247,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M97">
-        <v>4389.50304136471</v>
+        <v>4435.708336536971</v>
       </c>
       <c r="N97">
-        <v>-3712.60304136471</v>
+        <v>-3758.808336536971</v>
       </c>
       <c r="O97">
-        <v>-928.1507603411776</v>
+        <v>-939.7020841342428</v>
       </c>
       <c r="P97">
-        <v>-2784.452281023533</v>
+        <v>-2819.106252402728</v>
       </c>
       <c r="Q97">
-        <v>-2162.352281023533</v>
+        <v>-2197.006252402728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4861716313782887</v>
+        <v>0.5962645392228612</v>
       </c>
       <c r="T97">
-        <v>8.583662758849295</v>
+        <v>10.72957844856163</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03855220019334749</v>
+        <v>0.03815061477466677</v>
       </c>
       <c r="W97">
-        <v>0.2324171382228976</v>
+        <v>0.2325142161233105</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1542088007733899</v>
+        <v>0.1526024590986671</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2470642290472924</v>
+        <v>0.2490235952139178</v>
       </c>
       <c r="C98">
-        <v>-14060.64451738243</v>
+        <v>-14267.76803999895</v>
       </c>
       <c r="D98">
-        <v>1657.899482617571</v>
+        <v>1641.914960001054</v>
       </c>
       <c r="E98">
-        <v>4896.844000000001</v>
+        <v>5087.983</v>
       </c>
       <c r="F98">
-        <v>18349.344</v>
+        <v>18540.483</v>
       </c>
       <c r="G98">
         <v>2630.8</v>
@@ -9329,37 +9329,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M98">
-        <v>4435.70833653697</v>
+        <v>4481.913631709231</v>
       </c>
       <c r="N98">
-        <v>-3758.80833653697</v>
+        <v>-3805.013631709231</v>
       </c>
       <c r="O98">
-        <v>-939.7020841342426</v>
+        <v>-951.2534079273078</v>
       </c>
       <c r="P98">
-        <v>-2819.106252402727</v>
+        <v>-2853.760223781923</v>
       </c>
       <c r="Q98">
-        <v>-2197.006252402728</v>
+        <v>-2231.660223781923</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5962645392228596</v>
+        <v>0.7797527189638128</v>
       </c>
       <c r="T98">
-        <v>10.7295784485616</v>
+        <v>14.30610459808213</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03815061477466678</v>
+        <v>0.03775730946771145</v>
       </c>
       <c r="W98">
-        <v>0.2325142161233105</v>
+        <v>0.2326092924175293</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1526024590986671</v>
+        <v>0.1510292378708458</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2490235952139178</v>
+        <v>0.2509829613805432</v>
       </c>
       <c r="C99">
-        <v>-14267.76803999895</v>
+        <v>-14474.58627866212</v>
       </c>
       <c r="D99">
-        <v>1641.914960001054</v>
+        <v>1626.235721337882</v>
       </c>
       <c r="E99">
-        <v>5087.983</v>
+        <v>5279.121999999999</v>
       </c>
       <c r="F99">
-        <v>18540.483</v>
+        <v>18731.622</v>
       </c>
       <c r="G99">
         <v>2630.8</v>
@@ -9411,37 +9411,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M99">
-        <v>4481.913631709231</v>
+        <v>4528.118926881491</v>
       </c>
       <c r="N99">
-        <v>-3805.013631709231</v>
+        <v>-3851.218926881491</v>
       </c>
       <c r="O99">
-        <v>-951.2534079273078</v>
+        <v>-962.8047317203727</v>
       </c>
       <c r="P99">
-        <v>-2853.760223781923</v>
+        <v>-2888.414195161118</v>
       </c>
       <c r="Q99">
-        <v>-2231.660223781923</v>
+        <v>-2266.314195161118</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7797527189638128</v>
+        <v>1.146729078445719</v>
       </c>
       <c r="T99">
-        <v>14.30610459808213</v>
+        <v>21.45915689712319</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03775730946771145</v>
+        <v>0.03737203079967358</v>
       </c>
       <c r="W99">
-        <v>0.2326092924175293</v>
+        <v>0.232702428379213</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1510292378708458</v>
+        <v>0.1494881231986943</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2509829613805432</v>
+        <v>0.2529423275471684</v>
       </c>
       <c r="C100">
-        <v>-14474.58627866212</v>
+        <v>-14681.10789644516</v>
       </c>
       <c r="D100">
-        <v>1626.235721337882</v>
+        <v>1610.853103554844</v>
       </c>
       <c r="E100">
-        <v>5279.121999999999</v>
+        <v>5470.261000000002</v>
       </c>
       <c r="F100">
-        <v>18731.622</v>
+        <v>18922.761</v>
       </c>
       <c r="G100">
         <v>2630.8</v>
@@ -9493,37 +9493,37 @@
         <v>676.8999999999997</v>
       </c>
       <c r="M100">
-        <v>4528.118926881491</v>
+        <v>4574.324222053751</v>
       </c>
       <c r="N100">
-        <v>-3851.218926881491</v>
+        <v>-3897.424222053752</v>
       </c>
       <c r="O100">
-        <v>-962.8047317203727</v>
+        <v>-974.3560555134379</v>
       </c>
       <c r="P100">
-        <v>-2888.414195161118</v>
+        <v>-2923.068166540314</v>
       </c>
       <c r="Q100">
-        <v>-2266.314195161118</v>
+        <v>-2300.968166540314</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.146729078445719</v>
+        <v>2.247658156891438</v>
       </c>
       <c r="T100">
-        <v>21.45915689712319</v>
+        <v>42.91831379424638</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03737203079967358</v>
+        <v>0.03699453553907081</v>
       </c>
       <c r="W100">
-        <v>0.232702428379213</v>
+        <v>0.2327936828063172</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1494881231986943</v>
+        <v>0.1479781421562832</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2529423275471684</v>
-      </c>
-      <c r="C101">
-        <v>-14681.10789644516</v>
-      </c>
-      <c r="D101">
-        <v>1610.853103554844</v>
-      </c>
-      <c r="E101">
-        <v>5470.261000000002</v>
-      </c>
-      <c r="F101">
-        <v>18922.761</v>
-      </c>
-      <c r="G101">
-        <v>2630.8</v>
-      </c>
-      <c r="H101">
-        <v>5661.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1299</v>
-      </c>
-      <c r="K101">
-        <v>622.1</v>
-      </c>
-      <c r="L101">
-        <v>676.8999999999997</v>
-      </c>
-      <c r="M101">
-        <v>4574.324222053751</v>
-      </c>
-      <c r="N101">
-        <v>-3897.424222053752</v>
-      </c>
-      <c r="O101">
-        <v>-974.3560555134379</v>
-      </c>
-      <c r="P101">
-        <v>-2923.068166540314</v>
-      </c>
-      <c r="Q101">
-        <v>-2300.968166540314</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.247658156891438</v>
-      </c>
-      <c r="T101">
-        <v>42.91831379424638</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.03699453553907081</v>
-      </c>
-      <c r="W101">
-        <v>0.2327936828063172</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1479781421562832</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
